--- a/research/traditional_assets/database/data/luxembourg/luxembourg_chemical_basic.xlsx
+++ b/research/traditional_assets/database/data/luxembourg/luxembourg_chemical_basic.xlsx
@@ -650,10 +650,10 @@
         <v>0.06605922551252848</v>
       </c>
       <c r="X2">
-        <v>0.1170332546686013</v>
+        <v>0.1169874580192359</v>
       </c>
       <c r="Y2">
-        <v>-0.05097402915607281</v>
+        <v>-0.0509282325067074</v>
       </c>
       <c r="Z2">
         <v>1.615967573831034</v>
@@ -662,10 +662,10 @@
         <v>0.05095742710312144</v>
       </c>
       <c r="AB2">
-        <v>0.08113873548532129</v>
+        <v>0.08111679045532127</v>
       </c>
       <c r="AC2">
-        <v>-0.03018130838219985</v>
+        <v>-0.03015936335219983</v>
       </c>
       <c r="AD2">
         <v>970.5</v>
@@ -787,10 +787,10 @@
         <v>0.06605922551252848</v>
       </c>
       <c r="X3">
-        <v>0.1170332546686013</v>
+        <v>0.1169874580192359</v>
       </c>
       <c r="Y3">
-        <v>-0.05097402915607281</v>
+        <v>-0.0509282325067074</v>
       </c>
       <c r="Z3">
         <v>1.615967573831034</v>
@@ -799,10 +799,10 @@
         <v>0.05095742710312144</v>
       </c>
       <c r="AB3">
-        <v>0.08113873548532129</v>
+        <v>0.08111679045532127</v>
       </c>
       <c r="AC3">
-        <v>-0.03018130838219985</v>
+        <v>-0.03015936335219983</v>
       </c>
       <c r="AD3">
         <v>970.5</v>
@@ -1139,49 +1139,49 @@
         <v>2.46268656716418</v>
       </c>
       <c r="F2">
-        <v>4.53835771766819</v>
+        <v>4.61974176956731</v>
       </c>
       <c r="G2">
         <v>4.16736494008317</v>
       </c>
       <c r="H2">
-        <v>2.80056342528489</v>
+        <v>2.88057952315018</v>
       </c>
       <c r="I2">
         <v>0.520815817224611</v>
       </c>
       <c r="J2">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="K2">
         <v>911.4</v>
       </c>
       <c r="L2">
-        <v>1254.9291125187</v>
+        <v>1281.03876286158</v>
       </c>
       <c r="M2">
         <v>1848.78264625777</v>
       </c>
       <c r="N2">
-        <v>1867.42303870892</v>
+        <v>1912.55251551438</v>
       </c>
       <c r="O2">
         <v>990.5826462577691</v>
       </c>
       <c r="P2">
-        <v>665.693926190219</v>
+        <v>684.713752652797</v>
       </c>
       <c r="Q2">
-        <v>0.0811387354853213</v>
+        <v>0.0811167904553213</v>
       </c>
       <c r="R2">
-        <v>0.0807859884727166</v>
+        <v>0.0799392295299978</v>
       </c>
       <c r="S2">
         <v>0.04811346</v>
       </c>
       <c r="T2">
-        <v>0.04345974</v>
+        <v>0.04150818</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1194,16 +1194,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.117033254668601</v>
+        <v>0.116987458019236</v>
       </c>
       <c r="X2">
-        <v>0.100884737650333</v>
+        <v>0.101556694890622</v>
       </c>
       <c r="Y2">
         <v>1.64405214825025</v>
       </c>
       <c r="Z2">
-        <v>1.27134695292465</v>
+        <v>1.28768348477186</v>
       </c>
       <c r="AA2">
         <v>970.5</v>
@@ -1236,7 +1236,7 @@
         <v>911.4</v>
       </c>
       <c r="AK2">
-        <v>0.043327855959079</v>
+        <v>0.0433</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1424,13 +1424,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.08502941511840185</v>
+        <v>0.08500419409238885</v>
       </c>
       <c r="C2">
-        <v>1718.624801995295</v>
+        <v>1718.661332056717</v>
       </c>
       <c r="D2">
-        <v>1665.424801995295</v>
+        <v>1665.461332056717</v>
       </c>
       <c r="E2">
         <v>-990.5826462577693</v>
@@ -1475,19 +1475,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.08502941511840185</v>
+        <v>0.08500419409238885</v>
       </c>
       <c r="T2">
         <v>0.9054086395470867</v>
       </c>
       <c r="U2">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V2">
         <v>0.2494</v>
       </c>
       <c r="W2">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.08486163715709655</v>
+        <v>0.08482597063232243</v>
       </c>
       <c r="C3">
-        <v>1706.758325937932</v>
+        <v>1707.247319783937</v>
       </c>
       <c r="D3">
-        <v>1672.578152400509</v>
+        <v>1673.067146246515</v>
       </c>
       <c r="E3">
         <v>-971.5628197951916</v>
@@ -1539,37 +1539,37 @@
         <v>174.925</v>
       </c>
       <c r="M3">
-        <v>0.9833250281152669</v>
+        <v>0.9566972710676581</v>
       </c>
       <c r="N3">
-        <v>173.9416749718847</v>
+        <v>173.9683027289323</v>
       </c>
       <c r="O3">
-        <v>43.38105373798804</v>
+        <v>43.38769470059572</v>
       </c>
       <c r="P3">
-        <v>130.5606212338967</v>
+        <v>130.5806080283366</v>
       </c>
       <c r="Q3">
-        <v>252.7606212338966</v>
+        <v>252.7806080283366</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.08532684541120863</v>
+        <v>0.08530143316396205</v>
       </c>
       <c r="T3">
         <v>0.91227328323238</v>
       </c>
       <c r="U3">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V3">
         <v>0.2494</v>
       </c>
       <c r="W3">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>177.891332975911</v>
+        <v>182.8425828002902</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1588,13 +1588,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.08469385919579127</v>
+        <v>0.08464774717225602</v>
       </c>
       <c r="C4">
-        <v>1694.953565255298</v>
+        <v>1695.903094544909</v>
       </c>
       <c r="D4">
-        <v>1679.793218180453</v>
+        <v>1680.742747470064</v>
       </c>
       <c r="E4">
         <v>-952.5429933326139</v>
@@ -1621,37 +1621,37 @@
         <v>174.925</v>
       </c>
       <c r="M4">
-        <v>1.966650056230534</v>
+        <v>1.913394542135316</v>
       </c>
       <c r="N4">
-        <v>172.9583499437694</v>
+        <v>173.0116054578646</v>
       </c>
       <c r="O4">
-        <v>43.1358124759761</v>
+        <v>43.14909440119145</v>
       </c>
       <c r="P4">
-        <v>129.8225374677933</v>
+        <v>129.8625110566732</v>
       </c>
       <c r="Q4">
-        <v>252.0225374677933</v>
+        <v>252.0625110566732</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.08563034570999109</v>
+        <v>0.08560473833903676</v>
       </c>
       <c r="T4">
         <v>0.9192780216867611</v>
       </c>
       <c r="U4">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V4">
         <v>0.2494</v>
       </c>
       <c r="W4">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>88.94566648795549</v>
+        <v>91.42129140014511</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1670,13 +1670,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.08452608123448596</v>
+        <v>0.08446952371218959</v>
       </c>
       <c r="C5">
-        <v>1683.211322079661</v>
+        <v>1684.629621261262</v>
       </c>
       <c r="D5">
-        <v>1687.070801467394</v>
+        <v>1688.489100648995</v>
       </c>
       <c r="E5">
         <v>-933.5231668700362</v>
@@ -1703,37 +1703,37 @@
         <v>174.925</v>
       </c>
       <c r="M5">
-        <v>2.949975084345801</v>
+        <v>2.870091813202974</v>
       </c>
       <c r="N5">
-        <v>171.9750249156542</v>
+        <v>172.054908186797</v>
       </c>
       <c r="O5">
-        <v>42.89057121396415</v>
+        <v>42.91049410178717</v>
       </c>
       <c r="P5">
-        <v>129.08445370169</v>
+        <v>129.1444140850098</v>
       </c>
       <c r="Q5">
-        <v>251.28445370169</v>
+        <v>251.3444140850098</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.08594010374689275</v>
+        <v>0.08591429722906144</v>
       </c>
       <c r="T5">
         <v>0.9264271877381395</v>
       </c>
       <c r="U5">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V5">
         <v>0.2494</v>
       </c>
       <c r="W5">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>59.29711099197032</v>
+        <v>60.94752760009673</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1752,13 +1752,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.08435830327318067</v>
+        <v>0.08429130025212318</v>
       </c>
       <c r="C6">
-        <v>1671.532412504491</v>
+        <v>1673.427882725852</v>
       </c>
       <c r="D6">
-        <v>1694.411718354801</v>
+        <v>1696.307188576162</v>
       </c>
       <c r="E6">
         <v>-914.5033404074585</v>
@@ -1785,37 +1785,37 @@
         <v>174.925</v>
       </c>
       <c r="M6">
-        <v>3.933300112461068</v>
+        <v>3.826789084270632</v>
       </c>
       <c r="N6">
-        <v>170.9916998875389</v>
+        <v>171.0982109157293</v>
       </c>
       <c r="O6">
-        <v>42.6453299519522</v>
+        <v>42.67189380238289</v>
       </c>
       <c r="P6">
-        <v>128.3463699355867</v>
+        <v>128.4263171133464</v>
       </c>
       <c r="Q6">
-        <v>250.5463699355867</v>
+        <v>250.6263171133464</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.08625631507622987</v>
+        <v>0.08623030526262832</v>
       </c>
       <c r="T6">
         <v>0.9337252947489219</v>
       </c>
       <c r="U6">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V6">
         <v>0.2494</v>
       </c>
       <c r="W6">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>44.47283324397774</v>
+        <v>45.71064570007255</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1834,13 +1834,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.08419052531187537</v>
+        <v>0.08411307679205676</v>
       </c>
       <c r="C7">
-        <v>1659.917666889542</v>
+        <v>1662.298880018422</v>
       </c>
       <c r="D7">
-        <v>1701.81679920243</v>
+        <v>1704.19801233131</v>
       </c>
       <c r="E7">
         <v>-895.4835139448808</v>
@@ -1867,37 +1867,37 @@
         <v>174.925</v>
       </c>
       <c r="M7">
-        <v>4.916625140576335</v>
+        <v>4.78348635533829</v>
       </c>
       <c r="N7">
-        <v>170.0083748594236</v>
+        <v>170.1415136446617</v>
       </c>
       <c r="O7">
-        <v>42.40008868994025</v>
+        <v>42.43329350297862</v>
       </c>
       <c r="P7">
-        <v>127.6082861694834</v>
+        <v>127.7082201416831</v>
       </c>
       <c r="Q7">
-        <v>249.8082861694834</v>
+        <v>249.908220141683</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.08657918348618461</v>
+        <v>0.08655296609690186</v>
       </c>
       <c r="T7">
         <v>0.9411770461178258</v>
       </c>
       <c r="U7">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V7">
         <v>0.2494</v>
       </c>
       <c r="W7">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>35.57826659518219</v>
+        <v>36.56851656005804</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1916,13 +1916,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.08402274735057008</v>
+        <v>0.08393485333199034</v>
       </c>
       <c r="C8">
-        <v>1648.367930173954</v>
+        <v>1651.243632932926</v>
       </c>
       <c r="D8">
-        <v>1709.28688894942</v>
+        <v>1712.162591708392</v>
       </c>
       <c r="E8">
         <v>-876.4636874823032</v>
@@ -1949,37 +1949,37 @@
         <v>174.925</v>
       </c>
       <c r="M8">
-        <v>5.899950168691602</v>
+        <v>5.740183626405948</v>
       </c>
       <c r="N8">
-        <v>169.0250498313084</v>
+        <v>169.184816373594</v>
       </c>
       <c r="O8">
-        <v>42.15484742792831</v>
+        <v>42.19469320357435</v>
       </c>
       <c r="P8">
-        <v>126.8702024033801</v>
+        <v>126.9901231700197</v>
       </c>
       <c r="Q8">
-        <v>249.0702024033801</v>
+        <v>249.1901231700197</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.08690892143677668</v>
+        <v>0.08688249205530887</v>
       </c>
       <c r="T8">
         <v>0.9487873453881958</v>
       </c>
       <c r="U8">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V8">
         <v>0.2494</v>
       </c>
       <c r="W8">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>29.64855549598516</v>
+        <v>30.47376380004837</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1998,13 +1998,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.08385496938926479</v>
+        <v>0.08375662987192393</v>
       </c>
       <c r="C9">
-        <v>1636.884062197647</v>
+        <v>1640.263180416881</v>
       </c>
       <c r="D9">
-        <v>1716.822847435691</v>
+        <v>1720.201965654925</v>
       </c>
       <c r="E9">
         <v>-857.4438610197254</v>
@@ -2031,37 +2031,37 @@
         <v>174.925</v>
       </c>
       <c r="M9">
-        <v>6.88327519680687</v>
+        <v>6.696880897473608</v>
       </c>
       <c r="N9">
-        <v>168.0417248031931</v>
+        <v>168.2281191025263</v>
       </c>
       <c r="O9">
-        <v>41.90960616591636</v>
+        <v>41.95609290417007</v>
       </c>
       <c r="P9">
-        <v>126.1321186372767</v>
+        <v>126.2720261983563</v>
       </c>
       <c r="Q9">
-        <v>248.3321186372767</v>
+        <v>248.4720261983562</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.08724575052609118</v>
+        <v>0.0872191045934666</v>
       </c>
       <c r="T9">
         <v>0.9565613070084664</v>
       </c>
       <c r="U9">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V9">
         <v>0.2494</v>
       </c>
       <c r="W9">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>25.41304756798728</v>
+        <v>26.12036897147002</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2080,13 +2080,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.0836871914279595</v>
+        <v>0.08357840641185751</v>
       </c>
       <c r="C10">
-        <v>1625.466938031248</v>
+        <v>1629.358581023168</v>
       </c>
       <c r="D10">
-        <v>1724.42554973187</v>
+        <v>1728.31719272379</v>
       </c>
       <c r="E10">
         <v>-838.4240345571477</v>
@@ -2113,37 +2113,37 @@
         <v>174.925</v>
       </c>
       <c r="M10">
-        <v>7.866600224922135</v>
+        <v>7.653578168541265</v>
       </c>
       <c r="N10">
-        <v>167.0583997750778</v>
+        <v>167.2714218314587</v>
       </c>
       <c r="O10">
-        <v>41.66436490390441</v>
+        <v>41.7174926047658</v>
       </c>
       <c r="P10">
-        <v>125.3940348711734</v>
+        <v>125.5539292266929</v>
       </c>
       <c r="Q10">
-        <v>247.5940348711734</v>
+        <v>247.7539292266929</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.08758990198691249</v>
+        <v>0.08756303479549729</v>
       </c>
       <c r="T10">
         <v>0.9645042677943949</v>
       </c>
       <c r="U10">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V10">
         <v>0.2494</v>
       </c>
       <c r="W10">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>22.23641662198887</v>
+        <v>22.85532285003628</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2162,13 +2162,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.0835194134666542</v>
+        <v>0.08340018295179111</v>
       </c>
       <c r="C11">
-        <v>1614.117448314827</v>
+        <v>1618.53091337467</v>
       </c>
       <c r="D11">
-        <v>1732.095886478027</v>
+        <v>1736.509351537869</v>
       </c>
       <c r="E11">
         <v>-819.4042080945701</v>
@@ -2195,37 +2195,37 @@
         <v>174.925</v>
       </c>
       <c r="M11">
-        <v>8.849925253037403</v>
+        <v>8.610275439608923</v>
       </c>
       <c r="N11">
-        <v>166.0750747469625</v>
+        <v>166.314724560391</v>
       </c>
       <c r="O11">
-        <v>41.41912364189246</v>
+        <v>41.47889230536153</v>
       </c>
       <c r="P11">
-        <v>124.6559511050701</v>
+        <v>124.8358322550295</v>
       </c>
       <c r="Q11">
-        <v>246.8559511050701</v>
+        <v>247.0358322550295</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.08794161721610352</v>
+        <v>0.08791452390306714</v>
       </c>
       <c r="T11">
         <v>0.9726217991470472</v>
       </c>
       <c r="U11">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V11">
         <v>0.2494</v>
       </c>
       <c r="W11">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>19.7657036639901</v>
+        <v>20.31584253336558</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2244,13 +2244,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.08335163550534892</v>
+        <v>0.08322195949172469</v>
       </c>
       <c r="C12">
-        <v>1602.836499605714</v>
+        <v>1607.781276642194</v>
       </c>
       <c r="D12">
-        <v>1739.834764231491</v>
+        <v>1744.779541267971</v>
       </c>
       <c r="E12">
         <v>-800.3843816319924</v>
@@ -2277,37 +2277,37 @@
         <v>174.925</v>
       </c>
       <c r="M12">
-        <v>9.833250281152671</v>
+        <v>9.566972710676581</v>
       </c>
       <c r="N12">
-        <v>165.0917497188473</v>
+        <v>165.3580272893234</v>
       </c>
       <c r="O12">
-        <v>41.17388237988052</v>
+        <v>41.24029200595726</v>
       </c>
       <c r="P12">
-        <v>123.9178673389668</v>
+        <v>124.1177352833661</v>
       </c>
       <c r="Q12">
-        <v>246.1178673389668</v>
+        <v>246.3177352833661</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.08830114833927658</v>
+        <v>0.08827382387969408</v>
       </c>
       <c r="T12">
         <v>0.9809197200853137</v>
       </c>
       <c r="U12">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V12">
         <v>0.2494</v>
       </c>
       <c r="W12">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>17.7891332975911</v>
+        <v>18.28425828002902</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2326,13 +2326,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.0831838575440436</v>
+        <v>0.08304373603165827</v>
       </c>
       <c r="C13">
-        <v>1591.62501473568</v>
+        <v>1597.110791036118</v>
       </c>
       <c r="D13">
-        <v>1747.643105824035</v>
+        <v>1753.128882124473</v>
       </c>
       <c r="E13">
         <v>-781.3645551694146</v>
@@ -2359,37 +2359,37 @@
         <v>174.925</v>
       </c>
       <c r="M13">
-        <v>10.81657530926794</v>
+        <v>10.52366998174424</v>
       </c>
       <c r="N13">
-        <v>164.108424690732</v>
+        <v>164.4013300182557</v>
       </c>
       <c r="O13">
-        <v>40.92864111786857</v>
+        <v>41.00169170655298</v>
       </c>
       <c r="P13">
-        <v>123.1797835728635</v>
+        <v>123.3996383117027</v>
       </c>
       <c r="Q13">
-        <v>245.3797835728635</v>
+        <v>245.5996383117027</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.08866875881353214</v>
+        <v>0.08864119801309917</v>
       </c>
       <c r="T13">
         <v>0.9894041111570246</v>
       </c>
       <c r="U13">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V13">
         <v>0.2494</v>
       </c>
       <c r="W13">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>16.17193936144645</v>
+        <v>16.62205298184456</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2408,13 +2408,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.08301607958273832</v>
+        <v>0.08286551257159183</v>
       </c>
       <c r="C14">
-        <v>1580.483933177775</v>
+        <v>1586.520598312211</v>
       </c>
       <c r="D14">
-        <v>1755.521850728707</v>
+        <v>1761.558515863144</v>
       </c>
       <c r="E14">
         <v>-762.344728706837</v>
@@ -2441,37 +2441,37 @@
         <v>174.925</v>
       </c>
       <c r="M14">
-        <v>11.7999003373832</v>
+        <v>11.4803672528119</v>
       </c>
       <c r="N14">
-        <v>163.1250996626167</v>
+        <v>163.4446327471881</v>
       </c>
       <c r="O14">
-        <v>40.68339985585662</v>
+        <v>40.7630914071487</v>
       </c>
       <c r="P14">
-        <v>122.4416998067601</v>
+        <v>122.6815413400394</v>
       </c>
       <c r="Q14">
-        <v>244.6416998067601</v>
+        <v>244.8815413400393</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.08904472407129355</v>
+        <v>0.08901692155862709</v>
       </c>
       <c r="T14">
         <v>0.9980813292985471</v>
       </c>
       <c r="U14">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V14">
         <v>0.2494</v>
       </c>
       <c r="W14">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>14.82427774799258</v>
+        <v>15.23688190002418</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2490,13 +2490,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.08284830162143303</v>
+        <v>0.08268728911152542</v>
       </c>
       <c r="C15">
-        <v>1569.414211423148</v>
+        <v>1576.011862292126</v>
       </c>
       <c r="D15">
-        <v>1763.471955436658</v>
+        <v>1770.069606305636</v>
       </c>
       <c r="E15">
         <v>-743.3249022442592</v>
@@ -2523,37 +2523,37 @@
         <v>174.925</v>
       </c>
       <c r="M15">
-        <v>12.78322536549847</v>
+        <v>12.43706452387956</v>
       </c>
       <c r="N15">
-        <v>162.1417746345015</v>
+        <v>162.4879354761204</v>
       </c>
       <c r="O15">
-        <v>40.43815859384467</v>
+        <v>40.52449110774443</v>
       </c>
       <c r="P15">
-        <v>121.7036160406568</v>
+        <v>121.963444368376</v>
       </c>
       <c r="Q15">
-        <v>243.9036160406568</v>
+        <v>244.163444368376</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.08942933220854371</v>
+        <v>0.08940128242704071</v>
       </c>
       <c r="T15">
         <v>1.006958023719185</v>
       </c>
       <c r="U15">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V15">
         <v>0.2494</v>
       </c>
       <c r="W15">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>13.68394869045469</v>
+        <v>14.06481406156079</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2572,13 +2572,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.08279611606012775</v>
+        <v>0.08250906565145902</v>
       </c>
       <c r="C16">
-        <v>1552.881883207441</v>
+        <v>1565.585769399055</v>
       </c>
       <c r="D16">
-        <v>1765.959453683529</v>
+        <v>1778.663339875143</v>
       </c>
       <c r="E16">
         <v>-724.3050757816816</v>
@@ -2605,45 +2605,45 @@
         <v>174.925</v>
       </c>
       <c r="M16">
-        <v>14.05945572113744</v>
+        <v>13.39376179494722</v>
       </c>
       <c r="N16">
-        <v>160.8655442788625</v>
+        <v>161.5312382050527</v>
       </c>
       <c r="O16">
-        <v>40.11986674314831</v>
+        <v>40.28589080834016</v>
       </c>
       <c r="P16">
-        <v>120.7456775357142</v>
+        <v>121.2453473967126</v>
       </c>
       <c r="Q16">
-        <v>242.9456775357142</v>
+        <v>243.4453473967126</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.08982288472107877</v>
+        <v>0.08979458192030118</v>
       </c>
       <c r="T16">
         <v>1.016041152893792</v>
       </c>
       <c r="U16">
-        <v>0.05280000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V16">
         <v>0.2494</v>
       </c>
       <c r="W16">
-        <v>0.03963168</v>
+        <v>0.03775518</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>Aaa/AAA</t>
         </is>
       </c>
       <c r="Y16">
-        <v>12.44180453849377</v>
+        <v>13.06018448573501</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2654,13 +2654,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.08263659469882242</v>
+        <v>0.08249972719139259</v>
       </c>
       <c r="C17">
-        <v>1541.509567552115</v>
+        <v>1547.018534218272</v>
       </c>
       <c r="D17">
-        <v>1773.606964490781</v>
+        <v>1779.115931156937</v>
       </c>
       <c r="E17">
         <v>-705.285249319104</v>
@@ -2687,37 +2687,37 @@
         <v>174.925</v>
       </c>
       <c r="M17">
-        <v>15.06370255836153</v>
+        <v>14.77840516142287</v>
       </c>
       <c r="N17">
-        <v>159.8612974416384</v>
+        <v>160.1465948385771</v>
       </c>
       <c r="O17">
-        <v>39.86940758194462</v>
+        <v>39.94056075274112</v>
       </c>
       <c r="P17">
-        <v>119.9918898596938</v>
+        <v>120.206034085836</v>
       </c>
       <c r="Q17">
-        <v>242.1918898596938</v>
+        <v>242.4060340858359</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.09022569729273228</v>
+        <v>0.0901971355192854</v>
       </c>
       <c r="T17">
         <v>1.025338002754859</v>
       </c>
       <c r="U17">
-        <v>0.05280000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V17">
         <v>0.2494</v>
       </c>
       <c r="W17">
-        <v>0.03963168</v>
+        <v>0.03888108</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>11.61235090259419</v>
+        <v>11.83652756094543</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2736,13 +2736,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.08247707333751715</v>
+        <v>0.08233276273132617</v>
       </c>
       <c r="C18">
-        <v>1530.203775270849</v>
+        <v>1536.129741617704</v>
       </c>
       <c r="D18">
-        <v>1781.320998672092</v>
+        <v>1787.246965018947</v>
       </c>
       <c r="E18">
         <v>-686.2654228565261</v>
@@ -2769,37 +2769,37 @@
         <v>174.925</v>
       </c>
       <c r="M18">
-        <v>16.06794939558564</v>
+        <v>15.76363217218439</v>
       </c>
       <c r="N18">
-        <v>158.8570506044143</v>
+        <v>159.1613678278156</v>
       </c>
       <c r="O18">
-        <v>39.61894842074094</v>
+        <v>39.6948451362572</v>
       </c>
       <c r="P18">
-        <v>119.2381021836734</v>
+        <v>119.4665226915584</v>
       </c>
       <c r="Q18">
-        <v>241.4381021836734</v>
+        <v>241.6665226915583</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.09063810063990137</v>
+        <v>0.09060927372776925</v>
       </c>
       <c r="T18">
         <v>1.034856206184047</v>
       </c>
       <c r="U18">
-        <v>0.05280000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V18">
         <v>0.2494</v>
       </c>
       <c r="W18">
-        <v>0.03963168</v>
+        <v>0.03888108</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>10.88657897118205</v>
+        <v>11.09674458838634</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2818,13 +2818,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.08231755197621186</v>
+        <v>0.08216579827125975</v>
       </c>
       <c r="C19">
-        <v>1518.965378155315</v>
+        <v>1525.315612230545</v>
       </c>
       <c r="D19">
-        <v>1789.102428019135</v>
+        <v>1795.452662094366</v>
       </c>
       <c r="E19">
         <v>-667.2455963939485</v>
@@ -2851,37 +2851,37 @@
         <v>174.925</v>
       </c>
       <c r="M19">
-        <v>17.07219623280974</v>
+        <v>16.74885918294592</v>
       </c>
       <c r="N19">
-        <v>157.8528037671902</v>
+        <v>158.176140817054</v>
       </c>
       <c r="O19">
-        <v>39.36848925953724</v>
+        <v>39.44912951977328</v>
       </c>
       <c r="P19">
-        <v>118.484314507653</v>
+        <v>118.7270112972808</v>
       </c>
       <c r="Q19">
-        <v>240.684314507653</v>
+        <v>240.9270112972807</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.09106044141712272</v>
+        <v>0.09103134297742138</v>
       </c>
       <c r="T19">
         <v>1.044603763912734</v>
       </c>
       <c r="U19">
-        <v>0.05280000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V19">
         <v>0.2494</v>
       </c>
       <c r="W19">
-        <v>0.03963168</v>
+        <v>0.03888108</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>10.24619197287722</v>
+        <v>10.44399490671655</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2900,13 +2900,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.08245526821490656</v>
+        <v>0.08199883381119334</v>
       </c>
       <c r="C20">
-        <v>1493.223776924052</v>
+        <v>1514.577179192544</v>
       </c>
       <c r="D20">
-        <v>1782.38065325045</v>
+        <v>1803.734055518943</v>
       </c>
       <c r="E20">
         <v>-648.2257699313708</v>
@@ -2933,45 +2933,45 @@
         <v>174.925</v>
       </c>
       <c r="M20">
-        <v>18.82962819795192</v>
+        <v>17.73408619370744</v>
       </c>
       <c r="N20">
-        <v>156.095371802048</v>
+        <v>157.1909138062925</v>
       </c>
       <c r="O20">
-        <v>38.93018572743077</v>
+        <v>39.20341390328935</v>
       </c>
       <c r="P20">
-        <v>117.1651860746173</v>
+        <v>117.9874999030032</v>
       </c>
       <c r="Q20">
-        <v>239.3651860746172</v>
+        <v>240.1874999030032</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.09149308318891045</v>
+        <v>0.09146370659901626</v>
       </c>
       <c r="T20">
         <v>1.054589066951877</v>
       </c>
       <c r="U20">
-        <v>0.05500000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V20">
         <v>0.2494</v>
       </c>
       <c r="W20">
-        <v>0.041283</v>
+        <v>0.03888108</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y20">
-        <v>9.289880722075349</v>
+        <v>9.863772967454523</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2982,13 +2982,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.08231226005360127</v>
+        <v>0.08207431315112691</v>
       </c>
       <c r="C21">
-        <v>1481.185029682351</v>
+        <v>1491.804155381775</v>
       </c>
       <c r="D21">
-        <v>1789.361732471328</v>
+        <v>1799.980858170752</v>
       </c>
       <c r="E21">
         <v>-629.2059434687931</v>
@@ -3015,37 +3015,37 @@
         <v>174.925</v>
       </c>
       <c r="M21">
-        <v>19.87571865339369</v>
+        <v>19.33365359921023</v>
       </c>
       <c r="N21">
-        <v>155.0492813466063</v>
+        <v>155.5913464007897</v>
       </c>
       <c r="O21">
-        <v>38.66929076784361</v>
+        <v>38.80448179235696</v>
       </c>
       <c r="P21">
-        <v>116.3799905787627</v>
+        <v>116.7868646084328</v>
       </c>
       <c r="Q21">
-        <v>238.5799905787626</v>
+        <v>238.9868646084327</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.09193640747358181</v>
+        <v>0.09190674586558878</v>
       </c>
       <c r="T21">
         <v>1.064820920683344</v>
       </c>
       <c r="U21">
-        <v>0.05500000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V21">
         <v>0.2494</v>
       </c>
       <c r="W21">
-        <v>0.041283</v>
+        <v>0.0401571</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.800939631439807</v>
+        <v>9.047694948209147</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3064,13 +3064,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.08216925189229597</v>
+        <v>0.08192010889106051</v>
       </c>
       <c r="C22">
-        <v>1469.201183284159</v>
+        <v>1480.468821709766</v>
       </c>
       <c r="D22">
-        <v>1796.397712535713</v>
+        <v>1807.66535096132</v>
       </c>
       <c r="E22">
         <v>-610.1861170062155</v>
@@ -3097,37 +3097,37 @@
         <v>174.925</v>
       </c>
       <c r="M22">
-        <v>20.92180910883546</v>
+        <v>20.35121431495813</v>
       </c>
       <c r="N22">
-        <v>154.0031908911645</v>
+        <v>154.5737856850418</v>
       </c>
       <c r="O22">
-        <v>38.40839580825642</v>
+        <v>38.55070214984944</v>
       </c>
       <c r="P22">
-        <v>115.5947950829081</v>
+        <v>116.0230835351924</v>
       </c>
       <c r="Q22">
-        <v>237.7947950829081</v>
+        <v>238.2230835351924</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.09239081486536996</v>
+        <v>0.09236086111382563</v>
       </c>
       <c r="T22">
         <v>1.075308570758098</v>
       </c>
       <c r="U22">
-        <v>0.05500000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V22">
         <v>0.2494</v>
       </c>
       <c r="W22">
-        <v>0.041283</v>
+        <v>0.0401571</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.360892649867814</v>
+        <v>8.595310200798689</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3146,13 +3146,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.08202624373099068</v>
+        <v>0.08176590463099409</v>
       </c>
       <c r="C23">
-        <v>1457.272887915736</v>
+        <v>1469.199382753151</v>
       </c>
       <c r="D23">
-        <v>1803.489243629868</v>
+        <v>1815.415738467283</v>
       </c>
       <c r="E23">
         <v>-591.1662905436377</v>
@@ -3179,37 +3179,37 @@
         <v>174.925</v>
       </c>
       <c r="M23">
-        <v>21.96789956427724</v>
+        <v>21.36877503070604</v>
       </c>
       <c r="N23">
-        <v>152.9571004357227</v>
+        <v>153.5562249692939</v>
       </c>
       <c r="O23">
-        <v>38.14750084866925</v>
+        <v>38.2969225073419</v>
       </c>
       <c r="P23">
-        <v>114.8095995870535</v>
+        <v>115.259302461952</v>
       </c>
       <c r="Q23">
-        <v>237.0095995870535</v>
+        <v>237.459302461952</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.09285672624176035</v>
+        <v>0.09282647295062542</v>
       </c>
       <c r="T23">
         <v>1.086061730961326</v>
       </c>
       <c r="U23">
-        <v>0.05500000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V23">
         <v>0.2494</v>
       </c>
       <c r="W23">
-        <v>0.041283</v>
+        <v>0.0401571</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>7.962754904636014</v>
+        <v>8.186009715046371</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3228,13 +3228,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.08213093356968539</v>
+        <v>0.08161170037092767</v>
       </c>
       <c r="C24">
-        <v>1433.056195326911</v>
+        <v>1457.996689734774</v>
       </c>
       <c r="D24">
-        <v>1798.29237750362</v>
+        <v>1823.232871911483</v>
       </c>
       <c r="E24">
         <v>-572.14646408106</v>
@@ -3261,45 +3261,45 @@
         <v>174.925</v>
       </c>
       <c r="M24">
-        <v>23.64164429298408</v>
+        <v>22.38633574645395</v>
       </c>
       <c r="N24">
-        <v>151.2833557070159</v>
+        <v>152.538664253546</v>
       </c>
       <c r="O24">
-        <v>37.73006891332977</v>
+        <v>38.04314286483438</v>
       </c>
       <c r="P24">
-        <v>113.5532867936861</v>
+        <v>114.4955213887116</v>
       </c>
       <c r="Q24">
-        <v>235.7532867936861</v>
+        <v>236.6955213887116</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.09333458406369921</v>
+        <v>0.09330402355247136</v>
       </c>
       <c r="T24">
         <v>1.097090613221048</v>
       </c>
       <c r="U24">
-        <v>0.05650000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V24">
         <v>0.2494</v>
       </c>
       <c r="W24">
-        <v>0.0424089</v>
+        <v>0.0401571</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>7.399020044130809</v>
+        <v>7.813918364362444</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3310,13 +3310,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.0819991844083801</v>
+        <v>0.08159560651086124</v>
       </c>
       <c r="C25">
-        <v>1420.5813647362</v>
+        <v>1439.796596685574</v>
       </c>
       <c r="D25">
-        <v>1804.837373375487</v>
+        <v>1824.052605324861</v>
       </c>
       <c r="E25">
         <v>-553.1266376184824</v>
@@ -3343,37 +3343,37 @@
         <v>174.925</v>
       </c>
       <c r="M25">
-        <v>24.71626448811972</v>
+        <v>23.75386126911328</v>
       </c>
       <c r="N25">
-        <v>150.2087355118802</v>
+        <v>151.1711387308867</v>
       </c>
       <c r="O25">
-        <v>37.46205863666293</v>
+        <v>37.70208199948313</v>
       </c>
       <c r="P25">
-        <v>112.7466768752173</v>
+        <v>113.4690567314035</v>
       </c>
       <c r="Q25">
-        <v>234.9466768752173</v>
+        <v>235.6690567314035</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.093824853777117</v>
+        <v>0.09379397806605357</v>
       </c>
       <c r="T25">
         <v>1.108405959955048</v>
       </c>
       <c r="U25">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V25">
         <v>0.2494</v>
       </c>
       <c r="W25">
-        <v>0.0424089</v>
+        <v>0.04075758</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>7.077323520472949</v>
+        <v>7.364065909884376</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3392,13 +3392,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.08186743524707479</v>
+        <v>0.08144740705079483</v>
       </c>
       <c r="C26">
-        <v>1408.154350005474</v>
+        <v>1428.360031772895</v>
       </c>
       <c r="D26">
-        <v>1811.430185107338</v>
+        <v>1831.63586687476</v>
       </c>
       <c r="E26">
         <v>-534.1068111559047</v>
@@ -3425,37 +3425,37 @@
         <v>174.925</v>
       </c>
       <c r="M26">
-        <v>25.79088468325536</v>
+        <v>24.78663784603125</v>
       </c>
       <c r="N26">
-        <v>149.1341153167446</v>
+        <v>150.1383621539687</v>
       </c>
       <c r="O26">
-        <v>37.19404835999611</v>
+        <v>37.4445075211998</v>
       </c>
       <c r="P26">
-        <v>111.9400669567485</v>
+        <v>112.6938546327689</v>
       </c>
       <c r="Q26">
-        <v>234.1400669567485</v>
+        <v>234.8938546327689</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.0943280253250984</v>
+        <v>0.09429682611946688</v>
       </c>
       <c r="T26">
         <v>1.120019078971521</v>
       </c>
       <c r="U26">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V26">
         <v>0.2494</v>
       </c>
       <c r="W26">
-        <v>0.0424089</v>
+        <v>0.04075758</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>6.782435040453243</v>
+        <v>7.057229830305861</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3474,13 +3474,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.0817356860857695</v>
+        <v>0.08129920759072841</v>
       </c>
       <c r="C27">
-        <v>1395.775677049229</v>
+        <v>1416.986782936462</v>
       </c>
       <c r="D27">
-        <v>1818.071338613671</v>
+        <v>1839.282444500904</v>
       </c>
       <c r="E27">
         <v>-515.0869846933269</v>
@@ -3507,37 +3507,37 @@
         <v>174.925</v>
       </c>
       <c r="M27">
-        <v>26.865504878391</v>
+        <v>25.81941442294922</v>
       </c>
       <c r="N27">
-        <v>148.059495121609</v>
+        <v>149.1055855770507</v>
       </c>
       <c r="O27">
-        <v>36.92603808332927</v>
+        <v>37.18693304291645</v>
       </c>
       <c r="P27">
-        <v>111.1334570382797</v>
+        <v>111.9186525341343</v>
       </c>
       <c r="Q27">
-        <v>233.3334570382797</v>
+        <v>234.1186525341343</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.094844614781026</v>
+        <v>0.09481308345430454</v>
       </c>
       <c r="T27">
         <v>1.131941881161768</v>
       </c>
       <c r="U27">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V27">
         <v>0.2494</v>
       </c>
       <c r="W27">
-        <v>0.0424089</v>
+        <v>0.04075758</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>6.511137638835113</v>
+        <v>6.774940637093626</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3556,13 +3556,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.0816039369244642</v>
+        <v>0.08115100813066198</v>
       </c>
       <c r="C28">
-        <v>1383.445879522879</v>
+        <v>1405.677646482418</v>
       </c>
       <c r="D28">
-        <v>1824.761367549899</v>
+        <v>1846.993134509438</v>
       </c>
       <c r="E28">
         <v>-496.0671582307492</v>
@@ -3589,37 +3589,37 @@
         <v>174.925</v>
       </c>
       <c r="M28">
-        <v>27.94012507352664</v>
+        <v>26.85219099986719</v>
       </c>
       <c r="N28">
-        <v>146.9848749264733</v>
+        <v>148.0728090001328</v>
       </c>
       <c r="O28">
-        <v>36.65802780666245</v>
+        <v>36.92935856463311</v>
       </c>
       <c r="P28">
-        <v>110.3268471198109</v>
+        <v>111.1434504354997</v>
       </c>
       <c r="Q28">
-        <v>232.5268471198108</v>
+        <v>233.3434504354996</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.09537516611414082</v>
+        <v>0.09534329369008376</v>
       </c>
       <c r="T28">
         <v>1.144186921249048</v>
       </c>
       <c r="U28">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V28">
         <v>0.2494</v>
       </c>
       <c r="W28">
-        <v>0.0424089</v>
+        <v>0.04075758</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.260709268110685</v>
+        <v>6.514365997205409</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3638,13 +3638,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.08175591456315891</v>
+        <v>0.08100280867059556</v>
       </c>
       <c r="C29">
-        <v>1356.71319337669</v>
+        <v>1394.433432126306</v>
       </c>
       <c r="D29">
-        <v>1817.048507866288</v>
+        <v>1854.768746615904</v>
       </c>
       <c r="E29">
         <v>-477.0473317681715</v>
@@ -3671,45 +3671,45 @@
         <v>174.925</v>
       </c>
       <c r="M29">
-        <v>29.73369470894772</v>
+        <v>27.88496757678517</v>
       </c>
       <c r="N29">
-        <v>145.1913052910522</v>
+        <v>147.0400324232148</v>
       </c>
       <c r="O29">
-        <v>36.21071153958843</v>
+        <v>36.67178408634977</v>
       </c>
       <c r="P29">
-        <v>108.9805937514638</v>
+        <v>110.368248336865</v>
       </c>
       <c r="Q29">
-        <v>231.1805937514638</v>
+        <v>232.568248336865</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.09592025310021768</v>
+        <v>0.09588803023369255</v>
       </c>
       <c r="T29">
         <v>1.156767441886664</v>
       </c>
       <c r="U29">
-        <v>0.05790000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V29">
         <v>0.2494</v>
       </c>
       <c r="W29">
-        <v>0.04345974</v>
+        <v>0.04075758</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y29">
-        <v>5.883056300680992</v>
+        <v>6.273093182494097</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3720,13 +3720,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.08163467380185362</v>
+        <v>0.08106477721052915</v>
       </c>
       <c r="C30">
-        <v>1343.841053527377</v>
+        <v>1372.154339046047</v>
       </c>
       <c r="D30">
-        <v>1823.196194479552</v>
+        <v>1851.509479998222</v>
       </c>
       <c r="E30">
         <v>-458.0275053055938</v>
@@ -3753,37 +3753,37 @@
         <v>174.925</v>
       </c>
       <c r="M30">
-        <v>30.83494266113097</v>
+        <v>29.45029929465531</v>
       </c>
       <c r="N30">
-        <v>144.090057338869</v>
+        <v>145.4747007053446</v>
       </c>
       <c r="O30">
-        <v>35.93606030031393</v>
+        <v>36.28139035591295</v>
       </c>
       <c r="P30">
-        <v>108.153997038555</v>
+        <v>109.1933103494317</v>
       </c>
       <c r="Q30">
-        <v>230.353997038555</v>
+        <v>231.3933103494317</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.09648048139146335</v>
+        <v>0.09644789834795717</v>
       </c>
       <c r="T30">
         <v>1.169697421430881</v>
       </c>
       <c r="U30">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V30">
         <v>0.2494</v>
       </c>
       <c r="W30">
-        <v>0.04345974</v>
+        <v>0.04150818000000001</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.672947147085242</v>
+        <v>5.939667989443681</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3802,13 +3802,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.08151343304054831</v>
+        <v>0.08092408375046273</v>
       </c>
       <c r="C31">
-        <v>1331.01065428611</v>
+        <v>1360.550941633617</v>
       </c>
       <c r="D31">
-        <v>1829.385621700863</v>
+        <v>1858.92590904837</v>
       </c>
       <c r="E31">
         <v>-439.0076788430162</v>
@@ -3835,37 +3835,37 @@
         <v>174.925</v>
       </c>
       <c r="M31">
-        <v>31.93619061331421</v>
+        <v>30.50209569803585</v>
       </c>
       <c r="N31">
-        <v>142.9888093866857</v>
+        <v>144.4229043019641</v>
       </c>
       <c r="O31">
-        <v>35.66140906103943</v>
+        <v>36.01907233290985</v>
       </c>
       <c r="P31">
-        <v>107.3274003256463</v>
+        <v>108.4038319690543</v>
       </c>
       <c r="Q31">
-        <v>229.5274003256463</v>
+        <v>230.6038319690543</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.09705649076133566</v>
+        <v>0.09702353739501793</v>
       </c>
       <c r="T31">
         <v>1.182991625750992</v>
       </c>
       <c r="U31">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V31">
         <v>0.2494</v>
       </c>
       <c r="W31">
-        <v>0.04345974</v>
+        <v>0.04150818000000001</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.477328279944373</v>
+        <v>5.734851851876658</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3884,13 +3884,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.08139219227924302</v>
+        <v>0.08078339029039631</v>
       </c>
       <c r="C32">
-        <v>1318.222422206813</v>
+        <v>1349.007197848564</v>
       </c>
       <c r="D32">
-        <v>1835.617216084144</v>
+        <v>1866.401991725895</v>
       </c>
       <c r="E32">
         <v>-419.9878523804385</v>
@@ -3917,37 +3917,37 @@
         <v>174.925</v>
       </c>
       <c r="M32">
-        <v>33.03743856549745</v>
+        <v>31.55389210141639</v>
       </c>
       <c r="N32">
-        <v>141.8875614345025</v>
+        <v>143.3711078985835</v>
       </c>
       <c r="O32">
-        <v>35.38675782176493</v>
+        <v>35.75675430990674</v>
       </c>
       <c r="P32">
-        <v>106.5008036127376</v>
+        <v>107.6143535886768</v>
       </c>
       <c r="Q32">
-        <v>228.7008036127376</v>
+        <v>229.8143535886768</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.09764895754177576</v>
+        <v>0.09761562327199474</v>
       </c>
       <c r="T32">
         <v>1.196665664480248</v>
       </c>
       <c r="U32">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V32">
         <v>0.2494</v>
       </c>
       <c r="W32">
-        <v>0.04345974</v>
+        <v>0.04150818000000001</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.294750670612896</v>
+        <v>5.543690123480769</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3966,13 +3966,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.08127095151793773</v>
+        <v>0.08064269683032989</v>
       </c>
       <c r="C33">
-        <v>1305.476789675306</v>
+        <v>1337.523830327999</v>
       </c>
       <c r="D33">
-        <v>1841.891410015214</v>
+        <v>1873.938450667908</v>
       </c>
       <c r="E33">
         <v>-400.9680259178608</v>
@@ -3999,37 +3999,37 @@
         <v>174.925</v>
       </c>
       <c r="M33">
-        <v>34.1386865176807</v>
+        <v>32.60568850479694</v>
       </c>
       <c r="N33">
-        <v>140.7863134823193</v>
+        <v>142.319311495203</v>
       </c>
       <c r="O33">
-        <v>35.11210658249043</v>
+        <v>35.49443628690364</v>
       </c>
       <c r="P33">
-        <v>105.6742068998288</v>
+        <v>106.8248752082994</v>
       </c>
       <c r="Q33">
-        <v>227.8742068998288</v>
+        <v>229.0248752082994</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.09825859727237353</v>
+        <v>0.09822487105844913</v>
       </c>
       <c r="T33">
         <v>1.210736052158179</v>
       </c>
       <c r="U33">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V33">
         <v>0.2494</v>
       </c>
       <c r="W33">
-        <v>0.04345974</v>
+        <v>0.04150818000000001</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.123952261883447</v>
+        <v>5.3648614098201</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4048,13 +4048,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.08114971075663244</v>
+        <v>0.08050200337026348</v>
       </c>
       <c r="C34">
-        <v>1292.774195009314</v>
+        <v>1326.101573428275</v>
       </c>
       <c r="D34">
-        <v>1848.2086418118</v>
+        <v>1881.536020230761</v>
       </c>
       <c r="E34">
         <v>-381.9481994552831</v>
@@ -4081,37 +4081,37 @@
         <v>174.925</v>
       </c>
       <c r="M34">
-        <v>35.23993446986395</v>
+        <v>33.65748490817749</v>
       </c>
       <c r="N34">
-        <v>139.685065530136</v>
+        <v>141.2675150918225</v>
       </c>
       <c r="O34">
-        <v>34.83745534321592</v>
+        <v>35.23211826390052</v>
       </c>
       <c r="P34">
-        <v>104.8476101869201</v>
+        <v>106.0353968279219</v>
       </c>
       <c r="Q34">
-        <v>227.0476101869201</v>
+        <v>228.2353968279219</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.098886167583283</v>
+        <v>0.09885203789744629</v>
       </c>
       <c r="T34">
         <v>1.225220274767813</v>
       </c>
       <c r="U34">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V34">
         <v>0.2494</v>
       </c>
       <c r="W34">
-        <v>0.04345974</v>
+        <v>0.04150818000000001</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.963828753699588</v>
+        <v>5.197209490763221</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4130,13 +4130,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.08102846999532715</v>
+        <v>0.08036130991019706</v>
       </c>
       <c r="C35">
-        <v>1280.115082560544</v>
+        <v>1314.741173463527</v>
       </c>
       <c r="D35">
-        <v>1854.569355825608</v>
+        <v>1889.19544672859</v>
       </c>
       <c r="E35">
         <v>-362.9283729927054</v>
@@ -4163,37 +4163,37 @@
         <v>174.925</v>
       </c>
       <c r="M35">
-        <v>36.3411824220472</v>
+        <v>34.70928131155804</v>
       </c>
       <c r="N35">
-        <v>138.5838175779527</v>
+        <v>140.2157186884419</v>
       </c>
       <c r="O35">
-        <v>34.56280410394142</v>
+        <v>34.96980024089741</v>
       </c>
       <c r="P35">
-        <v>104.0210134740113</v>
+        <v>105.2459184475445</v>
       </c>
       <c r="Q35">
-        <v>226.2210134740113</v>
+        <v>227.4459184475445</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.09953247133630917</v>
+        <v>0.09949792613462249</v>
       </c>
       <c r="T35">
         <v>1.240136862231466</v>
       </c>
       <c r="U35">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V35">
         <v>0.2494</v>
       </c>
       <c r="W35">
-        <v>0.04345974</v>
+        <v>0.04150818000000001</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.813409700557177</v>
+        <v>5.039718294073427</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4212,13 +4212,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.08090722923402184</v>
+        <v>0.08022061645013065</v>
       </c>
       <c r="C36">
-        <v>1267.499902818873</v>
+        <v>1303.443388950053</v>
       </c>
       <c r="D36">
-        <v>1860.974002546515</v>
+        <v>1896.917488677695</v>
       </c>
       <c r="E36">
         <v>-343.9085465301276</v>
@@ -4245,37 +4245,37 @@
         <v>174.925</v>
       </c>
       <c r="M36">
-        <v>37.44243037423045</v>
+        <v>35.76107771493859</v>
       </c>
       <c r="N36">
-        <v>137.4825696257695</v>
+        <v>139.1639222850614</v>
       </c>
       <c r="O36">
-        <v>34.28815286466691</v>
+        <v>34.70748221789431</v>
       </c>
       <c r="P36">
-        <v>103.1944167611026</v>
+        <v>104.4564400671671</v>
       </c>
       <c r="Q36">
-        <v>225.3944167611025</v>
+        <v>226.6564400671671</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1001983600515483</v>
+        <v>0.1001633867426222</v>
       </c>
       <c r="T36">
         <v>1.255505467497048</v>
       </c>
       <c r="U36">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V36">
         <v>0.2494</v>
       </c>
       <c r="W36">
-        <v>0.04345974</v>
+        <v>0.04150818000000001</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.671838827011376</v>
+        <v>4.891491285424209</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4294,13 +4294,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.08078598847271656</v>
+        <v>0.08007992299006422</v>
       </c>
       <c r="C37">
-        <v>1254.929112518701</v>
+        <v>1292.208990856727</v>
       </c>
       <c r="D37">
-        <v>1867.42303870892</v>
+        <v>1904.702917046946</v>
       </c>
       <c r="E37">
         <v>-324.8887200675499</v>
@@ -4327,37 +4327,37 @@
         <v>174.925</v>
       </c>
       <c r="M37">
-        <v>38.5436783264137</v>
+        <v>36.81287411831914</v>
       </c>
       <c r="N37">
-        <v>136.3813216735863</v>
+        <v>138.1121258816808</v>
       </c>
       <c r="O37">
-        <v>34.01350162539241</v>
+        <v>34.4451641948912</v>
       </c>
       <c r="P37">
-        <v>102.3678200481938</v>
+        <v>103.6669616867896</v>
       </c>
       <c r="Q37">
-        <v>224.5678200481938</v>
+        <v>225.8669616867896</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1008847376503332</v>
+        <v>0.1008493230616373</v>
       </c>
       <c r="T37">
         <v>1.271346952924649</v>
       </c>
       <c r="U37">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V37">
         <v>0.2494</v>
       </c>
       <c r="W37">
-        <v>0.04345974</v>
+        <v>0.04150818000000001</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.538357717668195</v>
+        <v>4.751734391554944</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4376,13 +4376,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.08136730931141128</v>
+        <v>0.07993922952999781</v>
       </c>
       <c r="C38">
-        <v>1205.38766527353</v>
+        <v>1281.038762861579</v>
       </c>
       <c r="D38">
-        <v>1836.901417926327</v>
+        <v>1912.552515514376</v>
       </c>
       <c r="E38">
         <v>-305.8688936049723</v>
@@ -4409,45 +4409,45 @@
         <v>174.925</v>
       </c>
       <c r="M38">
-        <v>41.42518203549422</v>
+        <v>37.86467052169968</v>
       </c>
       <c r="N38">
-        <v>133.4998179645057</v>
+        <v>137.0603294783003</v>
       </c>
       <c r="O38">
-        <v>33.29485460034773</v>
+        <v>34.18284617188809</v>
       </c>
       <c r="P38">
-        <v>100.204963364158</v>
+        <v>102.8774833064122</v>
       </c>
       <c r="Q38">
-        <v>222.404963364158</v>
+        <v>225.0774833064122</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1015925645490801</v>
+        <v>0.1015566948906216</v>
       </c>
       <c r="T38">
         <v>1.287683484771861</v>
       </c>
       <c r="U38">
-        <v>0.06050000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V38">
         <v>0.2494</v>
       </c>
       <c r="W38">
-        <v>0.0454113</v>
+        <v>0.04150818000000001</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y38">
-        <v>4.222673055488795</v>
+        <v>4.619741769567308</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4458,13 +4458,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.08126558415010597</v>
+        <v>0.08049284106993139</v>
       </c>
       <c r="C39">
-        <v>1191.636583074394</v>
+        <v>1231.499350494132</v>
       </c>
       <c r="D39">
-        <v>1842.170162189769</v>
+        <v>1882.032929609507</v>
       </c>
       <c r="E39">
         <v>-286.8490671423946</v>
@@ -4491,37 +4491,37 @@
         <v>174.925</v>
       </c>
       <c r="M39">
-        <v>42.57588153648017</v>
+        <v>40.67580087286866</v>
       </c>
       <c r="N39">
-        <v>132.3491184635198</v>
+        <v>134.2491991271313</v>
       </c>
       <c r="O39">
-        <v>33.00787014480184</v>
+        <v>33.48175026230655</v>
       </c>
       <c r="P39">
-        <v>99.34124831871793</v>
+        <v>100.7674488648248</v>
       </c>
       <c r="Q39">
-        <v>221.5412483187179</v>
+        <v>222.9674488648247</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1023228621430253</v>
+        <v>0.1022865229681451</v>
       </c>
       <c r="T39">
         <v>1.304538636677715</v>
       </c>
       <c r="U39">
-        <v>0.06050000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V39">
         <v>0.2494</v>
       </c>
       <c r="W39">
-        <v>0.0454113</v>
+        <v>0.04338468</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.108546756691801</v>
+        <v>4.300468491000934</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4540,13 +4540,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.08116385898880069</v>
+        <v>0.08037091260986498</v>
       </c>
       <c r="C40">
-        <v>1177.915812265214</v>
+        <v>1219.11728275928</v>
       </c>
       <c r="D40">
-        <v>1847.469217843166</v>
+        <v>1888.670688337232</v>
       </c>
       <c r="E40">
         <v>-267.829240679817</v>
@@ -4573,37 +4573,37 @@
         <v>174.925</v>
       </c>
       <c r="M40">
-        <v>43.72658103746612</v>
+        <v>41.77514684240565</v>
       </c>
       <c r="N40">
-        <v>131.1984189625338</v>
+        <v>133.1498531575943</v>
       </c>
       <c r="O40">
-        <v>32.72088568925594</v>
+        <v>33.20757337750402</v>
       </c>
       <c r="P40">
-        <v>98.47753327327788</v>
+        <v>99.94227978009027</v>
       </c>
       <c r="Q40">
-        <v>220.6775332732779</v>
+        <v>222.1422797800903</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1030767177238721</v>
+        <v>0.103039893886879</v>
       </c>
       <c r="T40">
         <v>1.321937503161178</v>
       </c>
       <c r="U40">
-        <v>0.06050000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V40">
         <v>0.2494</v>
       </c>
       <c r="W40">
-        <v>0.0454113</v>
+        <v>0.04338468</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.000427105199911</v>
+        <v>4.18729826755354</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4622,13 +4622,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.08185251562749538</v>
+        <v>0.08024898414979856</v>
       </c>
       <c r="C41">
-        <v>1123.606577573894</v>
+        <v>1206.782202285152</v>
       </c>
       <c r="D41">
-        <v>1812.179809614424</v>
+        <v>1895.355434325682</v>
       </c>
       <c r="E41">
         <v>-248.8094142172392</v>
@@ -4655,45 +4655,45 @@
         <v>174.925</v>
       </c>
       <c r="M41">
-        <v>46.8800682649615</v>
+        <v>42.87449281194264</v>
       </c>
       <c r="N41">
-        <v>128.0449317350385</v>
+        <v>132.0505071880573</v>
       </c>
       <c r="O41">
-        <v>31.93440597471859</v>
+        <v>32.9333964927015</v>
       </c>
       <c r="P41">
-        <v>96.11052576031986</v>
+        <v>99.11711069535582</v>
       </c>
       <c r="Q41">
-        <v>218.3105257603198</v>
+        <v>221.3171106953558</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.10385528988114</v>
+        <v>0.103817965491473</v>
       </c>
       <c r="T41">
         <v>1.339906824283442</v>
       </c>
       <c r="U41">
-        <v>0.06320000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V41">
         <v>0.2494</v>
       </c>
       <c r="W41">
-        <v>0.04743792</v>
+        <v>0.04338468</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y41">
-        <v>3.731329890804365</v>
+        <v>4.079931645308578</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4704,13 +4704,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.08177105666619008</v>
+        <v>0.08117789568973215</v>
       </c>
       <c r="C42">
-        <v>1108.690558412823</v>
+        <v>1137.996342515739</v>
       </c>
       <c r="D42">
-        <v>1816.283616915931</v>
+        <v>1845.589401018847</v>
       </c>
       <c r="E42">
         <v>-229.7895877546615</v>
@@ -4737,37 +4737,37 @@
         <v>174.925</v>
       </c>
       <c r="M42">
-        <v>48.08212129739642</v>
+        <v>46.63661448624051</v>
       </c>
       <c r="N42">
-        <v>126.8428787026035</v>
+        <v>128.2883855137594</v>
       </c>
       <c r="O42">
-        <v>31.63461394842933</v>
+        <v>31.99512334713161</v>
       </c>
       <c r="P42">
-        <v>95.20826475417422</v>
+        <v>96.29326216662783</v>
       </c>
       <c r="Q42">
-        <v>217.4082647541742</v>
+        <v>218.4932621666278</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1046598144436501</v>
+        <v>0.1046219728162202</v>
       </c>
       <c r="T42">
         <v>1.358475122776449</v>
       </c>
       <c r="U42">
-        <v>0.06320000000000001</v>
+        <v>0.06130000000000001</v>
       </c>
       <c r="V42">
         <v>0.2494</v>
       </c>
       <c r="W42">
-        <v>0.04743792</v>
+        <v>0.04601178</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.638046643534255</v>
+        <v>3.750808285014109</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4786,13 +4786,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.08168959770488479</v>
+        <v>0.08108223822966572</v>
       </c>
       <c r="C43">
-        <v>1093.79316815269</v>
+        <v>1123.980291416782</v>
       </c>
       <c r="D43">
-        <v>1820.406053118375</v>
+        <v>1850.593176382467</v>
       </c>
       <c r="E43">
         <v>-210.7697612920838</v>
@@ -4819,37 +4819,37 @@
         <v>174.925</v>
       </c>
       <c r="M43">
-        <v>49.28417432983133</v>
+        <v>47.80252984839652</v>
       </c>
       <c r="N43">
-        <v>125.6408256701686</v>
+        <v>127.1224701516034</v>
       </c>
       <c r="O43">
-        <v>31.33482192214005</v>
+        <v>31.7043440558099</v>
       </c>
       <c r="P43">
-        <v>94.30600374802857</v>
+        <v>95.41812609579354</v>
       </c>
       <c r="Q43">
-        <v>216.5060037480285</v>
+        <v>217.6181260957935</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1054916110252285</v>
+        <v>0.1054532346265521</v>
       </c>
       <c r="T43">
         <v>1.377672855116676</v>
       </c>
       <c r="U43">
-        <v>0.06320000000000001</v>
+        <v>0.06130000000000001</v>
       </c>
       <c r="V43">
         <v>0.2494</v>
       </c>
       <c r="W43">
-        <v>0.04743792</v>
+        <v>0.04601178</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.549313798570005</v>
+        <v>3.659325156111326</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4868,13 +4868,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.0830898231435795</v>
+        <v>0.0809865807695993</v>
       </c>
       <c r="C44">
-        <v>1006.417456640304</v>
+        <v>1109.991446623839</v>
       </c>
       <c r="D44">
-        <v>1752.050168068567</v>
+        <v>1855.624158052102</v>
       </c>
       <c r="E44">
         <v>-191.7499348295062</v>
@@ -4901,45 +4901,45 @@
         <v>174.925</v>
       </c>
       <c r="M44">
-        <v>54.24074110597908</v>
+        <v>48.96844521055253</v>
       </c>
       <c r="N44">
-        <v>120.6842588940209</v>
+        <v>125.9565547894474</v>
       </c>
       <c r="O44">
-        <v>30.09865416816881</v>
+        <v>31.41356476448819</v>
       </c>
       <c r="P44">
-        <v>90.58560472585206</v>
+        <v>94.54299002495924</v>
       </c>
       <c r="Q44">
-        <v>212.7856047258521</v>
+        <v>216.7429900249592</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1063520902475509</v>
+        <v>0.1063131606372402</v>
       </c>
       <c r="T44">
         <v>1.397532578227256</v>
       </c>
       <c r="U44">
-        <v>0.06790000000000002</v>
+        <v>0.06130000000000001</v>
       </c>
       <c r="V44">
         <v>0.2494</v>
       </c>
       <c r="W44">
-        <v>0.05096574000000001</v>
+        <v>0.04601178</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y44">
-        <v>3.224974372275264</v>
+        <v>3.572198366680105</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4950,13 +4950,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.08304364238227421</v>
+        <v>0.08179464570953289</v>
       </c>
       <c r="C45">
-        <v>989.5701086312566</v>
+        <v>1049.313623693788</v>
       </c>
       <c r="D45">
-        <v>1754.222646522097</v>
+        <v>1813.966161584628</v>
       </c>
       <c r="E45">
         <v>-172.7301083669284</v>
@@ -4983,37 +4983,37 @@
         <v>174.925</v>
       </c>
       <c r="M45">
-        <v>55.5321873227881</v>
+        <v>52.4243476788029</v>
       </c>
       <c r="N45">
-        <v>119.3928126772119</v>
+        <v>122.5006523211971</v>
       </c>
       <c r="O45">
-        <v>29.77656748169664</v>
+        <v>30.55166268890655</v>
       </c>
       <c r="P45">
-        <v>89.61624519551521</v>
+        <v>91.94898963229051</v>
       </c>
       <c r="Q45">
-        <v>211.8162451955152</v>
+        <v>214.1489896322905</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1072427617232881</v>
+        <v>0.1072032594904086</v>
       </c>
       <c r="T45">
         <v>1.418089133727681</v>
       </c>
       <c r="U45">
-        <v>0.06790000000000002</v>
+        <v>0.0641</v>
       </c>
       <c r="V45">
         <v>0.2494</v>
       </c>
       <c r="W45">
-        <v>0.05096574000000001</v>
+        <v>0.04811346</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.149974968268862</v>
+        <v>3.336712953907266</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5032,13 +5032,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.08299746162096891</v>
+        <v>0.08172000504946647</v>
       </c>
       <c r="C46">
-        <v>972.7281548993742</v>
+        <v>1034.063162838269</v>
       </c>
       <c r="D46">
-        <v>1756.400519252793</v>
+        <v>1817.735527191687</v>
       </c>
       <c r="E46">
         <v>-153.7102819043507</v>
@@ -5065,37 +5065,37 @@
         <v>174.925</v>
       </c>
       <c r="M46">
-        <v>56.82363353959713</v>
+        <v>53.64351855505414</v>
       </c>
       <c r="N46">
-        <v>118.1013664604028</v>
+        <v>121.2814814449458</v>
       </c>
       <c r="O46">
-        <v>29.45448079522447</v>
+        <v>30.24760147236949</v>
       </c>
       <c r="P46">
-        <v>88.64688566517836</v>
+        <v>91.03387997257633</v>
       </c>
       <c r="Q46">
-        <v>210.8468856651783</v>
+        <v>213.2338799725763</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1081652428945873</v>
+        <v>0.108125147588333</v>
       </c>
       <c r="T46">
         <v>1.439379851924549</v>
       </c>
       <c r="U46">
-        <v>0.06790000000000002</v>
+        <v>0.0641</v>
       </c>
       <c r="V46">
         <v>0.2494</v>
       </c>
       <c r="W46">
-        <v>0.05096574000000001</v>
+        <v>0.04811346</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.078384628080933</v>
+        <v>3.260878568591192</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5114,13 +5114,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.08295128085966362</v>
+        <v>0.08164536438940005</v>
       </c>
       <c r="C47">
-        <v>955.8916155606645</v>
+        <v>1018.82839985285</v>
       </c>
       <c r="D47">
-        <v>1758.583806376661</v>
+        <v>1821.520590668846</v>
       </c>
       <c r="E47">
         <v>-134.690455441773</v>
@@ -5147,37 +5147,37 @@
         <v>174.925</v>
       </c>
       <c r="M47">
-        <v>58.11507975640616</v>
+        <v>54.86268943130536</v>
       </c>
       <c r="N47">
-        <v>116.8099202435938</v>
+        <v>120.0623105686946</v>
       </c>
       <c r="O47">
-        <v>29.13239410875229</v>
+        <v>29.94354025583243</v>
       </c>
       <c r="P47">
-        <v>87.6775261348415</v>
+        <v>90.11877031286215</v>
       </c>
       <c r="Q47">
-        <v>209.8775261348415</v>
+        <v>212.3187703128621</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.109121268835752</v>
+        <v>0.1090805588898183</v>
       </c>
       <c r="T47">
         <v>1.461444778055849</v>
       </c>
       <c r="U47">
-        <v>0.06790000000000002</v>
+        <v>0.0641</v>
       </c>
       <c r="V47">
         <v>0.2494</v>
       </c>
       <c r="W47">
-        <v>0.05096574000000001</v>
+        <v>0.04811346</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.009976080790246</v>
+        <v>3.188414600400276</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5196,13 +5196,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.08611616689835833</v>
+        <v>0.08157072372933363</v>
       </c>
       <c r="C48">
-        <v>798.8200405102833</v>
+        <v>1003.609433004991</v>
       </c>
       <c r="D48">
-        <v>1620.532057788857</v>
+        <v>1825.321450283565</v>
       </c>
       <c r="E48">
         <v>-115.6706289791954</v>
@@ -5229,45 +5229,45 @@
         <v>174.925</v>
       </c>
       <c r="M48">
-        <v>67.5432077339059</v>
+        <v>56.08186030755659</v>
       </c>
       <c r="N48">
-        <v>107.3817922660941</v>
+        <v>118.8431396924434</v>
       </c>
       <c r="O48">
-        <v>26.78101899116386</v>
+        <v>29.63947903929538</v>
       </c>
       <c r="P48">
-        <v>80.60077327493019</v>
+        <v>89.20366065314799</v>
       </c>
       <c r="Q48">
-        <v>202.8007732749302</v>
+        <v>211.403660653148</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.110112703145108</v>
+        <v>0.1100713557950623</v>
       </c>
       <c r="T48">
         <v>1.484326923673494</v>
       </c>
       <c r="U48">
-        <v>0.0772</v>
+        <v>0.0641</v>
       </c>
       <c r="V48">
         <v>0.2494</v>
       </c>
       <c r="W48">
-        <v>0.05794632</v>
+        <v>0.04811346</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y48">
-        <v>2.589823697582395</v>
+        <v>3.11910123952201</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5278,13 +5278,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.08613979193705303</v>
+        <v>0.08149608306926721</v>
       </c>
       <c r="C49">
-        <v>778.8511478593871</v>
+        <v>988.4063613840631</v>
       </c>
       <c r="D49">
-        <v>1619.582991600539</v>
+        <v>1829.138205125215</v>
       </c>
       <c r="E49">
         <v>-96.65080251661766</v>
@@ -5311,45 +5311,45 @@
         <v>174.925</v>
       </c>
       <c r="M49">
-        <v>69.01153833681691</v>
+        <v>57.30103118380782</v>
       </c>
       <c r="N49">
-        <v>105.913461663183</v>
+        <v>117.6239688161921</v>
       </c>
       <c r="O49">
-        <v>26.41481733879785</v>
+        <v>29.33541782275832</v>
       </c>
       <c r="P49">
-        <v>79.4986443243852</v>
+        <v>88.28855099343382</v>
       </c>
       <c r="Q49">
-        <v>201.6986443243852</v>
+        <v>210.4885509934338</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1111415500699114</v>
+        <v>0.1110995412627683</v>
       </c>
       <c r="T49">
         <v>1.508072546484257</v>
       </c>
       <c r="U49">
-        <v>0.0772</v>
+        <v>0.0641</v>
       </c>
       <c r="V49">
         <v>0.2494</v>
       </c>
       <c r="W49">
-        <v>0.05794632</v>
+        <v>0.04811346</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y49">
-        <v>2.534721065718939</v>
+        <v>3.052737383361967</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5360,13 +5360,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.08785677057574773</v>
+        <v>0.0842316888092008</v>
       </c>
       <c r="C50">
-        <v>693.7114229333038</v>
+        <v>839.1866626776612</v>
       </c>
       <c r="D50">
-        <v>1553.463093137033</v>
+        <v>1698.93833288139</v>
       </c>
       <c r="E50">
         <v>-77.63097605404005</v>
@@ -5393,45 +5393,45 @@
         <v>174.925</v>
       </c>
       <c r="M50">
-        <v>74.77074178968543</v>
+        <v>65.64122508764814</v>
       </c>
       <c r="N50">
-        <v>100.1542582103145</v>
+        <v>109.2837749123518</v>
       </c>
       <c r="O50">
-        <v>24.97847199765244</v>
+        <v>27.25537346314054</v>
       </c>
       <c r="P50">
-        <v>75.17578621266208</v>
+        <v>82.02840144921127</v>
       </c>
       <c r="Q50">
-        <v>197.3757862126621</v>
+        <v>204.2284014492113</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1122099680302841</v>
+        <v>0.1121672723253861</v>
       </c>
       <c r="T50">
         <v>1.532731462480049</v>
       </c>
       <c r="U50">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V50">
         <v>0.2494</v>
       </c>
       <c r="W50">
-        <v>0.06147414</v>
+        <v>0.05396814</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y50">
-        <v>2.339484614075753</v>
+        <v>2.664864949830377</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5442,13 +5442,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.08791567381444243</v>
+        <v>0.08421559494913439</v>
       </c>
       <c r="C51">
-        <v>672.5189134980727</v>
+        <v>820.87859079879</v>
       </c>
       <c r="D51">
-        <v>1551.29041016438</v>
+        <v>1699.650087465097</v>
       </c>
       <c r="E51">
         <v>-58.61114959146232</v>
@@ -5475,45 +5475,45 @@
         <v>174.925</v>
       </c>
       <c r="M51">
-        <v>76.32846557697054</v>
+        <v>67.00875061030747</v>
       </c>
       <c r="N51">
-        <v>98.59653442302941</v>
+        <v>107.9162493896925</v>
       </c>
       <c r="O51">
-        <v>24.58997568510354</v>
+        <v>26.9143125977893</v>
       </c>
       <c r="P51">
-        <v>74.00655873792587</v>
+        <v>81.00193679190318</v>
       </c>
       <c r="Q51">
-        <v>196.2065587379259</v>
+        <v>203.2019367919032</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1133202847342009</v>
+        <v>0.1132768751943811</v>
       </c>
       <c r="T51">
         <v>1.558357394789403</v>
       </c>
       <c r="U51">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V51">
         <v>0.2494</v>
       </c>
       <c r="W51">
-        <v>0.06147414</v>
+        <v>0.05396814</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y51">
-        <v>2.291740030115023</v>
+        <v>2.610479950854247</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5524,13 +5524,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.08797457705313713</v>
+        <v>0.08419950108906796</v>
       </c>
       <c r="C52">
-        <v>651.3324730301053</v>
+        <v>802.5711155359352</v>
       </c>
       <c r="D52">
-        <v>1549.12379615899</v>
+        <v>1700.36243866482</v>
       </c>
       <c r="E52">
         <v>-39.5913231288846</v>
@@ -5557,45 +5557,45 @@
         <v>174.925</v>
       </c>
       <c r="M52">
-        <v>77.88618936425566</v>
+        <v>68.37627613296681</v>
       </c>
       <c r="N52">
-        <v>97.0388106357443</v>
+        <v>106.5487238670331</v>
       </c>
       <c r="O52">
-        <v>24.20147937255463</v>
+        <v>26.57325173243807</v>
       </c>
       <c r="P52">
-        <v>72.83733126318967</v>
+        <v>79.97547213459508</v>
       </c>
       <c r="Q52">
-        <v>195.0373312631897</v>
+        <v>202.1754721345951</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1144750141062743</v>
+        <v>0.1144308621781359</v>
       </c>
       <c r="T52">
         <v>1.58500836439113</v>
       </c>
       <c r="U52">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V52">
         <v>0.2494</v>
       </c>
       <c r="W52">
-        <v>0.06147414</v>
+        <v>0.05396814</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y52">
-        <v>2.245905229512722</v>
+        <v>2.558270351837162</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5606,13 +5606,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.08803348029183185</v>
+        <v>0.08418340722900154</v>
       </c>
       <c r="C53">
-        <v>630.1520761361472</v>
+        <v>784.2642376395646</v>
       </c>
       <c r="D53">
-        <v>1546.96322572761</v>
+        <v>1701.075387231027</v>
       </c>
       <c r="E53">
         <v>-20.57149666630687</v>
@@ -5639,45 +5639,45 @@
         <v>174.925</v>
       </c>
       <c r="M53">
-        <v>79.44391315154077</v>
+        <v>69.74380165562616</v>
       </c>
       <c r="N53">
-        <v>95.48108684845919</v>
+        <v>105.1811983443738</v>
       </c>
       <c r="O53">
-        <v>23.81298306000572</v>
+        <v>26.23219086708682</v>
       </c>
       <c r="P53">
-        <v>71.66810378845346</v>
+        <v>78.94900747728697</v>
       </c>
       <c r="Q53">
-        <v>193.8681037884535</v>
+        <v>201.1490074772869</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1156768752894528</v>
+        <v>0.1156319506714317</v>
       </c>
       <c r="T53">
         <v>1.612747128670479</v>
       </c>
       <c r="U53">
-        <v>0.0819</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V53">
         <v>0.2494</v>
       </c>
       <c r="W53">
-        <v>0.06147414</v>
+        <v>0.05396814</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y53">
-        <v>2.201867872071297</v>
+        <v>2.508108188075649</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.08809238353052656</v>
+        <v>0.08568953016893513</v>
       </c>
       <c r="C54">
-        <v>608.9776975644124</v>
+        <v>701.0163129162484</v>
       </c>
       <c r="D54">
-        <v>1544.808673618453</v>
+        <v>1636.847288970288</v>
       </c>
       <c r="E54">
         <v>-1.551670203729145</v>
@@ -5721,37 +5721,37 @@
         <v>174.925</v>
       </c>
       <c r="M54">
-        <v>81.00163693882588</v>
+        <v>74.96854798489625</v>
       </c>
       <c r="N54">
-        <v>93.92336306117407</v>
+        <v>99.95645201510371</v>
       </c>
       <c r="O54">
-        <v>23.42448674745681</v>
+        <v>24.92913913256687</v>
       </c>
       <c r="P54">
-        <v>70.49887631371726</v>
+        <v>75.02731288253685</v>
       </c>
       <c r="Q54">
-        <v>192.6988763137172</v>
+        <v>197.2273128825368</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1169288140219303</v>
+        <v>0.1168830845186148</v>
       </c>
       <c r="T54">
         <v>1.6416416747948</v>
       </c>
       <c r="U54">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V54">
         <v>0.2494</v>
       </c>
       <c r="W54">
-        <v>0.06147414</v>
+        <v>0.05689548</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.159524259146848</v>
+        <v>2.333311831452861</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5770,13 +5770,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.08815128676922127</v>
+        <v>0.0857027097088687</v>
       </c>
       <c r="C55">
-        <v>587.8093122035979</v>
+        <v>681.45584912935</v>
       </c>
       <c r="D55">
-        <v>1542.660114720216</v>
+        <v>1636.306651645968</v>
       </c>
       <c r="E55">
         <v>17.46815625884858</v>
@@ -5803,37 +5803,37 @@
         <v>174.925</v>
       </c>
       <c r="M55">
-        <v>82.55936072611101</v>
+        <v>76.41025083075964</v>
       </c>
       <c r="N55">
-        <v>92.36563927388895</v>
+        <v>98.51474916924032</v>
       </c>
       <c r="O55">
-        <v>23.03599043490791</v>
+        <v>24.56957844280853</v>
       </c>
       <c r="P55">
-        <v>69.32964883898104</v>
+        <v>73.94517072643178</v>
       </c>
       <c r="Q55">
-        <v>191.529648838981</v>
+        <v>196.1451707264318</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.118234026743024</v>
+        <v>0.118187458103976</v>
       </c>
       <c r="T55">
         <v>1.671765776073348</v>
       </c>
       <c r="U55">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V55">
         <v>0.2494</v>
       </c>
       <c r="W55">
-        <v>0.06147414</v>
+        <v>0.05689548</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.118778518408228</v>
+        <v>2.289287079916015</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5852,13 +5852,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.08821019000791597</v>
+        <v>0.0857158892488023</v>
       </c>
       <c r="C56">
-        <v>566.6468950819071</v>
+        <v>661.8957423607376</v>
       </c>
       <c r="D56">
-        <v>1540.517524061103</v>
+        <v>1635.766371339933</v>
       </c>
       <c r="E56">
         <v>36.48798272142631</v>
@@ -5885,37 +5885,37 @@
         <v>174.925</v>
       </c>
       <c r="M56">
-        <v>84.11708451339612</v>
+        <v>77.85195367662303</v>
       </c>
       <c r="N56">
-        <v>90.80791548660383</v>
+        <v>97.07304632337693</v>
       </c>
       <c r="O56">
-        <v>22.647494122359</v>
+        <v>24.21001775305021</v>
       </c>
       <c r="P56">
-        <v>68.16042136424484</v>
+        <v>72.86302857032672</v>
       </c>
       <c r="Q56">
-        <v>190.3604213642448</v>
+        <v>195.0630285703267</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1195959878432956</v>
+        <v>0.1195485435843528</v>
       </c>
       <c r="T56">
         <v>1.703199620885746</v>
       </c>
       <c r="U56">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V56">
         <v>0.2494</v>
       </c>
       <c r="W56">
-        <v>0.06147414</v>
+        <v>0.05689548</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.079541879178446</v>
+        <v>2.246892874732385</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5934,13 +5934,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.08826909324661067</v>
+        <v>0.08572906878873587</v>
       </c>
       <c r="C57">
-        <v>545.4904213660855</v>
+        <v>642.3359922568868</v>
       </c>
       <c r="D57">
-        <v>1538.380876807859</v>
+        <v>1635.22644769866</v>
       </c>
       <c r="E57">
         <v>55.50780918400392</v>
@@ -5967,37 +5967,37 @@
         <v>174.925</v>
       </c>
       <c r="M57">
-        <v>85.67480830068122</v>
+        <v>79.29365652248642</v>
       </c>
       <c r="N57">
-        <v>89.25019169931873</v>
+        <v>95.63134347751354</v>
       </c>
       <c r="O57">
-        <v>22.25899780981009</v>
+        <v>23.85045706329188</v>
       </c>
       <c r="P57">
-        <v>66.99119388950864</v>
+        <v>71.78088641422167</v>
       </c>
       <c r="Q57">
-        <v>189.1911938895086</v>
+        <v>193.9808864142217</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1210184805480237</v>
+        <v>0.1209701217527464</v>
       </c>
       <c r="T57">
         <v>1.736030525467584</v>
       </c>
       <c r="U57">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V57">
         <v>0.2494</v>
       </c>
       <c r="W57">
-        <v>0.06147414</v>
+        <v>0.05689548</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.041732026829748</v>
+        <v>2.206040277009977</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6016,13 +6016,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08832799648530537</v>
+        <v>0.08574224832866946</v>
       </c>
       <c r="C58">
-        <v>524.3398663604573</v>
+        <v>622.7765984647344</v>
       </c>
       <c r="D58">
-        <v>1536.250148264808</v>
+        <v>1634.686880369085</v>
       </c>
       <c r="E58">
         <v>74.52763564658176</v>
@@ -6049,37 +6049,37 @@
         <v>174.925</v>
       </c>
       <c r="M58">
-        <v>87.23253208796635</v>
+        <v>80.73535936834982</v>
       </c>
       <c r="N58">
-        <v>87.69246791203361</v>
+        <v>94.18964063165014</v>
       </c>
       <c r="O58">
-        <v>21.87050149726118</v>
+        <v>23.49089637353354</v>
       </c>
       <c r="P58">
-        <v>65.82196641477242</v>
+        <v>70.69874425811659</v>
       </c>
       <c r="Q58">
-        <v>188.0219664147724</v>
+        <v>192.8987442581166</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1225056320120577</v>
+        <v>0.1224563171106124</v>
       </c>
       <c r="T58">
         <v>1.770353743894051</v>
       </c>
       <c r="U58">
-        <v>0.0819</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V58">
         <v>0.2494</v>
       </c>
       <c r="W58">
-        <v>0.06147414</v>
+        <v>0.05689548</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.005272526350645</v>
+        <v>2.166646700634799</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6098,13 +6098,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09536072432400008</v>
+        <v>0.08575542786860305</v>
       </c>
       <c r="C59">
-        <v>287.3242512514075</v>
+        <v>603.2175606316871</v>
       </c>
       <c r="D59">
-        <v>1318.254359618336</v>
+        <v>1634.147668998616</v>
       </c>
       <c r="E59">
         <v>93.54746210915937</v>
@@ -6131,45 +6131,45 @@
         <v>174.925</v>
       </c>
       <c r="M59">
-        <v>106.4615766416324</v>
+        <v>82.17706221421319</v>
       </c>
       <c r="N59">
-        <v>68.46342335836755</v>
+        <v>92.74793778578676</v>
       </c>
       <c r="O59">
-        <v>17.07477778557687</v>
+        <v>23.13133568377522</v>
       </c>
       <c r="P59">
-        <v>51.38864557279068</v>
+        <v>69.61660210201154</v>
       </c>
       <c r="Q59">
-        <v>173.5886455727907</v>
+        <v>191.8166021020115</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1240619533116281</v>
+        <v>0.1240116378339606</v>
       </c>
       <c r="T59">
         <v>1.80627339108454</v>
       </c>
       <c r="U59">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V59">
         <v>0.2494</v>
       </c>
       <c r="W59">
-        <v>0.07370892</v>
+        <v>0.05689548</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y59">
-        <v>1.643081058143887</v>
+        <v>2.128635355009628</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6180,13 +6180,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.09554197536269479</v>
+        <v>0.08576860740853662</v>
       </c>
       <c r="C60">
-        <v>263.5009369859742</v>
+        <v>583.6588784056155</v>
       </c>
       <c r="D60">
-        <v>1313.45087181548</v>
+        <v>1633.608813235122</v>
       </c>
       <c r="E60">
         <v>112.567288571737</v>
@@ -6213,45 +6213,45 @@
         <v>174.925</v>
       </c>
       <c r="M60">
-        <v>108.3293236002575</v>
+        <v>83.61876506007658</v>
       </c>
       <c r="N60">
-        <v>66.59567639974243</v>
+        <v>91.30623493992337</v>
       </c>
       <c r="O60">
-        <v>16.60896169409576</v>
+        <v>22.77177499401689</v>
       </c>
       <c r="P60">
-        <v>49.98671470564667</v>
+        <v>68.53445994590648</v>
       </c>
       <c r="Q60">
-        <v>172.1867147056467</v>
+        <v>190.7344599459065</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1256923851492733</v>
+        <v>0.1256410214488967</v>
       </c>
       <c r="T60">
         <v>1.843903497665051</v>
       </c>
       <c r="U60">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V60">
         <v>0.2494</v>
       </c>
       <c r="W60">
-        <v>0.07370892</v>
+        <v>0.05689548</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y60">
-        <v>1.614752074382786</v>
+        <v>2.091934745440496</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6262,13 +6262,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.09572322640138949</v>
+        <v>0.08578178694847019</v>
       </c>
       <c r="C61">
-        <v>239.7125017624776</v>
+        <v>564.1005514348535</v>
       </c>
       <c r="D61">
-        <v>1308.682263054561</v>
+        <v>1633.070312726937</v>
       </c>
       <c r="E61">
         <v>131.5871150343146</v>
@@ -6295,45 +6295,45 @@
         <v>174.925</v>
       </c>
       <c r="M61">
-        <v>110.1970705588826</v>
+        <v>85.06046790593996</v>
       </c>
       <c r="N61">
-        <v>64.72792944111731</v>
+        <v>89.86453209406</v>
       </c>
       <c r="O61">
-        <v>16.14314560261466</v>
+        <v>22.41221430425857</v>
       </c>
       <c r="P61">
-        <v>48.58478383850265</v>
+        <v>67.45231778980143</v>
       </c>
       <c r="Q61">
-        <v>170.7847838385026</v>
+        <v>189.6523177898014</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1274023502472914</v>
+        <v>0.1273498871913907</v>
       </c>
       <c r="T61">
         <v>1.88336921920071</v>
       </c>
       <c r="U61">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V61">
         <v>0.2494</v>
       </c>
       <c r="W61">
-        <v>0.07370892</v>
+        <v>0.05689548</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y61">
-        <v>1.587383395155959</v>
+        <v>2.056478224331336</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6344,13 +6344,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.09590447744008419</v>
+        <v>0.08579496648840378</v>
       </c>
       <c r="C62">
-        <v>215.9585670601</v>
+        <v>544.5425793681991</v>
       </c>
       <c r="D62">
-        <v>1303.948154814761</v>
+        <v>1632.532167122861</v>
       </c>
       <c r="E62">
         <v>150.6069414968922</v>
@@ -6377,45 +6377,45 @@
         <v>174.925</v>
       </c>
       <c r="M62">
-        <v>112.0648175175078</v>
+        <v>86.50217075180335</v>
       </c>
       <c r="N62">
-        <v>62.86018248249219</v>
+        <v>88.42282924819661</v>
       </c>
       <c r="O62">
-        <v>15.67732951113355</v>
+        <v>22.05265361450023</v>
       </c>
       <c r="P62">
-        <v>47.18285297135864</v>
+        <v>66.37017563369638</v>
       </c>
       <c r="Q62">
-        <v>169.3828529713586</v>
+        <v>188.5701756336964</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1291978136002105</v>
+        <v>0.1291441962210094</v>
       </c>
       <c r="T62">
         <v>1.924808226813151</v>
       </c>
       <c r="U62">
-        <v>0.09820000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V62">
         <v>0.2494</v>
       </c>
       <c r="W62">
-        <v>0.07370892</v>
+        <v>0.05689548</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y62">
-        <v>1.560927005236694</v>
+        <v>2.022203587259146</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6426,13 +6426,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.0960857284787789</v>
+        <v>0.09230984322833737</v>
       </c>
       <c r="C63">
-        <v>192.238759815421</v>
+        <v>296.8454428023269</v>
       </c>
       <c r="D63">
-        <v>1299.24817403266</v>
+        <v>1403.854857019566</v>
       </c>
       <c r="E63">
         <v>169.62676795947</v>
@@ -6459,37 +6459,37 @@
         <v>174.925</v>
       </c>
       <c r="M63">
-        <v>113.9325644761329</v>
+        <v>104.4188472795516</v>
       </c>
       <c r="N63">
-        <v>60.99243552386704</v>
+        <v>70.5061527204484</v>
       </c>
       <c r="O63">
-        <v>15.21151341965244</v>
+        <v>17.58423448847983</v>
       </c>
       <c r="P63">
-        <v>45.7809221042146</v>
+        <v>52.92191823196856</v>
       </c>
       <c r="Q63">
-        <v>167.9809221042146</v>
+        <v>175.1219182319686</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.131085351996869</v>
+        <v>0.1310305210983009</v>
       </c>
       <c r="T63">
         <v>1.968372311739052</v>
       </c>
       <c r="U63">
-        <v>0.09820000000000001</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V63">
         <v>0.2494</v>
       </c>
       <c r="W63">
-        <v>0.07370892</v>
+        <v>0.067554</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>1.535338037937731</v>
+        <v>1.675224392505391</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6508,13 +6508,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.09626697951747362</v>
+        <v>0.09242960796827096</v>
       </c>
       <c r="C64">
-        <v>168.5527123244162</v>
+        <v>274.2199177464893</v>
       </c>
       <c r="D64">
-        <v>1294.581953004233</v>
+        <v>1400.249158426306</v>
       </c>
       <c r="E64">
         <v>188.6465944220477</v>
@@ -6541,37 +6541,37 @@
         <v>174.925</v>
       </c>
       <c r="M64">
-        <v>115.800311434758</v>
+        <v>106.1306316611835</v>
       </c>
       <c r="N64">
-        <v>59.12468856524193</v>
+        <v>68.79436833881641</v>
       </c>
       <c r="O64">
-        <v>14.74569732817134</v>
+        <v>17.15731546370082</v>
       </c>
       <c r="P64">
-        <v>44.37899123707059</v>
+        <v>51.6370528751156</v>
       </c>
       <c r="Q64">
-        <v>166.5789912370706</v>
+        <v>173.8370528751156</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1330722345196674</v>
+        <v>0.133016126232292</v>
       </c>
       <c r="T64">
         <v>2.01422924324</v>
       </c>
       <c r="U64">
-        <v>0.09820000000000001</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V64">
         <v>0.2494</v>
       </c>
       <c r="W64">
-        <v>0.07370892</v>
+        <v>0.067554</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>1.5105745211968</v>
+        <v>1.648204644239175</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6590,13 +6590,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1308060456450808</v>
+        <v>0.09254937270820454</v>
       </c>
       <c r="C65">
-        <v>-376.4726628388922</v>
+        <v>251.6128671868551</v>
       </c>
       <c r="D65">
-        <v>768.5764043035025</v>
+        <v>1396.66193432925</v>
       </c>
       <c r="E65">
         <v>207.6664208846255</v>
@@ -6623,45 +6623,45 @@
         <v>174.925</v>
       </c>
       <c r="M65">
-        <v>196.0335473844958</v>
+        <v>107.8424160428155</v>
       </c>
       <c r="N65">
-        <v>-21.10854738449586</v>
+        <v>67.08258395718441</v>
       </c>
       <c r="O65">
-        <v>-5.264471717693269</v>
+        <v>16.73039643892179</v>
       </c>
       <c r="P65">
-        <v>-15.8440756668026</v>
+        <v>50.35218751826262</v>
       </c>
       <c r="Q65">
-        <v>106.3559243331974</v>
+        <v>172.5521875182626</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1369603203803464</v>
+        <v>0.1351090613735258</v>
       </c>
       <c r="T65">
-        <v>2.103965644329199</v>
+        <v>2.062564927795052</v>
       </c>
       <c r="U65">
-        <v>0.1636</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V65">
-        <v>0.2225450469170583</v>
+        <v>0.2494</v>
       </c>
       <c r="W65">
-        <v>0.1271916303243693</v>
+        <v>0.067554</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y65">
-        <v>0.8923217598919738</v>
+        <v>1.622042665759188</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6672,13 +6672,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.1319840456450808</v>
+        <v>0.09266913744813812</v>
       </c>
       <c r="C66">
-        <v>-405.9977167770749</v>
+        <v>229.0241494997449</v>
       </c>
       <c r="D66">
-        <v>758.0711768278975</v>
+        <v>1393.093043104717</v>
       </c>
       <c r="E66">
         <v>226.6862473472031</v>
@@ -6705,45 +6705,45 @@
         <v>174.925</v>
       </c>
       <c r="M66">
-        <v>199.1451909937735</v>
+        <v>109.5542004244475</v>
       </c>
       <c r="N66">
-        <v>-24.22019099377357</v>
+        <v>65.37079957555243</v>
       </c>
       <c r="O66">
-        <v>-6.040515633847129</v>
+        <v>16.30347741414278</v>
       </c>
       <c r="P66">
-        <v>-18.17967535992644</v>
+        <v>49.06732216140965</v>
       </c>
       <c r="Q66">
-        <v>104.0203246400735</v>
+        <v>171.2673221614097</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1394925515020226</v>
+        <v>0.1373182706892725</v>
       </c>
       <c r="T66">
-        <v>2.162409134449454</v>
+        <v>2.113585928158719</v>
       </c>
       <c r="U66">
-        <v>0.1636</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V66">
-        <v>0.2190677805589793</v>
+        <v>0.2494</v>
       </c>
       <c r="W66">
-        <v>0.127760511100551</v>
+        <v>0.067554</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y66">
-        <v>0.8783792323936618</v>
+        <v>1.596698249106701</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6754,13 +6754,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1331620456450808</v>
+        <v>0.0927889021880717</v>
       </c>
       <c r="C67">
-        <v>-435.2394632932562</v>
+        <v>206.4536245053534</v>
       </c>
       <c r="D67">
-        <v>747.849256774294</v>
+        <v>1389.542344572904</v>
       </c>
       <c r="E67">
         <v>245.7060738097809</v>
@@ -6787,45 +6787,45 @@
         <v>174.925</v>
       </c>
       <c r="M67">
-        <v>202.2568346030513</v>
+        <v>111.2659848060795</v>
       </c>
       <c r="N67">
-        <v>-27.33183460305131</v>
+        <v>63.65901519392042</v>
       </c>
       <c r="O67">
-        <v>-6.816559550000996</v>
+        <v>15.87655838936375</v>
       </c>
       <c r="P67">
-        <v>-20.51527505305031</v>
+        <v>47.78245680455667</v>
       </c>
       <c r="Q67">
-        <v>101.6847249469497</v>
+        <v>169.9824568045566</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1421694815449376</v>
+        <v>0.1396537205373477</v>
       </c>
       <c r="T67">
-        <v>2.224192252576582</v>
+        <v>2.167522414257453</v>
       </c>
       <c r="U67">
-        <v>0.1636</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V67">
-        <v>0.215697507011918</v>
+        <v>0.2494</v>
       </c>
       <c r="W67">
-        <v>0.1283118878528502</v>
+        <v>0.067554</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y67">
-        <v>0.8648657057414515</v>
+        <v>1.572133660658905</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6836,13 +6836,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1343400456450808</v>
+        <v>0.09290866692800528</v>
       </c>
       <c r="C68">
-        <v>-464.2092103602521</v>
+        <v>183.9011534493975</v>
       </c>
       <c r="D68">
-        <v>737.8993361698757</v>
+        <v>1386.009699979525</v>
       </c>
       <c r="E68">
         <v>264.7259002723586</v>
@@ -6869,45 +6869,45 @@
         <v>174.925</v>
       </c>
       <c r="M68">
-        <v>205.3684782123289</v>
+        <v>112.9777691877115</v>
       </c>
       <c r="N68">
-        <v>-30.44347821232898</v>
+        <v>61.94723081228844</v>
       </c>
       <c r="O68">
-        <v>-7.592603466154848</v>
+        <v>15.44963936458474</v>
       </c>
       <c r="P68">
-        <v>-22.85087474617414</v>
+        <v>46.4975914477037</v>
       </c>
       <c r="Q68">
-        <v>99.34912525382586</v>
+        <v>168.6975914477037</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1450038780609652</v>
+        <v>0.1421265497882508</v>
       </c>
       <c r="T68">
-        <v>2.28960967177001</v>
+        <v>2.224631634832583</v>
       </c>
       <c r="U68">
-        <v>0.1636</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V68">
-        <v>0.2124293629662829</v>
+        <v>0.2494</v>
       </c>
       <c r="W68">
-        <v>0.1288465562187161</v>
+        <v>0.067554</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y68">
-        <v>0.8517616798968841</v>
+        <v>1.548313453679225</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6918,13 +6918,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.1355180456450808</v>
+        <v>0.09302843166793887</v>
       </c>
       <c r="C69">
-        <v>-492.9176720551084</v>
+        <v>161.3665989850399</v>
       </c>
       <c r="D69">
-        <v>728.210700937597</v>
+        <v>1382.494971977745</v>
       </c>
       <c r="E69">
         <v>283.7457267349362</v>
@@ -6951,45 +6951,45 @@
         <v>174.925</v>
       </c>
       <c r="M69">
-        <v>208.4801218216066</v>
+        <v>114.6895535693435</v>
       </c>
       <c r="N69">
-        <v>-33.55512182160669</v>
+        <v>60.23544643065645</v>
       </c>
       <c r="O69">
-        <v>-8.368647382308708</v>
+        <v>15.02272033980572</v>
       </c>
       <c r="P69">
-        <v>-25.18647443929798</v>
+        <v>45.21272609085074</v>
       </c>
       <c r="Q69">
-        <v>97.01352556070201</v>
+        <v>167.4127260908507</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1480100561840247</v>
+        <v>0.1447492474786026</v>
       </c>
       <c r="T69">
-        <v>2.358991783035768</v>
+        <v>2.285202020291054</v>
       </c>
       <c r="U69">
-        <v>0.1636</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V69">
-        <v>0.2092587754593235</v>
+        <v>0.2494</v>
       </c>
       <c r="W69">
-        <v>0.1293652643348547</v>
+        <v>0.067554</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y69">
-        <v>0.8390488190029008</v>
+        <v>1.525204297654162</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7000,13 +7000,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.1366960456450808</v>
+        <v>0.09314819640787245</v>
       </c>
       <c r="C70">
-        <v>-521.3750070431288</v>
+        <v>138.8498251550884</v>
       </c>
       <c r="D70">
-        <v>718.7731924121545</v>
+        <v>1378.998024610372</v>
       </c>
       <c r="E70">
         <v>302.765553197514</v>
@@ -7033,45 +7033,45 @@
         <v>174.925</v>
       </c>
       <c r="M70">
-        <v>211.5917654308844</v>
+        <v>116.4013379509755</v>
       </c>
       <c r="N70">
-        <v>-36.66676543088442</v>
+        <v>58.52366204902444</v>
       </c>
       <c r="O70">
-        <v>-9.144691298462575</v>
+        <v>14.5958013150267</v>
       </c>
       <c r="P70">
-        <v>-27.52207413242185</v>
+        <v>43.92786073399774</v>
       </c>
       <c r="Q70">
-        <v>94.67792586757814</v>
+        <v>166.1278607339977</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1512041204397755</v>
+        <v>0.1475358637746014</v>
       </c>
       <c r="T70">
-        <v>2.432710276255636</v>
+        <v>2.349558054840679</v>
       </c>
       <c r="U70">
-        <v>0.1636</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V70">
-        <v>0.2061814405260981</v>
+        <v>0.2494</v>
       </c>
       <c r="W70">
-        <v>0.1298687163299304</v>
+        <v>0.067554</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y70">
-        <v>0.8267098657822699</v>
+        <v>1.502774822688659</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7082,13 +7082,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1378740456450808</v>
+        <v>0.1256313265199632</v>
       </c>
       <c r="C71">
-        <v>-549.5908541077054</v>
+        <v>-441.2802096732903</v>
       </c>
       <c r="D71">
-        <v>709.5771718101555</v>
+        <v>817.8878162445706</v>
       </c>
       <c r="E71">
         <v>321.7853796600916</v>
@@ -7115,37 +7115,37 @@
         <v>174.925</v>
       </c>
       <c r="M71">
-        <v>214.7034090401621</v>
+        <v>192.655626204742</v>
       </c>
       <c r="N71">
-        <v>-39.77840904016213</v>
+        <v>-17.73062620474204</v>
       </c>
       <c r="O71">
-        <v>-9.920735214616435</v>
+        <v>-4.422018175462664</v>
       </c>
       <c r="P71">
-        <v>-29.8576738255457</v>
+        <v>-13.30860802927937</v>
       </c>
       <c r="Q71">
-        <v>92.34232617445429</v>
+        <v>108.8913919707206</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1546042533571876</v>
+        <v>0.1525051594051955</v>
       </c>
       <c r="T71">
-        <v>2.511184801296141</v>
+        <v>2.46432238811075</v>
       </c>
       <c r="U71">
-        <v>0.1636</v>
+        <v>0.1468</v>
       </c>
       <c r="V71">
-        <v>0.2031933037068793</v>
+        <v>0.2264470332864132</v>
       </c>
       <c r="W71">
-        <v>0.1303575755135546</v>
+        <v>0.1135575755135545</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.8147285633796283</v>
+        <v>0.9079672545565887</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7164,13 +7164,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1390520456450808</v>
+        <v>0.1266413265199632</v>
       </c>
       <c r="C72">
-        <v>-577.5743649871778</v>
+        <v>-470.5184074809133</v>
       </c>
       <c r="D72">
-        <v>700.6134873932609</v>
+        <v>807.6694448995254</v>
       </c>
       <c r="E72">
         <v>340.8052061226695</v>
@@ -7197,37 +7197,37 @@
         <v>174.925</v>
       </c>
       <c r="M72">
-        <v>217.8150526494398</v>
+        <v>195.4477367294484</v>
       </c>
       <c r="N72">
-        <v>-42.89005264943987</v>
+        <v>-20.52273672944847</v>
       </c>
       <c r="O72">
-        <v>-10.6967791307703</v>
+        <v>-5.118370540324448</v>
       </c>
       <c r="P72">
-        <v>-32.19327351866956</v>
+        <v>-15.40436618912402</v>
       </c>
       <c r="Q72">
-        <v>90.00672648133042</v>
+        <v>106.795633810876</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1582310618024272</v>
+        <v>0.1560619980520353</v>
       </c>
       <c r="T72">
-        <v>2.594890961339345</v>
+        <v>2.546466467714442</v>
       </c>
       <c r="U72">
-        <v>0.1636</v>
+        <v>0.1468</v>
       </c>
       <c r="V72">
-        <v>0.2002905422253524</v>
+        <v>0.2232120756680359</v>
       </c>
       <c r="W72">
-        <v>0.1308324672919323</v>
+        <v>0.1140324672919324</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.8030895839027764</v>
+        <v>0.8949962937772087</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7246,13 +7246,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.1786224675234616</v>
+        <v>0.1276513265199632</v>
       </c>
       <c r="C73">
-        <v>-805.3207102891818</v>
+        <v>-499.5044272115931</v>
       </c>
       <c r="D73">
-        <v>491.8869685538343</v>
+        <v>797.703251631423</v>
       </c>
       <c r="E73">
         <v>359.8250325852468</v>
@@ -7279,45 +7279,45 @@
         <v>174.925</v>
       </c>
       <c r="M73">
-        <v>291.4179770943229</v>
+        <v>198.2398472541548</v>
       </c>
       <c r="N73">
-        <v>-116.492977094323</v>
+        <v>-23.31484725415484</v>
       </c>
       <c r="O73">
-        <v>-29.05334848732415</v>
+        <v>-5.814722905186218</v>
       </c>
       <c r="P73">
-        <v>-87.43962860699881</v>
+        <v>-17.50012434896862</v>
       </c>
       <c r="Q73">
-        <v>34.76037139300118</v>
+        <v>104.6998756510314</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1666956566176169</v>
+        <v>0.1598641359158986</v>
       </c>
       <c r="T73">
-        <v>2.790252458644546</v>
+        <v>2.634275656256318</v>
       </c>
       <c r="U73">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V73">
-        <v>0.1497035132663745</v>
+        <v>0.2200682436163734</v>
       </c>
       <c r="W73">
-        <v>0.1834939818371164</v>
+        <v>0.1144939818371164</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y73">
-        <v>0.6002546642597213</v>
+        <v>0.8823907121747129</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7328,13 +7328,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.1803224675234616</v>
+        <v>0.1286613265199632</v>
       </c>
       <c r="C74">
-        <v>-830.5566570916253</v>
+        <v>-528.2474902911184</v>
       </c>
       <c r="D74">
-        <v>485.6708482139687</v>
+        <v>787.9800150144755</v>
       </c>
       <c r="E74">
         <v>378.8448590478247</v>
@@ -7361,45 +7361,45 @@
         <v>174.925</v>
       </c>
       <c r="M74">
-        <v>295.5224556449472</v>
+        <v>201.0319577788612</v>
       </c>
       <c r="N74">
-        <v>-120.5974556449473</v>
+        <v>-26.10695777886127</v>
       </c>
       <c r="O74">
-        <v>-30.07700543784985</v>
+        <v>-6.511075270048002</v>
       </c>
       <c r="P74">
-        <v>-90.52045020709743</v>
+        <v>-19.59588250881327</v>
       </c>
       <c r="Q74">
-        <v>31.67954979290256</v>
+        <v>102.6041174911867</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1710133586396747</v>
+        <v>0.1639378550557521</v>
       </c>
       <c r="T74">
-        <v>2.889904332167565</v>
+        <v>2.728356929694044</v>
       </c>
       <c r="U74">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V74">
-        <v>0.1476242978043415</v>
+        <v>0.2170117402328126</v>
       </c>
       <c r="W74">
-        <v>0.1839426765338231</v>
+        <v>0.1149426765338231</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y74">
-        <v>0.5919177939227807</v>
+        <v>0.8701352856167307</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7410,13 +7410,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.1820224675234615</v>
+        <v>0.1296713265199632</v>
       </c>
       <c r="C75">
-        <v>-855.6374546772047</v>
+        <v>-556.7563739581886</v>
       </c>
       <c r="D75">
-        <v>479.6098770909669</v>
+        <v>778.4909578099829</v>
       </c>
       <c r="E75">
         <v>397.8646855104023</v>
@@ -7443,45 +7443,45 @@
         <v>174.925</v>
       </c>
       <c r="M75">
-        <v>299.6269341955714</v>
+        <v>203.8240683035676</v>
       </c>
       <c r="N75">
-        <v>-124.7019341955715</v>
+        <v>-28.89906830356765</v>
       </c>
       <c r="O75">
-        <v>-31.10066238837553</v>
+        <v>-7.207427634909771</v>
       </c>
       <c r="P75">
-        <v>-93.60127180719596</v>
+        <v>-21.69164066865788</v>
       </c>
       <c r="Q75">
-        <v>28.59872819280403</v>
+        <v>100.5083593313421</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1756508904411441</v>
+        <v>0.1683133311689281</v>
       </c>
       <c r="T75">
-        <v>2.996937825951549</v>
+        <v>2.829407186349379</v>
       </c>
       <c r="U75">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.1456020471494875</v>
+        <v>0.2140389766679796</v>
       </c>
       <c r="W75">
-        <v>0.1843790782251406</v>
+        <v>0.1153790782251406</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y75">
-        <v>0.5838093309923317</v>
+        <v>0.8582156241699262</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7492,13 +7492,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.1837224675234615</v>
+        <v>0.1306813265199632</v>
       </c>
       <c r="C76">
-        <v>-880.5688400445414</v>
+        <v>-585.0394376912533</v>
       </c>
       <c r="D76">
-        <v>473.698318186208</v>
+        <v>769.2277205394961</v>
       </c>
       <c r="E76">
         <v>416.8845119729801</v>
@@ -7525,45 +7525,45 @@
         <v>174.925</v>
       </c>
       <c r="M76">
-        <v>303.7314127461958</v>
+        <v>206.616178828274</v>
       </c>
       <c r="N76">
-        <v>-128.8064127461958</v>
+        <v>-31.69117882827408</v>
       </c>
       <c r="O76">
-        <v>-32.12431933890124</v>
+        <v>-7.903779999771555</v>
       </c>
       <c r="P76">
-        <v>-96.68209340729456</v>
+        <v>-23.78739882850252</v>
       </c>
       <c r="Q76">
-        <v>25.51790659270543</v>
+        <v>98.41260117149747</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1806451554581112</v>
+        <v>0.173025382367733</v>
       </c>
       <c r="T76">
-        <v>3.112204665411224</v>
+        <v>2.938230539670509</v>
       </c>
       <c r="U76">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.1436344519177377</v>
+        <v>0.2111465580643583</v>
       </c>
       <c r="W76">
-        <v>0.1848036852761522</v>
+        <v>0.1158036852761522</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y76">
-        <v>0.5759200157086515</v>
+        <v>0.8466181157351974</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7574,13 +7574,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.1854224675234616</v>
+        <v>0.1316913265199632</v>
       </c>
       <c r="C77">
-        <v>-905.35627078457</v>
+        <v>-613.1046477708172</v>
       </c>
       <c r="D77">
-        <v>467.930713908757</v>
+        <v>760.1823369225098</v>
       </c>
       <c r="E77">
         <v>435.9043384355577</v>
@@ -7607,45 +7607,45 @@
         <v>174.925</v>
       </c>
       <c r="M77">
-        <v>307.83589129682</v>
+        <v>209.4082893529804</v>
       </c>
       <c r="N77">
-        <v>-132.9108912968201</v>
+        <v>-34.48328935298048</v>
       </c>
       <c r="O77">
-        <v>-33.14797628942693</v>
+        <v>-8.600132364633332</v>
       </c>
       <c r="P77">
-        <v>-99.76291500739313</v>
+        <v>-25.88315698834715</v>
       </c>
       <c r="Q77">
-        <v>22.43708499260686</v>
+        <v>96.31684301165285</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1860389616764356</v>
+        <v>0.1781143976624424</v>
       </c>
       <c r="T77">
-        <v>3.236692852027673</v>
+        <v>3.055759761257329</v>
       </c>
       <c r="U77">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.1417193258921678</v>
+        <v>0.2083312706235002</v>
       </c>
       <c r="W77">
-        <v>0.1852169694724702</v>
+        <v>0.1162169694724702</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y77">
-        <v>0.5682410821658694</v>
+        <v>0.8353298741920615</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7656,13 +7656,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.1871224675234616</v>
+        <v>0.1327013265199632</v>
       </c>
       <c r="C78">
-        <v>-930.0049418858306</v>
+        <v>-640.9596001289169</v>
       </c>
       <c r="D78">
-        <v>462.3018692700741</v>
+        <v>751.3472110269877</v>
       </c>
       <c r="E78">
         <v>454.9241648981354</v>
@@ -7689,45 +7689,45 @@
         <v>174.925</v>
       </c>
       <c r="M78">
-        <v>311.9403698474442</v>
+        <v>212.2003998776868</v>
       </c>
       <c r="N78">
-        <v>-137.0153698474443</v>
+        <v>-37.27539987768688</v>
       </c>
       <c r="O78">
-        <v>-34.17163323995261</v>
+        <v>-9.296484729495107</v>
       </c>
       <c r="P78">
-        <v>-102.8437366074917</v>
+        <v>-27.97891514819177</v>
       </c>
       <c r="Q78">
-        <v>19.35626339250831</v>
+        <v>94.22108485180821</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1918822517462871</v>
+        <v>0.1836274975650441</v>
       </c>
       <c r="T78">
-        <v>3.371555054195493</v>
+        <v>3.183083084643052</v>
       </c>
       <c r="U78">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.1398545979199025</v>
+        <v>0.2055900696942436</v>
       </c>
       <c r="W78">
-        <v>0.185619377768885</v>
+        <v>0.1166193777688851</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y78">
-        <v>0.5607642258215817</v>
+        <v>0.8243386916369028</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7738,13 +7738,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.1888224675234616</v>
+        <v>0.1337113265199632</v>
       </c>
       <c r="C79">
-        <v>-954.5198013412505</v>
+        <v>-668.6115416235086</v>
       </c>
       <c r="D79">
-        <v>456.8068362772319</v>
+        <v>742.7150959949738</v>
       </c>
       <c r="E79">
         <v>473.9439913607132</v>
@@ -7771,45 +7771,45 @@
         <v>174.925</v>
       </c>
       <c r="M79">
-        <v>316.0448483980686</v>
+        <v>214.9925104023932</v>
       </c>
       <c r="N79">
-        <v>-141.1198483980686</v>
+        <v>-40.06751040239328</v>
       </c>
       <c r="O79">
-        <v>-35.19529019047831</v>
+        <v>-9.992837094356885</v>
       </c>
       <c r="P79">
-        <v>-105.9245582075903</v>
+        <v>-30.0746733080364</v>
       </c>
       <c r="Q79">
-        <v>16.27544179240971</v>
+        <v>92.12532669196359</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.1982336539961257</v>
+        <v>0.1896199974591765</v>
       </c>
       <c r="T79">
-        <v>3.518144404377906</v>
+        <v>3.321478001366662</v>
       </c>
       <c r="U79">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.1380383044404232</v>
+        <v>0.2029200687891235</v>
       </c>
       <c r="W79">
-        <v>0.1860113339017567</v>
+        <v>0.1170113339017567</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y79">
-        <v>0.5534815735381845</v>
+        <v>0.813632994342917</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7820,13 +7820,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.1905224675234616</v>
+        <v>0.1347213265199632</v>
       </c>
       <c r="C80">
-        <v>-978.9055646549631</v>
+        <v>-696.0673898630049</v>
       </c>
       <c r="D80">
-        <v>451.440899426097</v>
+        <v>734.2790742180551</v>
       </c>
       <c r="E80">
         <v>492.9638178232908</v>
@@ -7853,45 +7853,45 @@
         <v>174.925</v>
       </c>
       <c r="M80">
-        <v>320.1493269486928</v>
+        <v>217.7846209270996</v>
       </c>
       <c r="N80">
-        <v>-145.2243269486929</v>
+        <v>-42.85962092709968</v>
       </c>
       <c r="O80">
-        <v>-36.218947141004</v>
+        <v>-10.68918945921866</v>
       </c>
       <c r="P80">
-        <v>-109.0053798076889</v>
+        <v>-32.17043146788102</v>
       </c>
       <c r="Q80">
-        <v>13.19462019231113</v>
+        <v>90.02956853211896</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.2051624564504951</v>
+        <v>0.1961572700709572</v>
       </c>
       <c r="T80">
-        <v>3.678060059122356</v>
+        <v>3.472454274156056</v>
       </c>
       <c r="U80">
-        <v>0.2158</v>
+        <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.1362685825886229</v>
+        <v>0.2003185294456732</v>
       </c>
       <c r="W80">
-        <v>0.1863932398773752</v>
+        <v>0.1173932398773752</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y80">
-        <v>0.5463856559287206</v>
+        <v>0.8032018021077515</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7902,13 +7902,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.1922224675234616</v>
+        <v>0.1800386477975829</v>
       </c>
       <c r="C81">
-        <v>-1003.166728338561</v>
+        <v>-962.9708270421376</v>
       </c>
       <c r="D81">
-        <v>446.1995622050768</v>
+        <v>486.3954635015003</v>
       </c>
       <c r="E81">
         <v>511.9836442858686</v>
@@ -7935,37 +7935,37 @@
         <v>174.925</v>
       </c>
       <c r="M81">
-        <v>324.2538054993171</v>
+        <v>301.7153111411625</v>
       </c>
       <c r="N81">
-        <v>-149.3288054993171</v>
+        <v>-126.7903111411625</v>
       </c>
       <c r="O81">
-        <v>-37.24260409152969</v>
+        <v>-31.62150359860594</v>
       </c>
       <c r="P81">
-        <v>-112.0862014077874</v>
+        <v>-95.16880754255659</v>
       </c>
       <c r="Q81">
-        <v>10.11379859221256</v>
+        <v>27.0311924574434</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.2127511448528996</v>
+        <v>0.2111615271106203</v>
       </c>
       <c r="T81">
-        <v>3.85320577622342</v>
+        <v>3.818972912485456</v>
       </c>
       <c r="U81">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.1345436638216783</v>
+        <v>0.1445942363183177</v>
       </c>
       <c r="W81">
-        <v>0.1867654773472818</v>
+        <v>0.1717654773472818</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.5394693818030406</v>
+        <v>0.5797683894078495</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7984,13 +7984,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.1939224675234616</v>
+        <v>0.1815886477975829</v>
       </c>
       <c r="C82">
-        <v>-1027.307582477973</v>
+        <v>-987.5427595213475</v>
       </c>
       <c r="D82">
-        <v>441.0785345282424</v>
+        <v>480.843357484868</v>
       </c>
       <c r="E82">
         <v>531.0034707484463</v>
@@ -8017,37 +8017,37 @@
         <v>174.925</v>
       </c>
       <c r="M82">
-        <v>328.3582840499413</v>
+        <v>305.5344922948481</v>
       </c>
       <c r="N82">
-        <v>-153.4332840499414</v>
+        <v>-130.6094922948481</v>
       </c>
       <c r="O82">
-        <v>-38.26626104205538</v>
+        <v>-32.57400737833512</v>
       </c>
       <c r="P82">
-        <v>-115.167023007886</v>
+        <v>-98.03548491651298</v>
       </c>
       <c r="Q82">
-        <v>7.032976992113987</v>
+        <v>24.164515083487</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.2210987020955446</v>
+        <v>0.2194296034661513</v>
       </c>
       <c r="T82">
-        <v>4.045866065034592</v>
+        <v>4.009921558109729</v>
       </c>
       <c r="U82">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.1328618680239074</v>
+        <v>0.1427868083643387</v>
       </c>
       <c r="W82">
-        <v>0.1871284088804408</v>
+        <v>0.1721284088804408</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.5327260145305026</v>
+        <v>0.5725212845402514</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8066,13 +8066,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1956224675234616</v>
+        <v>0.1831386477975829</v>
       </c>
       <c r="C83">
-        <v>-1051.332222444778</v>
+        <v>-1011.989370185267</v>
       </c>
       <c r="D83">
-        <v>436.0737210240156</v>
+        <v>475.4165732835264</v>
       </c>
       <c r="E83">
         <v>550.0232972110241</v>
@@ -8099,37 +8099,37 @@
         <v>174.925</v>
       </c>
       <c r="M83">
-        <v>332.4627626005657</v>
+        <v>309.3536734485337</v>
       </c>
       <c r="N83">
-        <v>-157.5377626005657</v>
+        <v>-134.4286734485337</v>
       </c>
       <c r="O83">
-        <v>-39.28991799258109</v>
+        <v>-33.52651115806432</v>
       </c>
       <c r="P83">
-        <v>-118.2478446079846</v>
+        <v>-100.9021622904694</v>
       </c>
       <c r="Q83">
-        <v>3.952155392015356</v>
+        <v>21.29783770953057</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.2303249495742575</v>
+        <v>0.2285680036485802</v>
       </c>
       <c r="T83">
-        <v>4.25880638424694</v>
+        <v>4.220970061168135</v>
       </c>
       <c r="U83">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.1312215980483036</v>
+        <v>0.1410240082610753</v>
       </c>
       <c r="W83">
-        <v>0.1874823791411761</v>
+        <v>0.1724823791411761</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.5261491501535827</v>
+        <v>0.5654531205335815</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8148,13 +8148,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1973224675234616</v>
+        <v>0.1846886477975829</v>
       </c>
       <c r="C84">
-        <v>-1075.244559819152</v>
+        <v>-1036.314854815555</v>
       </c>
       <c r="D84">
-        <v>431.1812101122194</v>
+        <v>470.1109151158162</v>
       </c>
       <c r="E84">
         <v>569.0431236736017</v>
@@ -8181,37 +8181,37 @@
         <v>174.925</v>
       </c>
       <c r="M84">
-        <v>336.5672411511899</v>
+        <v>313.1728546022193</v>
       </c>
       <c r="N84">
-        <v>-161.6422411511899</v>
+        <v>-138.2478546022194</v>
       </c>
       <c r="O84">
-        <v>-40.31357494310677</v>
+        <v>-34.47901493779352</v>
       </c>
       <c r="P84">
-        <v>-121.3286662080831</v>
+        <v>-103.7688396644259</v>
       </c>
       <c r="Q84">
-        <v>0.8713337919168396</v>
+        <v>18.43116033557413</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.2405763356617162</v>
+        <v>0.238721781629057</v>
       </c>
       <c r="T84">
-        <v>4.495406738927325</v>
+        <v>4.455468397899699</v>
       </c>
       <c r="U84">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.1296213346574706</v>
+        <v>0.1393042032822817</v>
       </c>
       <c r="W84">
-        <v>0.1878277159809179</v>
+        <v>0.1728277159809178</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.5197326971029294</v>
+        <v>0.5585573507709769</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8230,13 +8230,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1990224675234616</v>
+        <v>0.1862386477975829</v>
       </c>
       <c r="C85">
-        <v>-1099.048332585678</v>
+        <v>-1060.523223961054</v>
       </c>
       <c r="D85">
-        <v>426.3972638082705</v>
+        <v>464.922372432895</v>
       </c>
       <c r="E85">
         <v>588.0629501361793</v>
@@ -8263,37 +8263,37 @@
         <v>174.925</v>
       </c>
       <c r="M85">
-        <v>340.6717197018141</v>
+        <v>316.9920357559049</v>
       </c>
       <c r="N85">
-        <v>-165.7467197018142</v>
+        <v>-142.067035755905</v>
       </c>
       <c r="O85">
-        <v>-41.33723189363246</v>
+        <v>-35.4315187175227</v>
       </c>
       <c r="P85">
-        <v>-124.4094878081817</v>
+        <v>-106.6355170383823</v>
       </c>
       <c r="Q85">
-        <v>-2.209487808181734</v>
+        <v>15.56448296161773</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.2520337671712289</v>
+        <v>0.2500701217248839</v>
       </c>
       <c r="T85">
-        <v>4.759842429452462</v>
+        <v>4.71755477424674</v>
       </c>
       <c r="U85">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.1280596318302722</v>
+        <v>0.1376258393873144</v>
       </c>
       <c r="W85">
-        <v>0.1881647314510273</v>
+        <v>0.1731647314510273</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5134708573787977</v>
+        <v>0.551827744135182</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8312,13 +8312,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.2007224675234616</v>
+        <v>0.1877886477975829</v>
       </c>
       <c r="C86">
-        <v>-1122.747114657869</v>
+        <v>-1084.618313048136</v>
       </c>
       <c r="D86">
-        <v>421.7183081986572</v>
+        <v>459.8471098083904</v>
       </c>
       <c r="E86">
         <v>607.0827765987569</v>
@@ -8345,37 +8345,37 @@
         <v>174.925</v>
       </c>
       <c r="M86">
-        <v>344.7761982524384</v>
+        <v>320.8112169095905</v>
       </c>
       <c r="N86">
-        <v>-169.8511982524385</v>
+        <v>-145.8862169095905</v>
       </c>
       <c r="O86">
-        <v>-42.36088884415815</v>
+        <v>-36.38402249725188</v>
       </c>
       <c r="P86">
-        <v>-127.4903094082803</v>
+        <v>-109.5021944123387</v>
       </c>
       <c r="Q86">
-        <v>-5.290309408280308</v>
+        <v>12.69780558766134</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.2649233776194306</v>
+        <v>0.262837004332689</v>
       </c>
       <c r="T86">
-        <v>5.057332581293239</v>
+        <v>5.01240194763716</v>
       </c>
       <c r="U86">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1265351124037213</v>
+        <v>0.1359874365374654</v>
       </c>
       <c r="W86">
-        <v>0.188493722743277</v>
+        <v>0.173493722743277</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.5073581090766692</v>
+        <v>0.5452583662288109</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8394,13 +8394,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2024224675234615</v>
+        <v>0.1893386477975829</v>
       </c>
       <c r="C87">
-        <v>-1146.344324782406</v>
+        <v>-1108.603791835989</v>
       </c>
       <c r="D87">
-        <v>417.1409245366975</v>
+        <v>454.881457483115</v>
       </c>
       <c r="E87">
         <v>626.1026030613345</v>
@@ -8427,37 +8427,37 @@
         <v>174.925</v>
       </c>
       <c r="M87">
-        <v>348.8806768030626</v>
+        <v>324.6303980632761</v>
       </c>
       <c r="N87">
-        <v>-173.9556768030627</v>
+        <v>-149.7053980632761</v>
       </c>
       <c r="O87">
-        <v>-43.38454579468383</v>
+        <v>-37.33652627698106</v>
       </c>
       <c r="P87">
-        <v>-130.5711310083788</v>
+        <v>-112.368871786295</v>
       </c>
       <c r="Q87">
-        <v>-8.371131008378825</v>
+        <v>9.831128213704943</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.2795316027940594</v>
+        <v>0.2773061379548682</v>
       </c>
       <c r="T87">
-        <v>5.394488086712788</v>
+        <v>5.346562077479637</v>
       </c>
       <c r="U87">
-        <v>0.2158</v>
+        <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1250464640225011</v>
+        <v>0.134387584342907</v>
       </c>
       <c r="W87">
-        <v>0.1888149730639443</v>
+        <v>0.1738149730639443</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5013891901463554</v>
+        <v>0.5388435619202366</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8476,13 +8476,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.230431378186516</v>
+        <v>0.1908886477975829</v>
       </c>
       <c r="C88">
-        <v>-1228.645176409891</v>
+        <v>-1132.483173265834</v>
       </c>
       <c r="D88">
-        <v>353.8598993717907</v>
+        <v>450.0219025158474</v>
       </c>
       <c r="E88">
         <v>645.1224295239124</v>
@@ -8509,45 +8509,45 @@
         <v>174.925</v>
       </c>
       <c r="M88">
-        <v>402.0563076271374</v>
+        <v>328.4495792169617</v>
       </c>
       <c r="N88">
-        <v>-227.1313076271374</v>
+        <v>-153.5245792169617</v>
       </c>
       <c r="O88">
-        <v>-56.64654812220807</v>
+        <v>-38.28903005671026</v>
       </c>
       <c r="P88">
-        <v>-170.4847595049293</v>
+        <v>-115.2355491602515</v>
       </c>
       <c r="Q88">
-        <v>-48.28475950492935</v>
+        <v>6.964450839748508</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.2998617934440241</v>
+        <v>0.2938422906659303</v>
       </c>
       <c r="T88">
-        <v>5.863705642023293</v>
+        <v>5.728459368728182</v>
       </c>
       <c r="U88">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1085079233241592</v>
+        <v>0.1328249380133383</v>
       </c>
       <c r="W88">
-        <v>0.2191287524469217</v>
+        <v>0.1741287524469217</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y88">
-        <v>0.4350758753975911</v>
+        <v>0.5325779391072105</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8558,13 +8558,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.232431378186516</v>
+        <v>0.1924386477975829</v>
       </c>
       <c r="C89">
-        <v>-1251.457075811223</v>
+        <v>-1156.259821748909</v>
       </c>
       <c r="D89">
-        <v>350.0678264330363</v>
+        <v>445.2650804953498</v>
       </c>
       <c r="E89">
         <v>664.14225598649</v>
@@ -8591,45 +8591,45 @@
         <v>174.925</v>
       </c>
       <c r="M89">
-        <v>406.7313809716389</v>
+        <v>332.2687603706473</v>
       </c>
       <c r="N89">
-        <v>-231.806380971639</v>
+        <v>-157.3437603706473</v>
       </c>
       <c r="O89">
-        <v>-57.81251141432676</v>
+        <v>-39.24153383643944</v>
       </c>
       <c r="P89">
-        <v>-173.9938695573122</v>
+        <v>-118.1022265342079</v>
       </c>
       <c r="Q89">
-        <v>-51.79386955731223</v>
+        <v>4.097773465792116</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.3194050083243336</v>
+        <v>0.3129224668710018</v>
       </c>
       <c r="T89">
-        <v>6.31475992217893</v>
+        <v>6.169110089399581</v>
       </c>
       <c r="U89">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1072607058146861</v>
+        <v>0.1312982145878976</v>
       </c>
       <c r="W89">
-        <v>0.2194353185107502</v>
+        <v>0.1744353185107502</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y89">
-        <v>0.4300750032665843</v>
+        <v>0.5264563536002311</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8640,13 +8640,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.234431378186516</v>
+        <v>0.1939886477975829</v>
       </c>
       <c r="C90">
-        <v>-1274.188562865995</v>
+        <v>-1179.936960934325</v>
       </c>
       <c r="D90">
-        <v>346.3561658408422</v>
+        <v>440.6077677725121</v>
       </c>
       <c r="E90">
         <v>683.1620824490678</v>
@@ -8673,45 +8673,45 @@
         <v>174.925</v>
       </c>
       <c r="M90">
-        <v>411.4064543161406</v>
+        <v>336.0879415243329</v>
       </c>
       <c r="N90">
-        <v>-236.4814543161406</v>
+        <v>-161.162941524333</v>
       </c>
       <c r="O90">
-        <v>-58.97847470644547</v>
+        <v>-40.19403761616864</v>
       </c>
       <c r="P90">
-        <v>-177.5029796096952</v>
+        <v>-120.9689039081643</v>
       </c>
       <c r="Q90">
-        <v>-55.30297960969517</v>
+        <v>1.231096091835681</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.3422054256846948</v>
+        <v>0.3351826724435853</v>
       </c>
       <c r="T90">
-        <v>6.840989915693842</v>
+        <v>6.683202596849546</v>
       </c>
       <c r="U90">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.106041834157701</v>
+        <v>0.1298061894221261</v>
       </c>
       <c r="W90">
-        <v>0.2197349171640371</v>
+        <v>0.1747349171640371</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y90">
-        <v>0.4251877873203731</v>
+        <v>0.5204738950365921</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8722,13 +8722,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2364313781865161</v>
+        <v>0.1955386477975829</v>
       </c>
       <c r="C91">
-        <v>-1296.842168501086</v>
+        <v>-1203.517680994463</v>
       </c>
       <c r="D91">
-        <v>342.7223866683291</v>
+        <v>436.0468741749514</v>
       </c>
       <c r="E91">
         <v>702.1819089116455</v>
@@ -8755,45 +8755,45 @@
         <v>174.925</v>
       </c>
       <c r="M91">
-        <v>416.0815276606422</v>
+        <v>339.9071226780185</v>
       </c>
       <c r="N91">
-        <v>-241.1565276606422</v>
+        <v>-164.9821226780185</v>
       </c>
       <c r="O91">
-        <v>-60.14443799856417</v>
+        <v>-41.14654139589782</v>
       </c>
       <c r="P91">
-        <v>-181.012089662078</v>
+        <v>-123.8355812821207</v>
       </c>
       <c r="Q91">
-        <v>-58.81208966207805</v>
+        <v>-1.635581282120711</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.3691513734742126</v>
+        <v>0.3614901881202749</v>
       </c>
       <c r="T91">
-        <v>7.462898089847829</v>
+        <v>7.290766469290415</v>
       </c>
       <c r="U91">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1048503528750303</v>
+        <v>0.1283476929117651</v>
       </c>
       <c r="W91">
-        <v>0.2200277832633176</v>
+        <v>0.1750277832633176</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y91">
-        <v>0.4204103964516048</v>
+        <v>0.5146258737440461</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8804,13 +8804,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.238431378186516</v>
+        <v>0.1970886477975829</v>
       </c>
       <c r="C92">
-        <v>-1319.420318533736</v>
+        <v>-1227.004945462538</v>
       </c>
       <c r="D92">
-        <v>339.1640630982563</v>
+        <v>431.5794361694544</v>
       </c>
       <c r="E92">
         <v>721.2017353742233</v>
@@ -8837,45 +8837,45 @@
         <v>174.925</v>
       </c>
       <c r="M92">
-        <v>420.7566010051438</v>
+        <v>343.7263038317041</v>
       </c>
       <c r="N92">
-        <v>-245.8316010051439</v>
+        <v>-168.8013038317042</v>
       </c>
       <c r="O92">
-        <v>-61.31040129068288</v>
+        <v>-42.09904517562702</v>
       </c>
       <c r="P92">
-        <v>-184.521199714461</v>
+        <v>-126.7022586560771</v>
       </c>
       <c r="Q92">
-        <v>-62.32119971446099</v>
+        <v>-4.502258656077146</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.4014865108216338</v>
+        <v>0.3930592069323024</v>
       </c>
       <c r="T92">
-        <v>8.209187898832612</v>
+        <v>8.019843116219455</v>
       </c>
       <c r="U92">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.1036853489541966</v>
+        <v>0.1269216074349677</v>
       </c>
       <c r="W92">
-        <v>0.2203141412270585</v>
+        <v>0.1753141412270585</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y92">
-        <v>0.4157391698243648</v>
+        <v>0.5089078084802234</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8886,13 +8886,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.240431378186516</v>
+        <v>0.1986386477975829</v>
       </c>
       <c r="C93">
-        <v>-1341.925339071991</v>
+        <v>-1250.401597654094</v>
       </c>
       <c r="D93">
-        <v>335.6788690225795</v>
+        <v>427.2026104404765</v>
       </c>
       <c r="E93">
         <v>740.2215618368009</v>
@@ -8919,45 +8919,45 @@
         <v>174.925</v>
       </c>
       <c r="M93">
-        <v>425.4316743496454</v>
+        <v>347.5454849853897</v>
       </c>
       <c r="N93">
-        <v>-250.5066743496454</v>
+        <v>-172.6204849853897</v>
       </c>
       <c r="O93">
-        <v>-62.47636458280157</v>
+        <v>-43.0515489553562</v>
       </c>
       <c r="P93">
-        <v>-188.0303097668439</v>
+        <v>-129.5689360300335</v>
       </c>
       <c r="Q93">
-        <v>-65.83030976684387</v>
+        <v>-7.368936030033552</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.4410072342462598</v>
+        <v>0.4316435632581139</v>
       </c>
       <c r="T93">
-        <v>9.121319887591792</v>
+        <v>8.910936795799397</v>
       </c>
       <c r="U93">
-        <v>0.2458</v>
+        <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.1025459495151395</v>
+        <v>0.1255268644961219</v>
       </c>
       <c r="W93">
-        <v>0.2205942056091787</v>
+        <v>0.1755942056091787</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>D2/D</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y93">
-        <v>0.4111706075186025</v>
+        <v>0.5033154149804407</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8968,13 +8968,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.242431378186516</v>
+        <v>0.2330533618305369</v>
       </c>
       <c r="C94">
-        <v>-1364.35946158557</v>
+        <v>-1347.935665616622</v>
       </c>
       <c r="D94">
-        <v>332.264572971578</v>
+        <v>348.6883689405257</v>
       </c>
       <c r="E94">
         <v>759.2413882993785</v>
@@ -9001,37 +9001,37 @@
         <v>174.925</v>
       </c>
       <c r="M94">
-        <v>430.106747694147</v>
+        <v>412.6085073485755</v>
       </c>
       <c r="N94">
-        <v>-255.181747694147</v>
+        <v>-237.6835073485755</v>
       </c>
       <c r="O94">
-        <v>-63.64232787492027</v>
+        <v>-59.27826673273474</v>
       </c>
       <c r="P94">
-        <v>-191.5394198192267</v>
+        <v>-178.4052406158408</v>
       </c>
       <c r="Q94">
-        <v>-69.33941981922675</v>
+        <v>-56.20524061584081</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.4904081385270424</v>
+        <v>0.4881829340773032</v>
       </c>
       <c r="T94">
-        <v>10.26148487354077</v>
+        <v>10.21669593712017</v>
       </c>
       <c r="U94">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.1014313196291053</v>
+        <v>0.1057329023105772</v>
       </c>
       <c r="W94">
-        <v>0.2208681816351659</v>
+        <v>0.2108681816351659</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.4067013617847046</v>
+        <v>0.4239490870512316</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9050,13 +9050,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2444313781865161</v>
+        <v>0.2349533618305368</v>
       </c>
       <c r="C95">
-        <v>-1386.724827670388</v>
+        <v>-1370.457982833663</v>
       </c>
       <c r="D95">
-        <v>328.9190333493379</v>
+        <v>345.185878186063</v>
       </c>
       <c r="E95">
         <v>778.2612147619564</v>
@@ -9083,37 +9083,37 @@
         <v>174.925</v>
       </c>
       <c r="M95">
-        <v>434.7818210386486</v>
+        <v>417.0933824284513</v>
       </c>
       <c r="N95">
-        <v>-259.8568210386487</v>
+        <v>-242.1683824284514</v>
       </c>
       <c r="O95">
-        <v>-64.80829116703897</v>
+        <v>-60.39679457765578</v>
       </c>
       <c r="P95">
-        <v>-195.0485298716097</v>
+        <v>-181.7715878507956</v>
       </c>
       <c r="Q95">
-        <v>-72.84852987160968</v>
+        <v>-59.57158785079559</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.5539235868880485</v>
+        <v>0.5513804960883464</v>
       </c>
       <c r="T95">
-        <v>11.72741128404659</v>
+        <v>11.67622392813733</v>
       </c>
       <c r="U95">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.1003406602782547</v>
+        <v>0.1045959893825064</v>
       </c>
       <c r="W95">
-        <v>0.221136265703605</v>
+        <v>0.211136265703605</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.4023282288622885</v>
+        <v>0.4193904947173474</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9132,13 +9132,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2464313781865161</v>
+        <v>0.2368533618305369</v>
       </c>
       <c r="C96">
-        <v>-1409.023493528103</v>
+        <v>-1392.91063645128</v>
       </c>
       <c r="D96">
-        <v>325.6401939542005</v>
+        <v>341.7530510310231</v>
       </c>
       <c r="E96">
         <v>797.281041224534</v>
@@ -9165,37 +9165,37 @@
         <v>174.925</v>
       </c>
       <c r="M96">
-        <v>439.4568943831502</v>
+        <v>421.5782575083271</v>
       </c>
       <c r="N96">
-        <v>-264.5318943831502</v>
+        <v>-246.6532575083272</v>
       </c>
       <c r="O96">
-        <v>-65.97425445915768</v>
+        <v>-61.51532242257679</v>
       </c>
       <c r="P96">
-        <v>-198.5576399239926</v>
+        <v>-185.1379350857504</v>
       </c>
       <c r="Q96">
-        <v>-76.35763992399256</v>
+        <v>-62.93793508575038</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.6386108513693901</v>
+        <v>0.635643912103071</v>
       </c>
       <c r="T96">
-        <v>13.6819798313877</v>
+        <v>13.62226124949356</v>
       </c>
       <c r="U96">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.09927320644550734</v>
+        <v>0.1034832660912032</v>
       </c>
       <c r="W96">
-        <v>0.2213986458556943</v>
+        <v>0.2113986458556943</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3980481413212003</v>
+        <v>0.4149288937097161</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9214,13 +9214,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2484313781865161</v>
+        <v>0.2387533618305369</v>
       </c>
       <c r="C97">
-        <v>-1431.257434180384</v>
+        <v>-1415.295684389135</v>
       </c>
       <c r="D97">
-        <v>322.4260797644974</v>
+        <v>338.3878295557463</v>
       </c>
       <c r="E97">
         <v>816.3008676871118</v>
@@ -9247,37 +9247,37 @@
         <v>174.925</v>
       </c>
       <c r="M97">
-        <v>444.1319677276518</v>
+        <v>426.063132588203</v>
       </c>
       <c r="N97">
-        <v>-269.2069677276518</v>
+        <v>-251.138132588203</v>
       </c>
       <c r="O97">
-        <v>-67.14021775127637</v>
+        <v>-62.63385026749783</v>
       </c>
       <c r="P97">
-        <v>-202.0667499763755</v>
+        <v>-188.5042823207052</v>
       </c>
       <c r="Q97">
-        <v>-79.86674997637547</v>
+        <v>-66.30428232070517</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.7571730216432685</v>
+        <v>0.7536126945236856</v>
       </c>
       <c r="T97">
-        <v>16.41837579766525</v>
+        <v>16.34671349939228</v>
       </c>
       <c r="U97">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.09822822532502833</v>
+        <v>0.102393968553401</v>
       </c>
       <c r="W97">
-        <v>0.2216555022151081</v>
+        <v>0.2116555022151081</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3938581608862403</v>
+        <v>0.4105612211443506</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9296,13 +9296,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.250431378186516</v>
+        <v>0.2406533618305369</v>
       </c>
       <c r="C98">
-        <v>-1453.428547436041</v>
+        <v>-1437.615104300426</v>
       </c>
       <c r="D98">
-        <v>319.2747929714171</v>
+        <v>335.0882361070326</v>
       </c>
       <c r="E98">
         <v>835.3206941496892</v>
@@ -9329,37 +9329,37 @@
         <v>174.925</v>
       </c>
       <c r="M98">
-        <v>448.8070410721533</v>
+        <v>430.5480076680788</v>
       </c>
       <c r="N98">
-        <v>-273.8820410721534</v>
+        <v>-255.6230076680788</v>
       </c>
       <c r="O98">
-        <v>-68.30618104339506</v>
+        <v>-63.75237811241885</v>
       </c>
       <c r="P98">
-        <v>-205.5758600287583</v>
+        <v>-191.8706295556599</v>
       </c>
       <c r="Q98">
-        <v>-83.37586002875832</v>
+        <v>-69.67062955565996</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.9350162770540835</v>
+        <v>0.9305658681546051</v>
       </c>
       <c r="T98">
-        <v>20.52296974708151</v>
+        <v>20.4333918742403</v>
       </c>
       <c r="U98">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.0972050146445593</v>
+        <v>0.1013273647143031</v>
       </c>
       <c r="W98">
-        <v>0.2219070074003673</v>
+        <v>0.2119070074003673</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.389755471710342</v>
+        <v>0.4062845417574302</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9378,13 +9378,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.252431378186516</v>
+        <v>0.2425533618305369</v>
       </c>
       <c r="C99">
-        <v>-1475.538657627775</v>
+        <v>-1459.870797447466</v>
       </c>
       <c r="D99">
-        <v>316.1845092422612</v>
+        <v>331.8523694225705</v>
       </c>
       <c r="E99">
         <v>854.340520612267</v>
@@ -9411,37 +9411,37 @@
         <v>174.925</v>
       </c>
       <c r="M99">
-        <v>453.482114416655</v>
+        <v>435.0328827479546</v>
       </c>
       <c r="N99">
-        <v>-278.557114416655</v>
+        <v>-260.1078827479546</v>
       </c>
       <c r="O99">
-        <v>-69.47214433551376</v>
+        <v>-64.87090595733989</v>
       </c>
       <c r="P99">
-        <v>-209.0849700811413</v>
+        <v>-195.2369767906148</v>
       </c>
       <c r="Q99">
-        <v>-86.88497008114126</v>
+        <v>-73.03697679061477</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.231421702738778</v>
+        <v>1.22548782420614</v>
       </c>
       <c r="T99">
-        <v>27.36395966277535</v>
+        <v>27.24452249898707</v>
       </c>
       <c r="U99">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.0962029010915226</v>
+        <v>0.1002827527069392</v>
       </c>
       <c r="W99">
-        <v>0.2221533269117038</v>
+        <v>0.2121533269117037</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3857373740638436</v>
+        <v>0.4020960413269413</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9460,13 +9460,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.254431378186516</v>
+        <v>0.2444533618305369</v>
       </c>
       <c r="C100">
-        <v>-1497.589519133985</v>
+        <v>-1482.06459235484</v>
       </c>
       <c r="D100">
-        <v>313.1534741986295</v>
+        <v>328.6784009777737</v>
       </c>
       <c r="E100">
         <v>873.3603470748446</v>
@@ -9493,37 +9493,37 @@
         <v>174.925</v>
       </c>
       <c r="M100">
-        <v>458.1571877611565</v>
+        <v>439.5177578278304</v>
       </c>
       <c r="N100">
-        <v>-283.2321877611566</v>
+        <v>-264.5927578278304</v>
       </c>
       <c r="O100">
-        <v>-70.63810762763245</v>
+        <v>-65.98943380226092</v>
       </c>
       <c r="P100">
-        <v>-212.5940801335241</v>
+        <v>-198.6033240255695</v>
       </c>
       <c r="Q100">
-        <v>-90.39408013352414</v>
+        <v>-76.40332402556953</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.824232554108167</v>
+        <v>1.81533173630921</v>
       </c>
       <c r="T100">
-        <v>41.04593949416302</v>
+        <v>40.86678374848061</v>
       </c>
       <c r="U100">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.09522123883548667</v>
+        <v>0.0992594593119704</v>
       </c>
       <c r="W100">
-        <v>0.2223946194942374</v>
+        <v>0.2123946194942374</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3818012784101309</v>
+        <v>0.3979930204970745</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9542,13 +9542,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.256431378186516</v>
+        <v>0.2463533618305369</v>
       </c>
       <c r="C101">
-        <v>-1519.582819699944</v>
+        <v>-1504.198248254919</v>
       </c>
       <c r="D101">
-        <v>310.1800000952475</v>
+        <v>325.5645715402725</v>
       </c>
       <c r="E101">
         <v>892.3801735374225</v>
@@ -9575,37 +9575,37 @@
         <v>174.925</v>
       </c>
       <c r="M101">
-        <v>462.8322611056582</v>
+        <v>444.0026329077062</v>
       </c>
       <c r="N101">
-        <v>-287.9072611056582</v>
+        <v>-269.0776329077063</v>
       </c>
       <c r="O101">
-        <v>-71.80407091975117</v>
+        <v>-67.10796164718195</v>
       </c>
       <c r="P101">
-        <v>-216.1031901859071</v>
+        <v>-201.9696712605243</v>
       </c>
       <c r="Q101">
-        <v>-93.90319018590708</v>
+        <v>-79.76967126052435</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>3.602665108216334</v>
+        <v>3.58486347261842</v>
       </c>
       <c r="T101">
-        <v>82.09187898832603</v>
+        <v>81.73356749696121</v>
       </c>
       <c r="U101">
-        <v>0.2458</v>
+        <v>0.2358</v>
       </c>
       <c r="V101">
-        <v>0.0942594081401787</v>
+        <v>0.09825683851083938</v>
       </c>
       <c r="W101">
-        <v>0.2226310374791441</v>
+        <v>0.2126310374791441</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.3779446998403316</v>
+        <v>0.3939728889769021</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/luxembourg/luxembourg_chemical_basic.xlsx
+++ b/research/traditional_assets/database/data/luxembourg/luxembourg_chemical_basic.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08500419409238885</v>
+        <v>0.08482597063232243</v>
       </c>
       <c r="C2">
-        <v>1718.661332056717</v>
+        <v>1707.247319783937</v>
       </c>
       <c r="D2">
-        <v>1665.461332056717</v>
+        <v>1673.067146246515</v>
       </c>
       <c r="E2">
-        <v>-990.5826462577693</v>
+        <v>-971.5628197951916</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>19.01982646257769</v>
       </c>
       <c r="G2">
         <v>53.2</v>
@@ -1457,28 +1457,28 @@
         <v>174.925</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.9566972710676581</v>
       </c>
       <c r="N2">
-        <v>174.925</v>
+        <v>173.9683027289323</v>
       </c>
       <c r="O2">
-        <v>43.62629499999999</v>
+        <v>43.38769470059572</v>
       </c>
       <c r="P2">
-        <v>131.298705</v>
+        <v>130.5806080283366</v>
       </c>
       <c r="Q2">
-        <v>253.4987049999999</v>
+        <v>252.7806080283366</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08500419409238885</v>
+        <v>0.08530143316396205</v>
       </c>
       <c r="T2">
-        <v>0.9054086395470867</v>
+        <v>0.91227328323238</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>182.8425828002902</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08482597063232243</v>
+        <v>0.08464774717225602</v>
       </c>
       <c r="C3">
-        <v>1707.247319783937</v>
+        <v>1695.903094544909</v>
       </c>
       <c r="D3">
-        <v>1673.067146246515</v>
+        <v>1680.742747470064</v>
       </c>
       <c r="E3">
-        <v>-971.5628197951916</v>
+        <v>-952.5429933326139</v>
       </c>
       <c r="F3">
-        <v>19.01982646257769</v>
+        <v>38.03965292515539</v>
       </c>
       <c r="G3">
         <v>53.2</v>
@@ -1539,28 +1539,28 @@
         <v>174.925</v>
       </c>
       <c r="M3">
-        <v>0.9566972710676581</v>
+        <v>1.913394542135316</v>
       </c>
       <c r="N3">
-        <v>173.9683027289323</v>
+        <v>173.0116054578646</v>
       </c>
       <c r="O3">
-        <v>43.38769470059572</v>
+        <v>43.14909440119145</v>
       </c>
       <c r="P3">
-        <v>130.5806080283366</v>
+        <v>129.8625110566732</v>
       </c>
       <c r="Q3">
-        <v>252.7806080283366</v>
+        <v>252.0625110566732</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08530143316396205</v>
+        <v>0.08560473833903676</v>
       </c>
       <c r="T3">
-        <v>0.91227328323238</v>
+        <v>0.9192780216867611</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>182.8425828002902</v>
+        <v>91.42129140014511</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08464774717225602</v>
+        <v>0.08446952371218959</v>
       </c>
       <c r="C4">
-        <v>1695.903094544909</v>
+        <v>1684.629621261262</v>
       </c>
       <c r="D4">
-        <v>1680.742747470064</v>
+        <v>1688.489100648995</v>
       </c>
       <c r="E4">
-        <v>-952.5429933326139</v>
+        <v>-933.5231668700362</v>
       </c>
       <c r="F4">
-        <v>38.03965292515539</v>
+        <v>57.05947938773308</v>
       </c>
       <c r="G4">
         <v>53.2</v>
@@ -1621,28 +1621,28 @@
         <v>174.925</v>
       </c>
       <c r="M4">
-        <v>1.913394542135316</v>
+        <v>2.870091813202974</v>
       </c>
       <c r="N4">
-        <v>173.0116054578646</v>
+        <v>172.054908186797</v>
       </c>
       <c r="O4">
-        <v>43.14909440119145</v>
+        <v>42.91049410178717</v>
       </c>
       <c r="P4">
-        <v>129.8625110566732</v>
+        <v>129.1444140850098</v>
       </c>
       <c r="Q4">
-        <v>252.0625110566732</v>
+        <v>251.3444140850098</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08560473833903676</v>
+        <v>0.08591429722906144</v>
       </c>
       <c r="T4">
-        <v>0.9192780216867611</v>
+        <v>0.9264271877381395</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>91.42129140014511</v>
+        <v>60.94752760009673</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08446952371218959</v>
+        <v>0.08429130025212318</v>
       </c>
       <c r="C5">
-        <v>1684.629621261262</v>
+        <v>1673.427882725852</v>
       </c>
       <c r="D5">
-        <v>1688.489100648995</v>
+        <v>1696.307188576162</v>
       </c>
       <c r="E5">
-        <v>-933.5231668700362</v>
+        <v>-914.5033404074585</v>
       </c>
       <c r="F5">
-        <v>57.05947938773308</v>
+        <v>76.07930585031077</v>
       </c>
       <c r="G5">
         <v>53.2</v>
@@ -1703,28 +1703,28 @@
         <v>174.925</v>
       </c>
       <c r="M5">
-        <v>2.870091813202974</v>
+        <v>3.826789084270632</v>
       </c>
       <c r="N5">
-        <v>172.054908186797</v>
+        <v>171.0982109157293</v>
       </c>
       <c r="O5">
-        <v>42.91049410178717</v>
+        <v>42.67189380238289</v>
       </c>
       <c r="P5">
-        <v>129.1444140850098</v>
+        <v>128.4263171133464</v>
       </c>
       <c r="Q5">
-        <v>251.3444140850098</v>
+        <v>250.6263171133464</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08591429722906144</v>
+        <v>0.08623030526262832</v>
       </c>
       <c r="T5">
-        <v>0.9264271877381395</v>
+        <v>0.9337252947489219</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>60.94752760009673</v>
+        <v>45.71064570007255</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08429130025212318</v>
+        <v>0.08411307679205676</v>
       </c>
       <c r="C6">
-        <v>1673.427882725852</v>
+        <v>1662.298880018422</v>
       </c>
       <c r="D6">
-        <v>1696.307188576162</v>
+        <v>1704.19801233131</v>
       </c>
       <c r="E6">
-        <v>-914.5033404074585</v>
+        <v>-895.4835139448808</v>
       </c>
       <c r="F6">
-        <v>76.07930585031077</v>
+        <v>95.09913231288847</v>
       </c>
       <c r="G6">
         <v>53.2</v>
@@ -1785,28 +1785,28 @@
         <v>174.925</v>
       </c>
       <c r="M6">
-        <v>3.826789084270632</v>
+        <v>4.78348635533829</v>
       </c>
       <c r="N6">
-        <v>171.0982109157293</v>
+        <v>170.1415136446617</v>
       </c>
       <c r="O6">
-        <v>42.67189380238289</v>
+        <v>42.43329350297862</v>
       </c>
       <c r="P6">
-        <v>128.4263171133464</v>
+        <v>127.7082201416831</v>
       </c>
       <c r="Q6">
-        <v>250.6263171133464</v>
+        <v>249.908220141683</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08623030526262832</v>
+        <v>0.08655296609690186</v>
       </c>
       <c r="T6">
-        <v>0.9337252947489219</v>
+        <v>0.9411770461178258</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>45.71064570007255</v>
+        <v>36.56851656005804</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08411307679205676</v>
+        <v>0.08393485333199034</v>
       </c>
       <c r="C7">
-        <v>1662.298880018422</v>
+        <v>1651.243632932926</v>
       </c>
       <c r="D7">
-        <v>1704.19801233131</v>
+        <v>1712.162591708392</v>
       </c>
       <c r="E7">
-        <v>-895.4835139448808</v>
+        <v>-876.4636874823032</v>
       </c>
       <c r="F7">
-        <v>95.09913231288847</v>
+        <v>114.1189587754662</v>
       </c>
       <c r="G7">
         <v>53.2</v>
@@ -1867,28 +1867,28 @@
         <v>174.925</v>
       </c>
       <c r="M7">
-        <v>4.78348635533829</v>
+        <v>5.740183626405948</v>
       </c>
       <c r="N7">
-        <v>170.1415136446617</v>
+        <v>169.184816373594</v>
       </c>
       <c r="O7">
-        <v>42.43329350297862</v>
+        <v>42.19469320357435</v>
       </c>
       <c r="P7">
-        <v>127.7082201416831</v>
+        <v>126.9901231700197</v>
       </c>
       <c r="Q7">
-        <v>249.908220141683</v>
+        <v>249.1901231700197</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08655296609690186</v>
+        <v>0.08688249205530887</v>
       </c>
       <c r="T7">
-        <v>0.9411770461178258</v>
+        <v>0.9487873453881958</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>36.56851656005804</v>
+        <v>30.47376380004837</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08393485333199034</v>
+        <v>0.08375662987192395</v>
       </c>
       <c r="C8">
-        <v>1651.243632932926</v>
+        <v>1640.26318041688</v>
       </c>
       <c r="D8">
-        <v>1712.162591708392</v>
+        <v>1720.201965654924</v>
       </c>
       <c r="E8">
-        <v>-876.4636874823032</v>
+        <v>-857.4438610197254</v>
       </c>
       <c r="F8">
-        <v>114.1189587754662</v>
+        <v>133.1387852380439</v>
       </c>
       <c r="G8">
         <v>53.2</v>
@@ -1949,28 +1949,28 @@
         <v>174.925</v>
       </c>
       <c r="M8">
-        <v>5.740183626405948</v>
+        <v>6.696880897473607</v>
       </c>
       <c r="N8">
-        <v>169.184816373594</v>
+        <v>168.2281191025263</v>
       </c>
       <c r="O8">
-        <v>42.19469320357435</v>
+        <v>41.95609290417007</v>
       </c>
       <c r="P8">
-        <v>126.9901231700197</v>
+        <v>126.2720261983563</v>
       </c>
       <c r="Q8">
-        <v>249.1901231700197</v>
+        <v>248.4720261983562</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08688249205530887</v>
+        <v>0.0872191045934666</v>
       </c>
       <c r="T8">
-        <v>0.9487873453881958</v>
+        <v>0.9565613070084664</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>30.47376380004837</v>
+        <v>26.12036897147003</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08375662987192393</v>
+        <v>0.08357840641185751</v>
       </c>
       <c r="C9">
-        <v>1640.263180416881</v>
+        <v>1629.358581023168</v>
       </c>
       <c r="D9">
-        <v>1720.201965654925</v>
+        <v>1728.31719272379</v>
       </c>
       <c r="E9">
-        <v>-857.4438610197254</v>
+        <v>-838.4240345571477</v>
       </c>
       <c r="F9">
-        <v>133.1387852380439</v>
+        <v>152.1586117006215</v>
       </c>
       <c r="G9">
         <v>53.2</v>
@@ -2031,28 +2031,28 @@
         <v>174.925</v>
       </c>
       <c r="M9">
-        <v>6.696880897473608</v>
+        <v>7.653578168541265</v>
       </c>
       <c r="N9">
-        <v>168.2281191025263</v>
+        <v>167.2714218314587</v>
       </c>
       <c r="O9">
-        <v>41.95609290417007</v>
+        <v>41.7174926047658</v>
       </c>
       <c r="P9">
-        <v>126.2720261983563</v>
+        <v>125.5539292266929</v>
       </c>
       <c r="Q9">
-        <v>248.4720261983562</v>
+        <v>247.7539292266929</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.0872191045934666</v>
+        <v>0.08756303479549729</v>
       </c>
       <c r="T9">
-        <v>0.9565613070084664</v>
+        <v>0.9645042677943949</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>26.12036897147002</v>
+        <v>22.85532285003628</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08357840641185751</v>
+        <v>0.08340018295179111</v>
       </c>
       <c r="C10">
-        <v>1629.358581023168</v>
+        <v>1618.53091337467</v>
       </c>
       <c r="D10">
-        <v>1728.31719272379</v>
+        <v>1736.509351537869</v>
       </c>
       <c r="E10">
-        <v>-838.4240345571477</v>
+        <v>-819.4042080945701</v>
       </c>
       <c r="F10">
-        <v>152.1586117006215</v>
+        <v>171.1784381631992</v>
       </c>
       <c r="G10">
         <v>53.2</v>
@@ -2113,28 +2113,28 @@
         <v>174.925</v>
       </c>
       <c r="M10">
-        <v>7.653578168541265</v>
+        <v>8.610275439608923</v>
       </c>
       <c r="N10">
-        <v>167.2714218314587</v>
+        <v>166.314724560391</v>
       </c>
       <c r="O10">
-        <v>41.7174926047658</v>
+        <v>41.47889230536153</v>
       </c>
       <c r="P10">
-        <v>125.5539292266929</v>
+        <v>124.8358322550295</v>
       </c>
       <c r="Q10">
-        <v>247.7539292266929</v>
+        <v>247.0358322550295</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08756303479549729</v>
+        <v>0.08791452390306714</v>
       </c>
       <c r="T10">
-        <v>0.9645042677943949</v>
+        <v>0.9726217991470472</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>22.85532285003628</v>
+        <v>20.31584253336558</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08340018295179111</v>
+        <v>0.08322195949172469</v>
       </c>
       <c r="C11">
-        <v>1618.53091337467</v>
+        <v>1607.781276642194</v>
       </c>
       <c r="D11">
-        <v>1736.509351537869</v>
+        <v>1744.779541267971</v>
       </c>
       <c r="E11">
-        <v>-819.4042080945701</v>
+        <v>-800.3843816319924</v>
       </c>
       <c r="F11">
-        <v>171.1784381631992</v>
+        <v>190.1982646257769</v>
       </c>
       <c r="G11">
         <v>53.2</v>
@@ -2195,28 +2195,28 @@
         <v>174.925</v>
       </c>
       <c r="M11">
-        <v>8.610275439608923</v>
+        <v>9.566972710676581</v>
       </c>
       <c r="N11">
-        <v>166.314724560391</v>
+        <v>165.3580272893234</v>
       </c>
       <c r="O11">
-        <v>41.47889230536153</v>
+        <v>41.24029200595726</v>
       </c>
       <c r="P11">
-        <v>124.8358322550295</v>
+        <v>124.1177352833661</v>
       </c>
       <c r="Q11">
-        <v>247.0358322550295</v>
+        <v>246.3177352833661</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08791452390306714</v>
+        <v>0.08827382387969408</v>
       </c>
       <c r="T11">
-        <v>0.9726217991470472</v>
+        <v>0.9809197200853137</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>20.31584253336558</v>
+        <v>18.28425828002902</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08322195949172469</v>
+        <v>0.08304373603165827</v>
       </c>
       <c r="C12">
-        <v>1607.781276642194</v>
+        <v>1597.110791036118</v>
       </c>
       <c r="D12">
-        <v>1744.779541267971</v>
+        <v>1753.128882124473</v>
       </c>
       <c r="E12">
-        <v>-800.3843816319924</v>
+        <v>-781.3645551694146</v>
       </c>
       <c r="F12">
-        <v>190.1982646257769</v>
+        <v>209.2180910883546</v>
       </c>
       <c r="G12">
         <v>53.2</v>
@@ -2277,28 +2277,28 @@
         <v>174.925</v>
       </c>
       <c r="M12">
-        <v>9.566972710676581</v>
+        <v>10.52366998174424</v>
       </c>
       <c r="N12">
-        <v>165.3580272893234</v>
+        <v>164.4013300182557</v>
       </c>
       <c r="O12">
-        <v>41.24029200595726</v>
+        <v>41.00169170655298</v>
       </c>
       <c r="P12">
-        <v>124.1177352833661</v>
+        <v>123.3996383117027</v>
       </c>
       <c r="Q12">
-        <v>246.3177352833661</v>
+        <v>245.5996383117027</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08827382387969408</v>
+        <v>0.08864119801309917</v>
       </c>
       <c r="T12">
-        <v>0.9809197200853137</v>
+        <v>0.9894041111570246</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>18.28425828002902</v>
+        <v>16.62205298184456</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08304373603165827</v>
+        <v>0.08286551257159183</v>
       </c>
       <c r="C13">
-        <v>1597.110791036118</v>
+        <v>1586.520598312211</v>
       </c>
       <c r="D13">
-        <v>1753.128882124473</v>
+        <v>1761.558515863144</v>
       </c>
       <c r="E13">
-        <v>-781.3645551694146</v>
+        <v>-762.344728706837</v>
       </c>
       <c r="F13">
-        <v>209.2180910883546</v>
+        <v>228.2379175509323</v>
       </c>
       <c r="G13">
         <v>53.2</v>
@@ -2359,28 +2359,28 @@
         <v>174.925</v>
       </c>
       <c r="M13">
-        <v>10.52366998174424</v>
+        <v>11.4803672528119</v>
       </c>
       <c r="N13">
-        <v>164.4013300182557</v>
+        <v>163.4446327471881</v>
       </c>
       <c r="O13">
-        <v>41.00169170655298</v>
+        <v>40.7630914071487</v>
       </c>
       <c r="P13">
-        <v>123.3996383117027</v>
+        <v>122.6815413400394</v>
       </c>
       <c r="Q13">
-        <v>245.5996383117027</v>
+        <v>244.8815413400393</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08864119801309917</v>
+        <v>0.08901692155862709</v>
       </c>
       <c r="T13">
-        <v>0.9894041111570246</v>
+        <v>0.9980813292985471</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>16.62205298184456</v>
+        <v>15.23688190002418</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08286551257159183</v>
+        <v>0.08268728911152542</v>
       </c>
       <c r="C14">
-        <v>1586.520598312211</v>
+        <v>1576.011862292126</v>
       </c>
       <c r="D14">
-        <v>1761.558515863144</v>
+        <v>1770.069606305636</v>
       </c>
       <c r="E14">
-        <v>-762.344728706837</v>
+        <v>-743.3249022442592</v>
       </c>
       <c r="F14">
-        <v>228.2379175509323</v>
+        <v>247.25774401351</v>
       </c>
       <c r="G14">
         <v>53.2</v>
@@ -2441,28 +2441,28 @@
         <v>174.925</v>
       </c>
       <c r="M14">
-        <v>11.4803672528119</v>
+        <v>12.43706452387956</v>
       </c>
       <c r="N14">
-        <v>163.4446327471881</v>
+        <v>162.4879354761204</v>
       </c>
       <c r="O14">
-        <v>40.7630914071487</v>
+        <v>40.52449110774443</v>
       </c>
       <c r="P14">
-        <v>122.6815413400394</v>
+        <v>121.963444368376</v>
       </c>
       <c r="Q14">
-        <v>244.8815413400393</v>
+        <v>244.163444368376</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08901692155862709</v>
+        <v>0.08940128242704071</v>
       </c>
       <c r="T14">
-        <v>0.9980813292985471</v>
+        <v>1.006958023719185</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>15.23688190002418</v>
+        <v>14.06481406156079</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08268728911152542</v>
+        <v>0.08250906565145902</v>
       </c>
       <c r="C15">
-        <v>1576.011862292126</v>
+        <v>1565.585769399055</v>
       </c>
       <c r="D15">
-        <v>1770.069606305636</v>
+        <v>1778.663339875143</v>
       </c>
       <c r="E15">
-        <v>-743.3249022442592</v>
+        <v>-724.3050757816816</v>
       </c>
       <c r="F15">
-        <v>247.25774401351</v>
+        <v>266.2775704760878</v>
       </c>
       <c r="G15">
         <v>53.2</v>
@@ -2523,28 +2523,28 @@
         <v>174.925</v>
       </c>
       <c r="M15">
-        <v>12.43706452387956</v>
+        <v>13.39376179494722</v>
       </c>
       <c r="N15">
-        <v>162.4879354761204</v>
+        <v>161.5312382050527</v>
       </c>
       <c r="O15">
-        <v>40.52449110774443</v>
+        <v>40.28589080834016</v>
       </c>
       <c r="P15">
-        <v>121.963444368376</v>
+        <v>121.2453473967126</v>
       </c>
       <c r="Q15">
-        <v>244.163444368376</v>
+        <v>243.4453473967126</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08940128242704071</v>
+        <v>0.08979458192030118</v>
       </c>
       <c r="T15">
-        <v>1.006958023719185</v>
+        <v>1.016041152893792</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>14.06481406156079</v>
+        <v>13.06018448573501</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08250906565145902</v>
+        <v>0.08249972719139259</v>
       </c>
       <c r="C16">
-        <v>1565.585769399055</v>
+        <v>1547.018534218272</v>
       </c>
       <c r="D16">
-        <v>1778.663339875143</v>
+        <v>1779.115931156937</v>
       </c>
       <c r="E16">
-        <v>-724.3050757816816</v>
+        <v>-705.2852493191039</v>
       </c>
       <c r="F16">
-        <v>266.2775704760878</v>
+        <v>285.2973969386654</v>
       </c>
       <c r="G16">
         <v>53.2</v>
@@ -2605,45 +2605,45 @@
         <v>174.925</v>
       </c>
       <c r="M16">
-        <v>13.39376179494722</v>
+        <v>14.77840516142287</v>
       </c>
       <c r="N16">
-        <v>161.5312382050527</v>
+        <v>160.1465948385771</v>
       </c>
       <c r="O16">
-        <v>40.28589080834016</v>
+        <v>39.94056075274112</v>
       </c>
       <c r="P16">
-        <v>121.2453473967126</v>
+        <v>120.206034085836</v>
       </c>
       <c r="Q16">
-        <v>243.4453473967126</v>
+        <v>242.4060340858359</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08979458192030118</v>
+        <v>0.0901971355192854</v>
       </c>
       <c r="T16">
-        <v>1.016041152893792</v>
+        <v>1.025338002754859</v>
       </c>
       <c r="U16">
-        <v>0.0503</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V16">
         <v>0.2494</v>
       </c>
       <c r="W16">
-        <v>0.03775518</v>
+        <v>0.03888108</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y16">
-        <v>13.06018448573501</v>
+        <v>11.83652756094543</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08249972719139259</v>
+        <v>0.08233276273132617</v>
       </c>
       <c r="C17">
-        <v>1547.018534218272</v>
+        <v>1536.129741617704</v>
       </c>
       <c r="D17">
-        <v>1779.115931156937</v>
+        <v>1787.246965018947</v>
       </c>
       <c r="E17">
-        <v>-705.285249319104</v>
+        <v>-686.2654228565261</v>
       </c>
       <c r="F17">
-        <v>285.2973969386654</v>
+        <v>304.3172234012431</v>
       </c>
       <c r="G17">
         <v>53.2</v>
@@ -2687,28 +2687,28 @@
         <v>174.925</v>
       </c>
       <c r="M17">
-        <v>14.77840516142287</v>
+        <v>15.76363217218439</v>
       </c>
       <c r="N17">
-        <v>160.1465948385771</v>
+        <v>159.1613678278156</v>
       </c>
       <c r="O17">
-        <v>39.94056075274112</v>
+        <v>39.6948451362572</v>
       </c>
       <c r="P17">
-        <v>120.206034085836</v>
+        <v>119.4665226915584</v>
       </c>
       <c r="Q17">
-        <v>242.4060340858359</v>
+        <v>241.6665226915583</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.0901971355192854</v>
+        <v>0.09060927372776925</v>
       </c>
       <c r="T17">
-        <v>1.025338002754859</v>
+        <v>1.034856206184047</v>
       </c>
       <c r="U17">
         <v>0.05180000000000001</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>11.83652756094543</v>
+        <v>11.09674458838634</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08233276273132617</v>
+        <v>0.08216579827125975</v>
       </c>
       <c r="C18">
-        <v>1536.129741617704</v>
+        <v>1525.315612230545</v>
       </c>
       <c r="D18">
-        <v>1787.246965018947</v>
+        <v>1795.452662094366</v>
       </c>
       <c r="E18">
-        <v>-686.2654228565261</v>
+        <v>-667.2455963939485</v>
       </c>
       <c r="F18">
-        <v>304.3172234012431</v>
+        <v>323.3370498638208</v>
       </c>
       <c r="G18">
         <v>53.2</v>
@@ -2769,28 +2769,28 @@
         <v>174.925</v>
       </c>
       <c r="M18">
-        <v>15.76363217218439</v>
+        <v>16.74885918294592</v>
       </c>
       <c r="N18">
-        <v>159.1613678278156</v>
+        <v>158.176140817054</v>
       </c>
       <c r="O18">
-        <v>39.6948451362572</v>
+        <v>39.44912951977328</v>
       </c>
       <c r="P18">
-        <v>119.4665226915584</v>
+        <v>118.7270112972808</v>
       </c>
       <c r="Q18">
-        <v>241.6665226915583</v>
+        <v>240.9270112972807</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09060927372776925</v>
+        <v>0.09103134297742138</v>
       </c>
       <c r="T18">
-        <v>1.034856206184047</v>
+        <v>1.044603763912734</v>
       </c>
       <c r="U18">
         <v>0.05180000000000001</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.09674458838634</v>
+        <v>10.44399490671655</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08216579827125975</v>
+        <v>0.08199883381119333</v>
       </c>
       <c r="C19">
-        <v>1525.315612230545</v>
+        <v>1514.577179192545</v>
       </c>
       <c r="D19">
-        <v>1795.452662094366</v>
+        <v>1803.734055518943</v>
       </c>
       <c r="E19">
-        <v>-667.2455963939485</v>
+        <v>-648.2257699313707</v>
       </c>
       <c r="F19">
-        <v>323.3370498638208</v>
+        <v>342.3568763263985</v>
       </c>
       <c r="G19">
         <v>53.2</v>
@@ -2851,28 +2851,28 @@
         <v>174.925</v>
       </c>
       <c r="M19">
-        <v>16.74885918294592</v>
+        <v>17.73408619370745</v>
       </c>
       <c r="N19">
-        <v>158.176140817054</v>
+        <v>157.1909138062925</v>
       </c>
       <c r="O19">
-        <v>39.44912951977328</v>
+        <v>39.20341390328935</v>
       </c>
       <c r="P19">
-        <v>118.7270112972808</v>
+        <v>117.9874999030032</v>
       </c>
       <c r="Q19">
-        <v>240.9270112972807</v>
+        <v>240.1874999030032</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09103134297742138</v>
+        <v>0.09146370659901626</v>
       </c>
       <c r="T19">
-        <v>1.044603763912734</v>
+        <v>1.054589066951877</v>
       </c>
       <c r="U19">
         <v>0.05180000000000001</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>10.44399490671655</v>
+        <v>9.863772967454521</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08199883381119334</v>
+        <v>0.08207431315112691</v>
       </c>
       <c r="C20">
-        <v>1514.577179192544</v>
+        <v>1491.804155381775</v>
       </c>
       <c r="D20">
-        <v>1803.734055518943</v>
+        <v>1799.980858170752</v>
       </c>
       <c r="E20">
-        <v>-648.2257699313708</v>
+        <v>-629.2059434687931</v>
       </c>
       <c r="F20">
-        <v>342.3568763263985</v>
+        <v>361.3767027889762</v>
       </c>
       <c r="G20">
         <v>53.2</v>
@@ -2933,45 +2933,45 @@
         <v>174.925</v>
       </c>
       <c r="M20">
-        <v>17.73408619370744</v>
+        <v>19.33365359921023</v>
       </c>
       <c r="N20">
-        <v>157.1909138062925</v>
+        <v>155.5913464007897</v>
       </c>
       <c r="O20">
-        <v>39.20341390328935</v>
+        <v>38.80448179235696</v>
       </c>
       <c r="P20">
-        <v>117.9874999030032</v>
+        <v>116.7868646084328</v>
       </c>
       <c r="Q20">
-        <v>240.1874999030032</v>
+        <v>238.9868646084327</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09146370659901626</v>
+        <v>0.09190674586558878</v>
       </c>
       <c r="T20">
-        <v>1.054589066951877</v>
+        <v>1.064820920683344</v>
       </c>
       <c r="U20">
-        <v>0.05180000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V20">
         <v>0.2494</v>
       </c>
       <c r="W20">
-        <v>0.03888108</v>
+        <v>0.0401571</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>9.863772967454523</v>
+        <v>9.047694948209147</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08207431315112691</v>
+        <v>0.08192010889106051</v>
       </c>
       <c r="C21">
-        <v>1491.804155381775</v>
+        <v>1480.468821709766</v>
       </c>
       <c r="D21">
-        <v>1799.980858170752</v>
+        <v>1807.66535096132</v>
       </c>
       <c r="E21">
-        <v>-629.2059434687931</v>
+        <v>-610.1861170062155</v>
       </c>
       <c r="F21">
-        <v>361.3767027889762</v>
+        <v>380.3965292515539</v>
       </c>
       <c r="G21">
         <v>53.2</v>
@@ -3015,28 +3015,28 @@
         <v>174.925</v>
       </c>
       <c r="M21">
-        <v>19.33365359921023</v>
+        <v>20.35121431495813</v>
       </c>
       <c r="N21">
-        <v>155.5913464007897</v>
+        <v>154.5737856850418</v>
       </c>
       <c r="O21">
-        <v>38.80448179235696</v>
+        <v>38.55070214984944</v>
       </c>
       <c r="P21">
-        <v>116.7868646084328</v>
+        <v>116.0230835351924</v>
       </c>
       <c r="Q21">
-        <v>238.9868646084327</v>
+        <v>238.2230835351924</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09190674586558878</v>
+        <v>0.09236086111382563</v>
       </c>
       <c r="T21">
-        <v>1.064820920683344</v>
+        <v>1.075308570758098</v>
       </c>
       <c r="U21">
         <v>0.05350000000000001</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>9.047694948209147</v>
+        <v>8.595310200798689</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08192010889106051</v>
+        <v>0.08176590463099409</v>
       </c>
       <c r="C22">
-        <v>1480.468821709766</v>
+        <v>1469.199382753151</v>
       </c>
       <c r="D22">
-        <v>1807.66535096132</v>
+        <v>1815.415738467283</v>
       </c>
       <c r="E22">
-        <v>-610.1861170062155</v>
+        <v>-591.1662905436376</v>
       </c>
       <c r="F22">
-        <v>380.3965292515539</v>
+        <v>399.4163557141316</v>
       </c>
       <c r="G22">
         <v>53.2</v>
@@ -3097,28 +3097,28 @@
         <v>174.925</v>
       </c>
       <c r="M22">
-        <v>20.35121431495813</v>
+        <v>21.36877503070604</v>
       </c>
       <c r="N22">
-        <v>154.5737856850418</v>
+        <v>153.5562249692939</v>
       </c>
       <c r="O22">
-        <v>38.55070214984944</v>
+        <v>38.2969225073419</v>
       </c>
       <c r="P22">
-        <v>116.0230835351924</v>
+        <v>115.259302461952</v>
       </c>
       <c r="Q22">
-        <v>238.2230835351924</v>
+        <v>237.459302461952</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09236086111382563</v>
+        <v>0.09282647295062542</v>
       </c>
       <c r="T22">
-        <v>1.075308570758098</v>
+        <v>1.086061730961326</v>
       </c>
       <c r="U22">
         <v>0.05350000000000001</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.595310200798689</v>
+        <v>8.186009715046369</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08176590463099409</v>
+        <v>0.08161170037092767</v>
       </c>
       <c r="C23">
-        <v>1469.199382753151</v>
+        <v>1457.996689734774</v>
       </c>
       <c r="D23">
-        <v>1815.415738467283</v>
+        <v>1823.232871911483</v>
       </c>
       <c r="E23">
-        <v>-591.1662905436377</v>
+        <v>-572.14646408106</v>
       </c>
       <c r="F23">
-        <v>399.4163557141316</v>
+        <v>418.4361821767093</v>
       </c>
       <c r="G23">
         <v>53.2</v>
@@ -3179,28 +3179,28 @@
         <v>174.925</v>
       </c>
       <c r="M23">
-        <v>21.36877503070604</v>
+        <v>22.38633574645395</v>
       </c>
       <c r="N23">
-        <v>153.5562249692939</v>
+        <v>152.538664253546</v>
       </c>
       <c r="O23">
-        <v>38.2969225073419</v>
+        <v>38.04314286483438</v>
       </c>
       <c r="P23">
-        <v>115.259302461952</v>
+        <v>114.4955213887116</v>
       </c>
       <c r="Q23">
-        <v>237.459302461952</v>
+        <v>236.6955213887116</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09282647295062542</v>
+        <v>0.09330402355247136</v>
       </c>
       <c r="T23">
-        <v>1.086061730961326</v>
+        <v>1.097090613221048</v>
       </c>
       <c r="U23">
         <v>0.05350000000000001</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.186009715046371</v>
+        <v>7.813918364362444</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08161170037092767</v>
+        <v>0.08159560651086124</v>
       </c>
       <c r="C24">
-        <v>1457.996689734774</v>
+        <v>1439.796596685574</v>
       </c>
       <c r="D24">
-        <v>1823.232871911483</v>
+        <v>1824.052605324861</v>
       </c>
       <c r="E24">
-        <v>-572.14646408106</v>
+        <v>-553.1266376184824</v>
       </c>
       <c r="F24">
-        <v>418.4361821767093</v>
+        <v>437.4560086392869</v>
       </c>
       <c r="G24">
         <v>53.2</v>
@@ -3261,45 +3261,45 @@
         <v>174.925</v>
       </c>
       <c r="M24">
-        <v>22.38633574645395</v>
+        <v>23.75386126911328</v>
       </c>
       <c r="N24">
-        <v>152.538664253546</v>
+        <v>151.1711387308867</v>
       </c>
       <c r="O24">
-        <v>38.04314286483438</v>
+        <v>37.70208199948313</v>
       </c>
       <c r="P24">
-        <v>114.4955213887116</v>
+        <v>113.4690567314035</v>
       </c>
       <c r="Q24">
-        <v>236.6955213887116</v>
+        <v>235.6690567314035</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09330402355247136</v>
+        <v>0.09379397806605357</v>
       </c>
       <c r="T24">
-        <v>1.097090613221048</v>
+        <v>1.108405959955048</v>
       </c>
       <c r="U24">
-        <v>0.05350000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V24">
         <v>0.2494</v>
       </c>
       <c r="W24">
-        <v>0.0401571</v>
+        <v>0.04075758</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y24">
-        <v>7.813918364362444</v>
+        <v>7.364065909884376</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08159560651086124</v>
+        <v>0.08144740705079483</v>
       </c>
       <c r="C25">
-        <v>1439.796596685574</v>
+        <v>1428.360031772895</v>
       </c>
       <c r="D25">
-        <v>1824.052605324861</v>
+        <v>1831.63586687476</v>
       </c>
       <c r="E25">
-        <v>-553.1266376184824</v>
+        <v>-534.1068111559046</v>
       </c>
       <c r="F25">
-        <v>437.4560086392869</v>
+        <v>456.4758351018647</v>
       </c>
       <c r="G25">
         <v>53.2</v>
@@ -3343,28 +3343,28 @@
         <v>174.925</v>
       </c>
       <c r="M25">
-        <v>23.75386126911328</v>
+        <v>24.78663784603125</v>
       </c>
       <c r="N25">
-        <v>151.1711387308867</v>
+        <v>150.1383621539687</v>
       </c>
       <c r="O25">
-        <v>37.70208199948313</v>
+        <v>37.4445075211998</v>
       </c>
       <c r="P25">
-        <v>113.4690567314035</v>
+        <v>112.6938546327689</v>
       </c>
       <c r="Q25">
-        <v>235.6690567314035</v>
+        <v>234.8938546327689</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09379397806605357</v>
+        <v>0.09429682611946688</v>
       </c>
       <c r="T25">
-        <v>1.108405959955048</v>
+        <v>1.120019078971521</v>
       </c>
       <c r="U25">
         <v>0.05430000000000001</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>7.364065909884376</v>
+        <v>7.05722983030586</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08144740705079483</v>
+        <v>0.08129920759072841</v>
       </c>
       <c r="C26">
-        <v>1428.360031772895</v>
+        <v>1416.986782936462</v>
       </c>
       <c r="D26">
-        <v>1831.63586687476</v>
+        <v>1839.282444500904</v>
       </c>
       <c r="E26">
-        <v>-534.1068111559047</v>
+        <v>-515.0869846933269</v>
       </c>
       <c r="F26">
-        <v>456.4758351018646</v>
+        <v>475.4956615644423</v>
       </c>
       <c r="G26">
         <v>53.2</v>
@@ -3425,28 +3425,28 @@
         <v>174.925</v>
       </c>
       <c r="M26">
-        <v>24.78663784603125</v>
+        <v>25.81941442294922</v>
       </c>
       <c r="N26">
-        <v>150.1383621539687</v>
+        <v>149.1055855770507</v>
       </c>
       <c r="O26">
-        <v>37.4445075211998</v>
+        <v>37.18693304291645</v>
       </c>
       <c r="P26">
-        <v>112.6938546327689</v>
+        <v>111.9186525341343</v>
       </c>
       <c r="Q26">
-        <v>234.8938546327689</v>
+        <v>234.1186525341343</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09429682611946688</v>
+        <v>0.09481308345430454</v>
       </c>
       <c r="T26">
-        <v>1.120019078971521</v>
+        <v>1.131941881161768</v>
       </c>
       <c r="U26">
         <v>0.05430000000000001</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.057229830305861</v>
+        <v>6.774940637093626</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08129920759072841</v>
+        <v>0.08115100813066198</v>
       </c>
       <c r="C27">
-        <v>1416.986782936462</v>
+        <v>1405.677646482418</v>
       </c>
       <c r="D27">
-        <v>1839.282444500904</v>
+        <v>1846.993134509438</v>
       </c>
       <c r="E27">
-        <v>-515.0869846933269</v>
+        <v>-496.0671582307492</v>
       </c>
       <c r="F27">
-        <v>475.4956615644423</v>
+        <v>494.5154880270201</v>
       </c>
       <c r="G27">
         <v>53.2</v>
@@ -3507,28 +3507,28 @@
         <v>174.925</v>
       </c>
       <c r="M27">
-        <v>25.81941442294922</v>
+        <v>26.85219099986719</v>
       </c>
       <c r="N27">
-        <v>149.1055855770507</v>
+        <v>148.0728090001328</v>
       </c>
       <c r="O27">
-        <v>37.18693304291645</v>
+        <v>36.92935856463311</v>
       </c>
       <c r="P27">
-        <v>111.9186525341343</v>
+        <v>111.1434504354997</v>
       </c>
       <c r="Q27">
-        <v>234.1186525341343</v>
+        <v>233.3434504354996</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09481308345430454</v>
+        <v>0.09534329369008376</v>
       </c>
       <c r="T27">
-        <v>1.131941881161768</v>
+        <v>1.144186921249048</v>
       </c>
       <c r="U27">
         <v>0.05430000000000001</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>6.774940637093626</v>
+        <v>6.514365997205409</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08115100813066198</v>
+        <v>0.08100280867059556</v>
       </c>
       <c r="C28">
-        <v>1405.677646482418</v>
+        <v>1394.433432126306</v>
       </c>
       <c r="D28">
-        <v>1846.993134509438</v>
+        <v>1854.768746615904</v>
       </c>
       <c r="E28">
-        <v>-496.0671582307492</v>
+        <v>-477.0473317681715</v>
       </c>
       <c r="F28">
-        <v>494.5154880270201</v>
+        <v>513.5353144895978</v>
       </c>
       <c r="G28">
         <v>53.2</v>
@@ -3589,28 +3589,28 @@
         <v>174.925</v>
       </c>
       <c r="M28">
-        <v>26.85219099986719</v>
+        <v>27.88496757678517</v>
       </c>
       <c r="N28">
-        <v>148.0728090001328</v>
+        <v>147.0400324232148</v>
       </c>
       <c r="O28">
-        <v>36.92935856463311</v>
+        <v>36.67178408634977</v>
       </c>
       <c r="P28">
-        <v>111.1434504354997</v>
+        <v>110.368248336865</v>
       </c>
       <c r="Q28">
-        <v>233.3434504354996</v>
+        <v>232.568248336865</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09534329369008376</v>
+        <v>0.09588803023369255</v>
       </c>
       <c r="T28">
-        <v>1.144186921249048</v>
+        <v>1.156767441886664</v>
       </c>
       <c r="U28">
         <v>0.05430000000000001</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.514365997205409</v>
+        <v>6.273093182494097</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08100280867059556</v>
+        <v>0.08106477721052915</v>
       </c>
       <c r="C29">
-        <v>1394.433432126306</v>
+        <v>1372.154339046047</v>
       </c>
       <c r="D29">
-        <v>1854.768746615904</v>
+        <v>1851.509479998222</v>
       </c>
       <c r="E29">
-        <v>-477.0473317681715</v>
+        <v>-458.0275053055938</v>
       </c>
       <c r="F29">
-        <v>513.5353144895978</v>
+        <v>532.5551409521755</v>
       </c>
       <c r="G29">
         <v>53.2</v>
@@ -3671,45 +3671,45 @@
         <v>174.925</v>
       </c>
       <c r="M29">
-        <v>27.88496757678517</v>
+        <v>29.45029929465531</v>
       </c>
       <c r="N29">
-        <v>147.0400324232148</v>
+        <v>145.4747007053446</v>
       </c>
       <c r="O29">
-        <v>36.67178408634977</v>
+        <v>36.28139035591295</v>
       </c>
       <c r="P29">
-        <v>110.368248336865</v>
+        <v>109.1933103494317</v>
       </c>
       <c r="Q29">
-        <v>232.568248336865</v>
+        <v>231.3933103494317</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09588803023369255</v>
+        <v>0.09644789834795717</v>
       </c>
       <c r="T29">
-        <v>1.156767441886664</v>
+        <v>1.169697421430881</v>
       </c>
       <c r="U29">
-        <v>0.05430000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V29">
         <v>0.2494</v>
       </c>
       <c r="W29">
-        <v>0.04075758</v>
+        <v>0.04150818000000001</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y29">
-        <v>6.273093182494097</v>
+        <v>5.939667989443681</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08106477721052915</v>
+        <v>0.08092408375046274</v>
       </c>
       <c r="C30">
-        <v>1372.154339046047</v>
+        <v>1360.550941633616</v>
       </c>
       <c r="D30">
-        <v>1851.509479998222</v>
+        <v>1858.925909048369</v>
       </c>
       <c r="E30">
-        <v>-458.0275053055938</v>
+        <v>-439.0076788430162</v>
       </c>
       <c r="F30">
-        <v>532.5551409521755</v>
+        <v>551.5749674147531</v>
       </c>
       <c r="G30">
         <v>53.2</v>
@@ -3753,28 +3753,28 @@
         <v>174.925</v>
       </c>
       <c r="M30">
-        <v>29.45029929465531</v>
+        <v>30.50209569803585</v>
       </c>
       <c r="N30">
-        <v>145.4747007053446</v>
+        <v>144.4229043019641</v>
       </c>
       <c r="O30">
-        <v>36.28139035591295</v>
+        <v>36.01907233290985</v>
       </c>
       <c r="P30">
-        <v>109.1933103494317</v>
+        <v>108.4038319690543</v>
       </c>
       <c r="Q30">
-        <v>231.3933103494317</v>
+        <v>230.6038319690543</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09644789834795717</v>
+        <v>0.09702353739501794</v>
       </c>
       <c r="T30">
-        <v>1.169697421430881</v>
+        <v>1.182991625750992</v>
       </c>
       <c r="U30">
         <v>0.05530000000000001</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.939667989443681</v>
+        <v>5.734851851876658</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08092408375046273</v>
+        <v>0.08078339029039631</v>
       </c>
       <c r="C31">
-        <v>1360.550941633617</v>
+        <v>1349.007197848564</v>
       </c>
       <c r="D31">
-        <v>1858.92590904837</v>
+        <v>1866.401991725895</v>
       </c>
       <c r="E31">
-        <v>-439.0076788430162</v>
+        <v>-419.9878523804385</v>
       </c>
       <c r="F31">
-        <v>551.5749674147531</v>
+        <v>570.5947938773307</v>
       </c>
       <c r="G31">
         <v>53.2</v>
@@ -3835,28 +3835,28 @@
         <v>174.925</v>
       </c>
       <c r="M31">
-        <v>30.50209569803585</v>
+        <v>31.55389210141639</v>
       </c>
       <c r="N31">
-        <v>144.4229043019641</v>
+        <v>143.3711078985835</v>
       </c>
       <c r="O31">
-        <v>36.01907233290985</v>
+        <v>35.75675430990674</v>
       </c>
       <c r="P31">
-        <v>108.4038319690543</v>
+        <v>107.6143535886768</v>
       </c>
       <c r="Q31">
-        <v>230.6038319690543</v>
+        <v>229.8143535886768</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09702353739501793</v>
+        <v>0.09761562327199474</v>
       </c>
       <c r="T31">
-        <v>1.182991625750992</v>
+        <v>1.196665664480248</v>
       </c>
       <c r="U31">
         <v>0.05530000000000001</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.734851851876658</v>
+        <v>5.543690123480769</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08078339029039631</v>
+        <v>0.08064269683032989</v>
       </c>
       <c r="C32">
-        <v>1349.007197848564</v>
+        <v>1337.523830327999</v>
       </c>
       <c r="D32">
-        <v>1866.401991725895</v>
+        <v>1873.938450667908</v>
       </c>
       <c r="E32">
-        <v>-419.9878523804385</v>
+        <v>-400.9680259178608</v>
       </c>
       <c r="F32">
-        <v>570.5947938773307</v>
+        <v>589.6146203399085</v>
       </c>
       <c r="G32">
         <v>53.2</v>
@@ -3917,28 +3917,28 @@
         <v>174.925</v>
       </c>
       <c r="M32">
-        <v>31.55389210141639</v>
+        <v>32.60568850479694</v>
       </c>
       <c r="N32">
-        <v>143.3711078985835</v>
+        <v>142.319311495203</v>
       </c>
       <c r="O32">
-        <v>35.75675430990674</v>
+        <v>35.49443628690364</v>
       </c>
       <c r="P32">
-        <v>107.6143535886768</v>
+        <v>106.8248752082994</v>
       </c>
       <c r="Q32">
-        <v>229.8143535886768</v>
+        <v>229.0248752082994</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09761562327199474</v>
+        <v>0.09822487105844913</v>
       </c>
       <c r="T32">
-        <v>1.196665664480248</v>
+        <v>1.210736052158179</v>
       </c>
       <c r="U32">
         <v>0.05530000000000001</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.543690123480769</v>
+        <v>5.3648614098201</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08064269683032989</v>
+        <v>0.08050200337026348</v>
       </c>
       <c r="C33">
-        <v>1337.523830327999</v>
+        <v>1326.101573428275</v>
       </c>
       <c r="D33">
-        <v>1873.938450667908</v>
+        <v>1881.536020230761</v>
       </c>
       <c r="E33">
-        <v>-400.9680259178608</v>
+        <v>-381.9481994552831</v>
       </c>
       <c r="F33">
-        <v>589.6146203399085</v>
+        <v>608.6344468024862</v>
       </c>
       <c r="G33">
         <v>53.2</v>
@@ -3999,28 +3999,28 @@
         <v>174.925</v>
       </c>
       <c r="M33">
-        <v>32.60568850479694</v>
+        <v>33.65748490817749</v>
       </c>
       <c r="N33">
-        <v>142.319311495203</v>
+        <v>141.2675150918225</v>
       </c>
       <c r="O33">
-        <v>35.49443628690364</v>
+        <v>35.23211826390052</v>
       </c>
       <c r="P33">
-        <v>106.8248752082994</v>
+        <v>106.0353968279219</v>
       </c>
       <c r="Q33">
-        <v>229.0248752082994</v>
+        <v>228.2353968279219</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09822487105844913</v>
+        <v>0.09885203789744629</v>
       </c>
       <c r="T33">
-        <v>1.210736052158179</v>
+        <v>1.225220274767813</v>
       </c>
       <c r="U33">
         <v>0.05530000000000001</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.3648614098201</v>
+        <v>5.197209490763221</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08050200337026348</v>
+        <v>0.08036130991019706</v>
       </c>
       <c r="C34">
-        <v>1326.101573428275</v>
+        <v>1314.741173463527</v>
       </c>
       <c r="D34">
-        <v>1881.536020230761</v>
+        <v>1889.19544672859</v>
       </c>
       <c r="E34">
-        <v>-381.9481994552831</v>
+        <v>-362.9283729927054</v>
       </c>
       <c r="F34">
-        <v>608.6344468024862</v>
+        <v>627.6542732650639</v>
       </c>
       <c r="G34">
         <v>53.2</v>
@@ -4081,28 +4081,28 @@
         <v>174.925</v>
       </c>
       <c r="M34">
-        <v>33.65748490817749</v>
+        <v>34.70928131155804</v>
       </c>
       <c r="N34">
-        <v>141.2675150918225</v>
+        <v>140.2157186884419</v>
       </c>
       <c r="O34">
-        <v>35.23211826390052</v>
+        <v>34.96980024089741</v>
       </c>
       <c r="P34">
-        <v>106.0353968279219</v>
+        <v>105.2459184475445</v>
       </c>
       <c r="Q34">
-        <v>228.2353968279219</v>
+        <v>227.4459184475445</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09885203789744629</v>
+        <v>0.09949792613462249</v>
       </c>
       <c r="T34">
-        <v>1.225220274767813</v>
+        <v>1.240136862231466</v>
       </c>
       <c r="U34">
         <v>0.05530000000000001</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.197209490763221</v>
+        <v>5.039718294073427</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08036130991019706</v>
+        <v>0.08022061645013065</v>
       </c>
       <c r="C35">
-        <v>1314.741173463527</v>
+        <v>1303.443388950053</v>
       </c>
       <c r="D35">
-        <v>1889.19544672859</v>
+        <v>1896.917488677695</v>
       </c>
       <c r="E35">
-        <v>-362.9283729927054</v>
+        <v>-343.9085465301276</v>
       </c>
       <c r="F35">
-        <v>627.6542732650639</v>
+        <v>646.6740997276416</v>
       </c>
       <c r="G35">
         <v>53.2</v>
@@ -4163,28 +4163,28 @@
         <v>174.925</v>
       </c>
       <c r="M35">
-        <v>34.70928131155804</v>
+        <v>35.76107771493859</v>
       </c>
       <c r="N35">
-        <v>140.2157186884419</v>
+        <v>139.1639222850614</v>
       </c>
       <c r="O35">
-        <v>34.96980024089741</v>
+        <v>34.70748221789431</v>
       </c>
       <c r="P35">
-        <v>105.2459184475445</v>
+        <v>104.4564400671671</v>
       </c>
       <c r="Q35">
-        <v>227.4459184475445</v>
+        <v>226.6564400671671</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09949792613462249</v>
+        <v>0.1001633867426222</v>
       </c>
       <c r="T35">
-        <v>1.240136862231466</v>
+        <v>1.255505467497048</v>
       </c>
       <c r="U35">
         <v>0.05530000000000001</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.039718294073427</v>
+        <v>4.891491285424209</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08022061645013065</v>
+        <v>0.08007992299006422</v>
       </c>
       <c r="C36">
-        <v>1303.443388950053</v>
+        <v>1292.208990856727</v>
       </c>
       <c r="D36">
-        <v>1896.917488677695</v>
+        <v>1904.702917046946</v>
       </c>
       <c r="E36">
-        <v>-343.9085465301276</v>
+        <v>-324.8887200675499</v>
       </c>
       <c r="F36">
-        <v>646.6740997276416</v>
+        <v>665.6939261902194</v>
       </c>
       <c r="G36">
         <v>53.2</v>
@@ -4245,28 +4245,28 @@
         <v>174.925</v>
       </c>
       <c r="M36">
-        <v>35.76107771493859</v>
+        <v>36.81287411831914</v>
       </c>
       <c r="N36">
-        <v>139.1639222850614</v>
+        <v>138.1121258816808</v>
       </c>
       <c r="O36">
-        <v>34.70748221789431</v>
+        <v>34.4451641948912</v>
       </c>
       <c r="P36">
-        <v>104.4564400671671</v>
+        <v>103.6669616867896</v>
       </c>
       <c r="Q36">
-        <v>226.6564400671671</v>
+        <v>225.8669616867896</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1001633867426222</v>
+        <v>0.1008493230616373</v>
       </c>
       <c r="T36">
-        <v>1.255505467497048</v>
+        <v>1.271346952924649</v>
       </c>
       <c r="U36">
         <v>0.05530000000000001</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.891491285424209</v>
+        <v>4.751734391554944</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08007992299006422</v>
+        <v>0.0799392295299978</v>
       </c>
       <c r="C37">
-        <v>1292.208990856727</v>
+        <v>1281.03876286158</v>
       </c>
       <c r="D37">
-        <v>1904.702917046946</v>
+        <v>1912.552515514377</v>
       </c>
       <c r="E37">
-        <v>-324.8887200675499</v>
+        <v>-305.8688936049722</v>
       </c>
       <c r="F37">
-        <v>665.6939261902194</v>
+        <v>684.7137526527971</v>
       </c>
       <c r="G37">
         <v>53.2</v>
@@ -4327,28 +4327,28 @@
         <v>174.925</v>
       </c>
       <c r="M37">
-        <v>36.81287411831914</v>
+        <v>37.86467052169969</v>
       </c>
       <c r="N37">
-        <v>138.1121258816808</v>
+        <v>137.0603294783003</v>
       </c>
       <c r="O37">
-        <v>34.4451641948912</v>
+        <v>34.18284617188809</v>
       </c>
       <c r="P37">
-        <v>103.6669616867896</v>
+        <v>102.8774833064122</v>
       </c>
       <c r="Q37">
-        <v>225.8669616867896</v>
+        <v>225.0774833064122</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1008493230616373</v>
+        <v>0.1015566948906216</v>
       </c>
       <c r="T37">
-        <v>1.271346952924649</v>
+        <v>1.287683484771861</v>
       </c>
       <c r="U37">
         <v>0.05530000000000001</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.751734391554944</v>
+        <v>4.619741769567307</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07993922952999781</v>
+        <v>0.08049284106993139</v>
       </c>
       <c r="C38">
-        <v>1281.038762861579</v>
+        <v>1231.499350494132</v>
       </c>
       <c r="D38">
-        <v>1912.552515514376</v>
+        <v>1882.032929609507</v>
       </c>
       <c r="E38">
-        <v>-305.8688936049723</v>
+        <v>-286.8490671423946</v>
       </c>
       <c r="F38">
-        <v>684.713752652797</v>
+        <v>703.7335791153747</v>
       </c>
       <c r="G38">
         <v>53.2</v>
@@ -4409,45 +4409,45 @@
         <v>174.925</v>
       </c>
       <c r="M38">
-        <v>37.86467052169968</v>
+        <v>40.67580087286866</v>
       </c>
       <c r="N38">
-        <v>137.0603294783003</v>
+        <v>134.2491991271313</v>
       </c>
       <c r="O38">
-        <v>34.18284617188809</v>
+        <v>33.48175026230655</v>
       </c>
       <c r="P38">
-        <v>102.8774833064122</v>
+        <v>100.7674488648248</v>
       </c>
       <c r="Q38">
-        <v>225.0774833064122</v>
+        <v>222.9674488648247</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1015566948906216</v>
+        <v>0.1022865229681451</v>
       </c>
       <c r="T38">
-        <v>1.287683484771861</v>
+        <v>1.304538636677715</v>
       </c>
       <c r="U38">
-        <v>0.05530000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V38">
         <v>0.2494</v>
       </c>
       <c r="W38">
-        <v>0.04150818000000001</v>
+        <v>0.04338468</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y38">
-        <v>4.619741769567308</v>
+        <v>4.300468491000934</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08049284106993139</v>
+        <v>0.08037091260986498</v>
       </c>
       <c r="C39">
-        <v>1231.499350494132</v>
+        <v>1219.11728275928</v>
       </c>
       <c r="D39">
-        <v>1882.032929609507</v>
+        <v>1888.670688337232</v>
       </c>
       <c r="E39">
-        <v>-286.8490671423946</v>
+        <v>-267.829240679817</v>
       </c>
       <c r="F39">
-        <v>703.7335791153747</v>
+        <v>722.7534055779523</v>
       </c>
       <c r="G39">
         <v>53.2</v>
@@ -4491,28 +4491,28 @@
         <v>174.925</v>
       </c>
       <c r="M39">
-        <v>40.67580087286866</v>
+        <v>41.77514684240565</v>
       </c>
       <c r="N39">
-        <v>134.2491991271313</v>
+        <v>133.1498531575943</v>
       </c>
       <c r="O39">
-        <v>33.48175026230655</v>
+        <v>33.20757337750402</v>
       </c>
       <c r="P39">
-        <v>100.7674488648248</v>
+        <v>99.94227978009027</v>
       </c>
       <c r="Q39">
-        <v>222.9674488648247</v>
+        <v>222.1422797800903</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1022865229681451</v>
+        <v>0.103039893886879</v>
       </c>
       <c r="T39">
-        <v>1.304538636677715</v>
+        <v>1.321937503161178</v>
       </c>
       <c r="U39">
         <v>0.0578</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.300468491000934</v>
+        <v>4.18729826755354</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08037091260986498</v>
+        <v>0.08024898414979856</v>
       </c>
       <c r="C40">
-        <v>1219.11728275928</v>
+        <v>1206.782202285152</v>
       </c>
       <c r="D40">
-        <v>1888.670688337232</v>
+        <v>1895.355434325682</v>
       </c>
       <c r="E40">
-        <v>-267.829240679817</v>
+        <v>-248.8094142172392</v>
       </c>
       <c r="F40">
-        <v>722.7534055779523</v>
+        <v>741.77323204053</v>
       </c>
       <c r="G40">
         <v>53.2</v>
@@ -4573,28 +4573,28 @@
         <v>174.925</v>
       </c>
       <c r="M40">
-        <v>41.77514684240565</v>
+        <v>42.87449281194264</v>
       </c>
       <c r="N40">
-        <v>133.1498531575943</v>
+        <v>132.0505071880573</v>
       </c>
       <c r="O40">
-        <v>33.20757337750402</v>
+        <v>32.9333964927015</v>
       </c>
       <c r="P40">
-        <v>99.94227978009027</v>
+        <v>99.11711069535582</v>
       </c>
       <c r="Q40">
-        <v>222.1422797800903</v>
+        <v>221.3171106953558</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.103039893886879</v>
+        <v>0.103817965491473</v>
       </c>
       <c r="T40">
-        <v>1.321937503161178</v>
+        <v>1.339906824283442</v>
       </c>
       <c r="U40">
         <v>0.0578</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.18729826755354</v>
+        <v>4.079931645308578</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08024898414979856</v>
+        <v>0.08117789568973215</v>
       </c>
       <c r="C41">
-        <v>1206.782202285152</v>
+        <v>1137.996342515739</v>
       </c>
       <c r="D41">
-        <v>1895.355434325682</v>
+        <v>1845.589401018847</v>
       </c>
       <c r="E41">
-        <v>-248.8094142172392</v>
+        <v>-229.7895877546615</v>
       </c>
       <c r="F41">
-        <v>741.77323204053</v>
+        <v>760.7930585031078</v>
       </c>
       <c r="G41">
         <v>53.2</v>
@@ -4655,45 +4655,45 @@
         <v>174.925</v>
       </c>
       <c r="M41">
-        <v>42.87449281194264</v>
+        <v>46.63661448624051</v>
       </c>
       <c r="N41">
-        <v>132.0505071880573</v>
+        <v>128.2883855137594</v>
       </c>
       <c r="O41">
-        <v>32.9333964927015</v>
+        <v>31.99512334713161</v>
       </c>
       <c r="P41">
-        <v>99.11711069535582</v>
+        <v>96.29326216662783</v>
       </c>
       <c r="Q41">
-        <v>221.3171106953558</v>
+        <v>218.4932621666278</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.103817965491473</v>
+        <v>0.1046219728162202</v>
       </c>
       <c r="T41">
-        <v>1.339906824283442</v>
+        <v>1.358475122776449</v>
       </c>
       <c r="U41">
-        <v>0.0578</v>
+        <v>0.06130000000000001</v>
       </c>
       <c r="V41">
         <v>0.2494</v>
       </c>
       <c r="W41">
-        <v>0.04338468</v>
+        <v>0.04601178</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y41">
-        <v>4.079931645308578</v>
+        <v>3.750808285014109</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08117789568973215</v>
+        <v>0.08108223822966572</v>
       </c>
       <c r="C42">
-        <v>1137.996342515739</v>
+        <v>1123.980291416782</v>
       </c>
       <c r="D42">
-        <v>1845.589401018847</v>
+        <v>1850.593176382467</v>
       </c>
       <c r="E42">
-        <v>-229.7895877546615</v>
+        <v>-210.7697612920838</v>
       </c>
       <c r="F42">
-        <v>760.7930585031078</v>
+        <v>779.8128849656855</v>
       </c>
       <c r="G42">
         <v>53.2</v>
@@ -4737,28 +4737,28 @@
         <v>174.925</v>
       </c>
       <c r="M42">
-        <v>46.63661448624051</v>
+        <v>47.80252984839652</v>
       </c>
       <c r="N42">
-        <v>128.2883855137594</v>
+        <v>127.1224701516034</v>
       </c>
       <c r="O42">
-        <v>31.99512334713161</v>
+        <v>31.7043440558099</v>
       </c>
       <c r="P42">
-        <v>96.29326216662783</v>
+        <v>95.41812609579354</v>
       </c>
       <c r="Q42">
-        <v>218.4932621666278</v>
+        <v>217.6181260957935</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1046219728162202</v>
+        <v>0.1054532346265521</v>
       </c>
       <c r="T42">
-        <v>1.358475122776449</v>
+        <v>1.377672855116676</v>
       </c>
       <c r="U42">
         <v>0.06130000000000001</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.750808285014109</v>
+        <v>3.659325156111326</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08108223822966572</v>
+        <v>0.0809865807695993</v>
       </c>
       <c r="C43">
-        <v>1123.980291416782</v>
+        <v>1109.991446623839</v>
       </c>
       <c r="D43">
-        <v>1850.593176382467</v>
+        <v>1855.624158052102</v>
       </c>
       <c r="E43">
-        <v>-210.7697612920838</v>
+        <v>-191.7499348295061</v>
       </c>
       <c r="F43">
-        <v>779.8128849656855</v>
+        <v>798.8327114282632</v>
       </c>
       <c r="G43">
         <v>53.2</v>
@@ -4819,28 +4819,28 @@
         <v>174.925</v>
       </c>
       <c r="M43">
-        <v>47.80252984839652</v>
+        <v>48.96844521055254</v>
       </c>
       <c r="N43">
-        <v>127.1224701516034</v>
+        <v>125.9565547894474</v>
       </c>
       <c r="O43">
-        <v>31.7043440558099</v>
+        <v>31.41356476448819</v>
       </c>
       <c r="P43">
-        <v>95.41812609579354</v>
+        <v>94.54299002495922</v>
       </c>
       <c r="Q43">
-        <v>217.6181260957935</v>
+        <v>216.7429900249592</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1054532346265521</v>
+        <v>0.1063131606372402</v>
       </c>
       <c r="T43">
-        <v>1.377672855116676</v>
+        <v>1.397532578227256</v>
       </c>
       <c r="U43">
         <v>0.06130000000000001</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.659325156111326</v>
+        <v>3.572198366680104</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.0809865807695993</v>
+        <v>0.08179464570953289</v>
       </c>
       <c r="C44">
-        <v>1109.991446623839</v>
+        <v>1049.313623693788</v>
       </c>
       <c r="D44">
-        <v>1855.624158052102</v>
+        <v>1813.966161584628</v>
       </c>
       <c r="E44">
-        <v>-191.7499348295062</v>
+        <v>-172.7301083669284</v>
       </c>
       <c r="F44">
-        <v>798.8327114282631</v>
+        <v>817.8525378908408</v>
       </c>
       <c r="G44">
         <v>53.2</v>
@@ -4901,45 +4901,45 @@
         <v>174.925</v>
       </c>
       <c r="M44">
-        <v>48.96844521055253</v>
+        <v>52.4243476788029</v>
       </c>
       <c r="N44">
-        <v>125.9565547894474</v>
+        <v>122.5006523211971</v>
       </c>
       <c r="O44">
-        <v>31.41356476448819</v>
+        <v>30.55166268890655</v>
       </c>
       <c r="P44">
-        <v>94.54299002495924</v>
+        <v>91.94898963229051</v>
       </c>
       <c r="Q44">
-        <v>216.7429900249592</v>
+        <v>214.1489896322905</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1063131606372402</v>
+        <v>0.1072032594904086</v>
       </c>
       <c r="T44">
-        <v>1.397532578227256</v>
+        <v>1.418089133727681</v>
       </c>
       <c r="U44">
-        <v>0.06130000000000001</v>
+        <v>0.0641</v>
       </c>
       <c r="V44">
         <v>0.2494</v>
       </c>
       <c r="W44">
-        <v>0.04601178</v>
+        <v>0.04811346</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y44">
-        <v>3.572198366680105</v>
+        <v>3.336712953907266</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08179464570953289</v>
+        <v>0.08172000504946647</v>
       </c>
       <c r="C45">
-        <v>1049.313623693788</v>
+        <v>1034.063162838269</v>
       </c>
       <c r="D45">
-        <v>1813.966161584628</v>
+        <v>1817.735527191687</v>
       </c>
       <c r="E45">
-        <v>-172.7301083669284</v>
+        <v>-153.7102819043507</v>
       </c>
       <c r="F45">
-        <v>817.8525378908408</v>
+        <v>836.8723643534186</v>
       </c>
       <c r="G45">
         <v>53.2</v>
@@ -4983,28 +4983,28 @@
         <v>174.925</v>
       </c>
       <c r="M45">
-        <v>52.4243476788029</v>
+        <v>53.64351855505414</v>
       </c>
       <c r="N45">
-        <v>122.5006523211971</v>
+        <v>121.2814814449458</v>
       </c>
       <c r="O45">
-        <v>30.55166268890655</v>
+        <v>30.24760147236949</v>
       </c>
       <c r="P45">
-        <v>91.94898963229051</v>
+        <v>91.03387997257633</v>
       </c>
       <c r="Q45">
-        <v>214.1489896322905</v>
+        <v>213.2338799725763</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1072032594904086</v>
+        <v>0.108125147588333</v>
       </c>
       <c r="T45">
-        <v>1.418089133727681</v>
+        <v>1.439379851924549</v>
       </c>
       <c r="U45">
         <v>0.0641</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.336712953907266</v>
+        <v>3.260878568591192</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08172000504946647</v>
+        <v>0.08164536438940005</v>
       </c>
       <c r="C46">
-        <v>1034.063162838269</v>
+        <v>1018.82839985285</v>
       </c>
       <c r="D46">
-        <v>1817.735527191687</v>
+        <v>1821.520590668846</v>
       </c>
       <c r="E46">
-        <v>-153.7102819043507</v>
+        <v>-134.690455441773</v>
       </c>
       <c r="F46">
-        <v>836.8723643534186</v>
+        <v>855.8921908159963</v>
       </c>
       <c r="G46">
         <v>53.2</v>
@@ -5065,28 +5065,28 @@
         <v>174.925</v>
       </c>
       <c r="M46">
-        <v>53.64351855505414</v>
+        <v>54.86268943130536</v>
       </c>
       <c r="N46">
-        <v>121.2814814449458</v>
+        <v>120.0623105686946</v>
       </c>
       <c r="O46">
-        <v>30.24760147236949</v>
+        <v>29.94354025583243</v>
       </c>
       <c r="P46">
-        <v>91.03387997257633</v>
+        <v>90.11877031286215</v>
       </c>
       <c r="Q46">
-        <v>213.2338799725763</v>
+        <v>212.3187703128621</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.108125147588333</v>
+        <v>0.1090805588898183</v>
       </c>
       <c r="T46">
-        <v>1.439379851924549</v>
+        <v>1.461444778055849</v>
       </c>
       <c r="U46">
         <v>0.0641</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.260878568591192</v>
+        <v>3.188414600400276</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08164536438940005</v>
+        <v>0.08157072372933363</v>
       </c>
       <c r="C47">
-        <v>1018.82839985285</v>
+        <v>1003.609433004991</v>
       </c>
       <c r="D47">
-        <v>1821.520590668846</v>
+        <v>1825.321450283565</v>
       </c>
       <c r="E47">
-        <v>-134.690455441773</v>
+        <v>-115.6706289791954</v>
       </c>
       <c r="F47">
-        <v>855.8921908159963</v>
+        <v>874.9120172785739</v>
       </c>
       <c r="G47">
         <v>53.2</v>
@@ -5147,28 +5147,28 @@
         <v>174.925</v>
       </c>
       <c r="M47">
-        <v>54.86268943130536</v>
+        <v>56.08186030755659</v>
       </c>
       <c r="N47">
-        <v>120.0623105686946</v>
+        <v>118.8431396924434</v>
       </c>
       <c r="O47">
-        <v>29.94354025583243</v>
+        <v>29.63947903929538</v>
       </c>
       <c r="P47">
-        <v>90.11877031286215</v>
+        <v>89.20366065314799</v>
       </c>
       <c r="Q47">
-        <v>212.3187703128621</v>
+        <v>211.403660653148</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1090805588898183</v>
+        <v>0.1100713557950623</v>
       </c>
       <c r="T47">
-        <v>1.461444778055849</v>
+        <v>1.484326923673494</v>
       </c>
       <c r="U47">
         <v>0.0641</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.188414600400276</v>
+        <v>3.11910123952201</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08157072372933363</v>
+        <v>0.08149608306926721</v>
       </c>
       <c r="C48">
-        <v>1003.609433004991</v>
+        <v>988.4063613840631</v>
       </c>
       <c r="D48">
-        <v>1825.321450283565</v>
+        <v>1829.138205125215</v>
       </c>
       <c r="E48">
-        <v>-115.6706289791954</v>
+        <v>-96.65080251661766</v>
       </c>
       <c r="F48">
-        <v>874.9120172785739</v>
+        <v>893.9318437411516</v>
       </c>
       <c r="G48">
         <v>53.2</v>
@@ -5229,28 +5229,28 @@
         <v>174.925</v>
       </c>
       <c r="M48">
-        <v>56.08186030755659</v>
+        <v>57.30103118380782</v>
       </c>
       <c r="N48">
-        <v>118.8431396924434</v>
+        <v>117.6239688161921</v>
       </c>
       <c r="O48">
-        <v>29.63947903929538</v>
+        <v>29.33541782275832</v>
       </c>
       <c r="P48">
-        <v>89.20366065314799</v>
+        <v>88.28855099343382</v>
       </c>
       <c r="Q48">
-        <v>211.403660653148</v>
+        <v>210.4885509934338</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1100713557950623</v>
+        <v>0.1110995412627683</v>
       </c>
       <c r="T48">
-        <v>1.484326923673494</v>
+        <v>1.508072546484257</v>
       </c>
       <c r="U48">
         <v>0.0641</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.11910123952201</v>
+        <v>3.052737383361967</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08149608306926721</v>
+        <v>0.0842316888092008</v>
       </c>
       <c r="C49">
-        <v>988.4063613840631</v>
+        <v>839.186662677661</v>
       </c>
       <c r="D49">
-        <v>1829.138205125215</v>
+        <v>1698.93833288139</v>
       </c>
       <c r="E49">
-        <v>-96.65080251661766</v>
+        <v>-77.63097605403993</v>
       </c>
       <c r="F49">
-        <v>893.9318437411516</v>
+        <v>912.9516702037293</v>
       </c>
       <c r="G49">
         <v>53.2</v>
@@ -5311,45 +5311,45 @@
         <v>174.925</v>
       </c>
       <c r="M49">
-        <v>57.30103118380782</v>
+        <v>65.64122508764815</v>
       </c>
       <c r="N49">
-        <v>117.6239688161921</v>
+        <v>109.2837749123518</v>
       </c>
       <c r="O49">
-        <v>29.33541782275832</v>
+        <v>27.25537346314054</v>
       </c>
       <c r="P49">
-        <v>88.28855099343382</v>
+        <v>82.02840144921126</v>
       </c>
       <c r="Q49">
-        <v>210.4885509934338</v>
+        <v>204.2284014492112</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1110995412627683</v>
+        <v>0.1121672723253861</v>
       </c>
       <c r="T49">
-        <v>1.508072546484257</v>
+        <v>1.53273146248005</v>
       </c>
       <c r="U49">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V49">
         <v>0.2494</v>
       </c>
       <c r="W49">
-        <v>0.04811346</v>
+        <v>0.05396814</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y49">
-        <v>3.052737383361967</v>
+        <v>2.664864949830377</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.0842316888092008</v>
+        <v>0.08421559494913439</v>
       </c>
       <c r="C50">
-        <v>839.1866626776612</v>
+        <v>820.87859079879</v>
       </c>
       <c r="D50">
-        <v>1698.93833288139</v>
+        <v>1699.650087465097</v>
       </c>
       <c r="E50">
-        <v>-77.63097605404005</v>
+        <v>-58.61114959146232</v>
       </c>
       <c r="F50">
-        <v>912.9516702037292</v>
+        <v>931.971496666307</v>
       </c>
       <c r="G50">
         <v>53.2</v>
@@ -5393,28 +5393,28 @@
         <v>174.925</v>
       </c>
       <c r="M50">
-        <v>65.64122508764814</v>
+        <v>67.00875061030747</v>
       </c>
       <c r="N50">
-        <v>109.2837749123518</v>
+        <v>107.9162493896925</v>
       </c>
       <c r="O50">
-        <v>27.25537346314054</v>
+        <v>26.9143125977893</v>
       </c>
       <c r="P50">
-        <v>82.02840144921127</v>
+        <v>81.00193679190318</v>
       </c>
       <c r="Q50">
-        <v>204.2284014492113</v>
+        <v>203.2019367919032</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1121672723253861</v>
+        <v>0.1132768751943811</v>
       </c>
       <c r="T50">
-        <v>1.532731462480049</v>
+        <v>1.558357394789403</v>
       </c>
       <c r="U50">
         <v>0.07190000000000001</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.664864949830377</v>
+        <v>2.610479950854247</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08421559494913439</v>
+        <v>0.08419950108906796</v>
       </c>
       <c r="C51">
-        <v>820.87859079879</v>
+        <v>802.5711155359352</v>
       </c>
       <c r="D51">
-        <v>1699.650087465097</v>
+        <v>1700.36243866482</v>
       </c>
       <c r="E51">
-        <v>-58.61114959146232</v>
+        <v>-39.5913231288846</v>
       </c>
       <c r="F51">
-        <v>931.971496666307</v>
+        <v>950.9913231288847</v>
       </c>
       <c r="G51">
         <v>53.2</v>
@@ -5475,28 +5475,28 @@
         <v>174.925</v>
       </c>
       <c r="M51">
-        <v>67.00875061030747</v>
+        <v>68.37627613296681</v>
       </c>
       <c r="N51">
-        <v>107.9162493896925</v>
+        <v>106.5487238670331</v>
       </c>
       <c r="O51">
-        <v>26.9143125977893</v>
+        <v>26.57325173243807</v>
       </c>
       <c r="P51">
-        <v>81.00193679190318</v>
+        <v>79.97547213459508</v>
       </c>
       <c r="Q51">
-        <v>203.2019367919032</v>
+        <v>202.1754721345951</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1132768751943811</v>
+        <v>0.1144308621781359</v>
       </c>
       <c r="T51">
-        <v>1.558357394789403</v>
+        <v>1.58500836439113</v>
       </c>
       <c r="U51">
         <v>0.07190000000000001</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.610479950854247</v>
+        <v>2.558270351837162</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08419950108906796</v>
+        <v>0.08418340722900154</v>
       </c>
       <c r="C52">
-        <v>802.5711155359352</v>
+        <v>784.2642376395646</v>
       </c>
       <c r="D52">
-        <v>1700.36243866482</v>
+        <v>1701.075387231027</v>
       </c>
       <c r="E52">
-        <v>-39.5913231288846</v>
+        <v>-20.57149666630687</v>
       </c>
       <c r="F52">
-        <v>950.9913231288847</v>
+        <v>970.0111495914624</v>
       </c>
       <c r="G52">
         <v>53.2</v>
@@ -5557,28 +5557,28 @@
         <v>174.925</v>
       </c>
       <c r="M52">
-        <v>68.37627613296681</v>
+        <v>69.74380165562616</v>
       </c>
       <c r="N52">
-        <v>106.5487238670331</v>
+        <v>105.1811983443738</v>
       </c>
       <c r="O52">
-        <v>26.57325173243807</v>
+        <v>26.23219086708682</v>
       </c>
       <c r="P52">
-        <v>79.97547213459508</v>
+        <v>78.94900747728697</v>
       </c>
       <c r="Q52">
-        <v>202.1754721345951</v>
+        <v>201.1490074772869</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1144308621781359</v>
+        <v>0.1156319506714317</v>
       </c>
       <c r="T52">
-        <v>1.58500836439113</v>
+        <v>1.612747128670479</v>
       </c>
       <c r="U52">
         <v>0.07190000000000001</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.558270351837162</v>
+        <v>2.508108188075649</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08418340722900154</v>
+        <v>0.08568953016893513</v>
       </c>
       <c r="C53">
-        <v>784.2642376395646</v>
+        <v>701.0163129162484</v>
       </c>
       <c r="D53">
-        <v>1701.075387231027</v>
+        <v>1636.847288970288</v>
       </c>
       <c r="E53">
-        <v>-20.57149666630687</v>
+        <v>-1.551670203729145</v>
       </c>
       <c r="F53">
-        <v>970.0111495914624</v>
+        <v>989.0309760540401</v>
       </c>
       <c r="G53">
         <v>53.2</v>
@@ -5639,45 +5639,45 @@
         <v>174.925</v>
       </c>
       <c r="M53">
-        <v>69.74380165562616</v>
+        <v>74.96854798489625</v>
       </c>
       <c r="N53">
-        <v>105.1811983443738</v>
+        <v>99.95645201510371</v>
       </c>
       <c r="O53">
-        <v>26.23219086708682</v>
+        <v>24.92913913256687</v>
       </c>
       <c r="P53">
-        <v>78.94900747728697</v>
+        <v>75.02731288253685</v>
       </c>
       <c r="Q53">
-        <v>201.1490074772869</v>
+        <v>197.2273128825368</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1156319506714317</v>
+        <v>0.1168830845186148</v>
       </c>
       <c r="T53">
-        <v>1.612747128670479</v>
+        <v>1.6416416747948</v>
       </c>
       <c r="U53">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V53">
         <v>0.2494</v>
       </c>
       <c r="W53">
-        <v>0.05396814</v>
+        <v>0.05689548</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y53">
-        <v>2.508108188075649</v>
+        <v>2.333311831452861</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08568953016893513</v>
+        <v>0.0857027097088687</v>
       </c>
       <c r="C54">
-        <v>701.0163129162484</v>
+        <v>681.45584912935</v>
       </c>
       <c r="D54">
-        <v>1636.847288970288</v>
+        <v>1636.306651645968</v>
       </c>
       <c r="E54">
-        <v>-1.551670203729145</v>
+        <v>17.46815625884858</v>
       </c>
       <c r="F54">
-        <v>989.0309760540401</v>
+        <v>1008.050802516618</v>
       </c>
       <c r="G54">
         <v>53.2</v>
@@ -5721,28 +5721,28 @@
         <v>174.925</v>
       </c>
       <c r="M54">
-        <v>74.96854798489625</v>
+        <v>76.41025083075964</v>
       </c>
       <c r="N54">
-        <v>99.95645201510371</v>
+        <v>98.51474916924032</v>
       </c>
       <c r="O54">
-        <v>24.92913913256687</v>
+        <v>24.56957844280853</v>
       </c>
       <c r="P54">
-        <v>75.02731288253685</v>
+        <v>73.94517072643178</v>
       </c>
       <c r="Q54">
-        <v>197.2273128825368</v>
+        <v>196.1451707264318</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1168830845186148</v>
+        <v>0.118187458103976</v>
       </c>
       <c r="T54">
-        <v>1.6416416747948</v>
+        <v>1.671765776073348</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.333311831452861</v>
+        <v>2.289287079916015</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.0857027097088687</v>
+        <v>0.0857158892488023</v>
       </c>
       <c r="C55">
-        <v>681.45584912935</v>
+        <v>661.8957423607376</v>
       </c>
       <c r="D55">
-        <v>1636.306651645968</v>
+        <v>1635.766371339933</v>
       </c>
       <c r="E55">
-        <v>17.46815625884858</v>
+        <v>36.48798272142631</v>
       </c>
       <c r="F55">
-        <v>1008.050802516618</v>
+        <v>1027.070628979196</v>
       </c>
       <c r="G55">
         <v>53.2</v>
@@ -5803,28 +5803,28 @@
         <v>174.925</v>
       </c>
       <c r="M55">
-        <v>76.41025083075964</v>
+        <v>77.85195367662303</v>
       </c>
       <c r="N55">
-        <v>98.51474916924032</v>
+        <v>97.07304632337693</v>
       </c>
       <c r="O55">
-        <v>24.56957844280853</v>
+        <v>24.21001775305021</v>
       </c>
       <c r="P55">
-        <v>73.94517072643178</v>
+        <v>72.86302857032672</v>
       </c>
       <c r="Q55">
-        <v>196.1451707264318</v>
+        <v>195.0630285703267</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.118187458103976</v>
+        <v>0.1195485435843528</v>
       </c>
       <c r="T55">
-        <v>1.671765776073348</v>
+        <v>1.703199620885746</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.289287079916015</v>
+        <v>2.246892874732385</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.0857158892488023</v>
+        <v>0.08572906878873587</v>
       </c>
       <c r="C56">
-        <v>661.8957423607376</v>
+        <v>642.3359922568868</v>
       </c>
       <c r="D56">
-        <v>1635.766371339933</v>
+        <v>1635.22644769866</v>
       </c>
       <c r="E56">
-        <v>36.48798272142631</v>
+        <v>55.50780918400392</v>
       </c>
       <c r="F56">
-        <v>1027.070628979196</v>
+        <v>1046.090455441773</v>
       </c>
       <c r="G56">
         <v>53.2</v>
@@ -5885,28 +5885,28 @@
         <v>174.925</v>
       </c>
       <c r="M56">
-        <v>77.85195367662303</v>
+        <v>79.29365652248642</v>
       </c>
       <c r="N56">
-        <v>97.07304632337693</v>
+        <v>95.63134347751354</v>
       </c>
       <c r="O56">
-        <v>24.21001775305021</v>
+        <v>23.85045706329188</v>
       </c>
       <c r="P56">
-        <v>72.86302857032672</v>
+        <v>71.78088641422167</v>
       </c>
       <c r="Q56">
-        <v>195.0630285703267</v>
+        <v>193.9808864142217</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1195485435843528</v>
+        <v>0.1209701217527464</v>
       </c>
       <c r="T56">
-        <v>1.703199620885746</v>
+        <v>1.736030525467584</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.246892874732385</v>
+        <v>2.206040277009977</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08572906878873587</v>
+        <v>0.08574224832866946</v>
       </c>
       <c r="C57">
-        <v>642.3359922568868</v>
+        <v>622.7765984647344</v>
       </c>
       <c r="D57">
-        <v>1635.22644769866</v>
+        <v>1634.686880369085</v>
       </c>
       <c r="E57">
-        <v>55.50780918400392</v>
+        <v>74.52763564658176</v>
       </c>
       <c r="F57">
-        <v>1046.090455441773</v>
+        <v>1065.110281904351</v>
       </c>
       <c r="G57">
         <v>53.2</v>
@@ -5967,28 +5967,28 @@
         <v>174.925</v>
       </c>
       <c r="M57">
-        <v>79.29365652248642</v>
+        <v>80.73535936834982</v>
       </c>
       <c r="N57">
-        <v>95.63134347751354</v>
+        <v>94.18964063165014</v>
       </c>
       <c r="O57">
-        <v>23.85045706329188</v>
+        <v>23.49089637353354</v>
       </c>
       <c r="P57">
-        <v>71.78088641422167</v>
+        <v>70.69874425811659</v>
       </c>
       <c r="Q57">
-        <v>193.9808864142217</v>
+        <v>192.8987442581166</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1209701217527464</v>
+        <v>0.1224563171106124</v>
       </c>
       <c r="T57">
-        <v>1.736030525467584</v>
+        <v>1.770353743894051</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.206040277009977</v>
+        <v>2.166646700634799</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08574224832866946</v>
+        <v>0.08575542786860305</v>
       </c>
       <c r="C58">
-        <v>622.7765984647344</v>
+        <v>603.2175606316871</v>
       </c>
       <c r="D58">
-        <v>1634.686880369085</v>
+        <v>1634.147668998616</v>
       </c>
       <c r="E58">
-        <v>74.52763564658176</v>
+        <v>93.54746210915937</v>
       </c>
       <c r="F58">
-        <v>1065.110281904351</v>
+        <v>1084.130108366929</v>
       </c>
       <c r="G58">
         <v>53.2</v>
@@ -6049,28 +6049,28 @@
         <v>174.925</v>
       </c>
       <c r="M58">
-        <v>80.73535936834982</v>
+        <v>82.17706221421319</v>
       </c>
       <c r="N58">
-        <v>94.18964063165014</v>
+        <v>92.74793778578676</v>
       </c>
       <c r="O58">
-        <v>23.49089637353354</v>
+        <v>23.13133568377522</v>
       </c>
       <c r="P58">
-        <v>70.69874425811659</v>
+        <v>69.61660210201154</v>
       </c>
       <c r="Q58">
-        <v>192.8987442581166</v>
+        <v>191.8166021020115</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1224563171106124</v>
+        <v>0.1240116378339606</v>
       </c>
       <c r="T58">
-        <v>1.770353743894051</v>
+        <v>1.80627339108454</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.166646700634799</v>
+        <v>2.128635355009628</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08575542786860305</v>
+        <v>0.08576860740853662</v>
       </c>
       <c r="C59">
-        <v>603.2175606316871</v>
+        <v>583.6588784056155</v>
       </c>
       <c r="D59">
-        <v>1634.147668998616</v>
+        <v>1633.608813235122</v>
       </c>
       <c r="E59">
-        <v>93.54746210915937</v>
+        <v>112.567288571737</v>
       </c>
       <c r="F59">
-        <v>1084.130108366929</v>
+        <v>1103.149934829506</v>
       </c>
       <c r="G59">
         <v>53.2</v>
@@ -6131,28 +6131,28 @@
         <v>174.925</v>
       </c>
       <c r="M59">
-        <v>82.17706221421319</v>
+        <v>83.61876506007658</v>
       </c>
       <c r="N59">
-        <v>92.74793778578676</v>
+        <v>91.30623493992337</v>
       </c>
       <c r="O59">
-        <v>23.13133568377522</v>
+        <v>22.77177499401689</v>
       </c>
       <c r="P59">
-        <v>69.61660210201154</v>
+        <v>68.53445994590648</v>
       </c>
       <c r="Q59">
-        <v>191.8166021020115</v>
+        <v>190.7344599459065</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1240116378339606</v>
+        <v>0.1256410214488967</v>
       </c>
       <c r="T59">
-        <v>1.80627339108454</v>
+        <v>1.843903497665051</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.128635355009628</v>
+        <v>2.091934745440496</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08576860740853662</v>
+        <v>0.08578178694847019</v>
       </c>
       <c r="C60">
-        <v>583.6588784056155</v>
+        <v>564.1005514348535</v>
       </c>
       <c r="D60">
-        <v>1633.608813235122</v>
+        <v>1633.070312726937</v>
       </c>
       <c r="E60">
-        <v>112.567288571737</v>
+        <v>131.5871150343146</v>
       </c>
       <c r="F60">
-        <v>1103.149934829506</v>
+        <v>1122.169761292084</v>
       </c>
       <c r="G60">
         <v>53.2</v>
@@ -6213,28 +6213,28 @@
         <v>174.925</v>
       </c>
       <c r="M60">
-        <v>83.61876506007658</v>
+        <v>85.06046790593996</v>
       </c>
       <c r="N60">
-        <v>91.30623493992337</v>
+        <v>89.86453209406</v>
       </c>
       <c r="O60">
-        <v>22.77177499401689</v>
+        <v>22.41221430425857</v>
       </c>
       <c r="P60">
-        <v>68.53445994590648</v>
+        <v>67.45231778980143</v>
       </c>
       <c r="Q60">
-        <v>190.7344599459065</v>
+        <v>189.6523177898014</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1256410214488967</v>
+        <v>0.1273498871913907</v>
       </c>
       <c r="T60">
-        <v>1.843903497665051</v>
+        <v>1.88336921920071</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.091934745440496</v>
+        <v>2.056478224331336</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08578178694847019</v>
+        <v>0.08579496648840378</v>
       </c>
       <c r="C61">
-        <v>564.1005514348535</v>
+        <v>544.5425793681991</v>
       </c>
       <c r="D61">
-        <v>1633.070312726937</v>
+        <v>1632.532167122861</v>
       </c>
       <c r="E61">
-        <v>131.5871150343146</v>
+        <v>150.6069414968922</v>
       </c>
       <c r="F61">
-        <v>1122.169761292084</v>
+        <v>1141.189587754661</v>
       </c>
       <c r="G61">
         <v>53.2</v>
@@ -6295,28 +6295,28 @@
         <v>174.925</v>
       </c>
       <c r="M61">
-        <v>85.06046790593996</v>
+        <v>86.50217075180335</v>
       </c>
       <c r="N61">
-        <v>89.86453209406</v>
+        <v>88.42282924819661</v>
       </c>
       <c r="O61">
-        <v>22.41221430425857</v>
+        <v>22.05265361450023</v>
       </c>
       <c r="P61">
-        <v>67.45231778980143</v>
+        <v>66.37017563369638</v>
       </c>
       <c r="Q61">
-        <v>189.6523177898014</v>
+        <v>188.5701756336964</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1273498871913907</v>
+        <v>0.1291441962210094</v>
       </c>
       <c r="T61">
-        <v>1.88336921920071</v>
+        <v>1.924808226813151</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.056478224331336</v>
+        <v>2.022203587259146</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08579496648840378</v>
+        <v>0.09230984322833737</v>
       </c>
       <c r="C62">
-        <v>544.5425793681991</v>
+        <v>296.8454428023269</v>
       </c>
       <c r="D62">
-        <v>1632.532167122861</v>
+        <v>1403.854857019566</v>
       </c>
       <c r="E62">
-        <v>150.6069414968922</v>
+        <v>169.62676795947</v>
       </c>
       <c r="F62">
-        <v>1141.189587754661</v>
+        <v>1160.209414217239</v>
       </c>
       <c r="G62">
         <v>53.2</v>
@@ -6377,45 +6377,45 @@
         <v>174.925</v>
       </c>
       <c r="M62">
-        <v>86.50217075180335</v>
+        <v>104.4188472795516</v>
       </c>
       <c r="N62">
-        <v>88.42282924819661</v>
+        <v>70.5061527204484</v>
       </c>
       <c r="O62">
-        <v>22.05265361450023</v>
+        <v>17.58423448847983</v>
       </c>
       <c r="P62">
-        <v>66.37017563369638</v>
+        <v>52.92191823196856</v>
       </c>
       <c r="Q62">
-        <v>188.5701756336964</v>
+        <v>175.1219182319686</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1291441962210094</v>
+        <v>0.1310305210983009</v>
       </c>
       <c r="T62">
-        <v>1.924808226813151</v>
+        <v>1.968372311739052</v>
       </c>
       <c r="U62">
-        <v>0.07580000000000001</v>
+        <v>0.09000000000000001</v>
       </c>
       <c r="V62">
         <v>0.2494</v>
       </c>
       <c r="W62">
-        <v>0.05689548</v>
+        <v>0.067554</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y62">
-        <v>2.022203587259146</v>
+        <v>1.675224392505391</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09230984322833737</v>
+        <v>0.09242960796827096</v>
       </c>
       <c r="C63">
-        <v>296.8454428023269</v>
+        <v>274.2199177464893</v>
       </c>
       <c r="D63">
-        <v>1403.854857019566</v>
+        <v>1400.249158426306</v>
       </c>
       <c r="E63">
-        <v>169.62676795947</v>
+        <v>188.6465944220477</v>
       </c>
       <c r="F63">
-        <v>1160.209414217239</v>
+        <v>1179.229240679817</v>
       </c>
       <c r="G63">
         <v>53.2</v>
@@ -6459,28 +6459,28 @@
         <v>174.925</v>
       </c>
       <c r="M63">
-        <v>104.4188472795516</v>
+        <v>106.1306316611835</v>
       </c>
       <c r="N63">
-        <v>70.5061527204484</v>
+        <v>68.79436833881641</v>
       </c>
       <c r="O63">
-        <v>17.58423448847983</v>
+        <v>17.15731546370082</v>
       </c>
       <c r="P63">
-        <v>52.92191823196856</v>
+        <v>51.6370528751156</v>
       </c>
       <c r="Q63">
-        <v>175.1219182319686</v>
+        <v>173.8370528751156</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1310305210983009</v>
+        <v>0.133016126232292</v>
       </c>
       <c r="T63">
-        <v>1.968372311739052</v>
+        <v>2.01422924324</v>
       </c>
       <c r="U63">
         <v>0.09000000000000001</v>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>1.675224392505391</v>
+        <v>1.648204644239175</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09242960796827096</v>
+        <v>0.09254937270820454</v>
       </c>
       <c r="C64">
-        <v>274.2199177464893</v>
+        <v>251.6128671868551</v>
       </c>
       <c r="D64">
-        <v>1400.249158426306</v>
+        <v>1396.66193432925</v>
       </c>
       <c r="E64">
-        <v>188.6465944220477</v>
+        <v>207.6664208846255</v>
       </c>
       <c r="F64">
-        <v>1179.229240679817</v>
+        <v>1198.249067142395</v>
       </c>
       <c r="G64">
         <v>53.2</v>
@@ -6541,28 +6541,28 @@
         <v>174.925</v>
       </c>
       <c r="M64">
-        <v>106.1306316611835</v>
+        <v>107.8424160428155</v>
       </c>
       <c r="N64">
-        <v>68.79436833881641</v>
+        <v>67.08258395718441</v>
       </c>
       <c r="O64">
-        <v>17.15731546370082</v>
+        <v>16.73039643892179</v>
       </c>
       <c r="P64">
-        <v>51.6370528751156</v>
+        <v>50.35218751826262</v>
       </c>
       <c r="Q64">
-        <v>173.8370528751156</v>
+        <v>172.5521875182626</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.133016126232292</v>
+        <v>0.1351090613735258</v>
       </c>
       <c r="T64">
-        <v>2.01422924324</v>
+        <v>2.062564927795052</v>
       </c>
       <c r="U64">
         <v>0.09000000000000001</v>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>1.648204644239175</v>
+        <v>1.622042665759188</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09254937270820454</v>
+        <v>0.09266913744813812</v>
       </c>
       <c r="C65">
-        <v>251.6128671868551</v>
+        <v>229.0241494997449</v>
       </c>
       <c r="D65">
-        <v>1396.66193432925</v>
+        <v>1393.093043104717</v>
       </c>
       <c r="E65">
-        <v>207.6664208846255</v>
+        <v>226.6862473472031</v>
       </c>
       <c r="F65">
-        <v>1198.249067142395</v>
+        <v>1217.268893604972</v>
       </c>
       <c r="G65">
         <v>53.2</v>
@@ -6623,28 +6623,28 @@
         <v>174.925</v>
       </c>
       <c r="M65">
-        <v>107.8424160428155</v>
+        <v>109.5542004244475</v>
       </c>
       <c r="N65">
-        <v>67.08258395718441</v>
+        <v>65.37079957555243</v>
       </c>
       <c r="O65">
-        <v>16.73039643892179</v>
+        <v>16.30347741414278</v>
       </c>
       <c r="P65">
-        <v>50.35218751826262</v>
+        <v>49.06732216140965</v>
       </c>
       <c r="Q65">
-        <v>172.5521875182626</v>
+        <v>171.2673221614097</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1351090613735258</v>
+        <v>0.1373182706892725</v>
       </c>
       <c r="T65">
-        <v>2.062564927795052</v>
+        <v>2.113585928158719</v>
       </c>
       <c r="U65">
         <v>0.09000000000000001</v>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>1.622042665759188</v>
+        <v>1.596698249106701</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09266913744813812</v>
+        <v>0.0927889021880717</v>
       </c>
       <c r="C66">
-        <v>229.0241494997449</v>
+        <v>206.4536245053534</v>
       </c>
       <c r="D66">
-        <v>1393.093043104717</v>
+        <v>1389.542344572904</v>
       </c>
       <c r="E66">
-        <v>226.6862473472031</v>
+        <v>245.7060738097809</v>
       </c>
       <c r="F66">
-        <v>1217.268893604972</v>
+        <v>1236.28872006755</v>
       </c>
       <c r="G66">
         <v>53.2</v>
@@ -6705,28 +6705,28 @@
         <v>174.925</v>
       </c>
       <c r="M66">
-        <v>109.5542004244475</v>
+        <v>111.2659848060795</v>
       </c>
       <c r="N66">
-        <v>65.37079957555243</v>
+        <v>63.65901519392042</v>
       </c>
       <c r="O66">
-        <v>16.30347741414278</v>
+        <v>15.87655838936375</v>
       </c>
       <c r="P66">
-        <v>49.06732216140965</v>
+        <v>47.78245680455667</v>
       </c>
       <c r="Q66">
-        <v>171.2673221614097</v>
+        <v>169.9824568045566</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1373182706892725</v>
+        <v>0.1396537205373477</v>
       </c>
       <c r="T66">
-        <v>2.113585928158719</v>
+        <v>2.167522414257453</v>
       </c>
       <c r="U66">
         <v>0.09000000000000001</v>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.596698249106701</v>
+        <v>1.572133660658905</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.0927889021880717</v>
+        <v>0.09290866692800528</v>
       </c>
       <c r="C67">
-        <v>206.4536245053534</v>
+        <v>183.9011534493975</v>
       </c>
       <c r="D67">
-        <v>1389.542344572904</v>
+        <v>1386.009699979525</v>
       </c>
       <c r="E67">
-        <v>245.7060738097809</v>
+        <v>264.7259002723586</v>
       </c>
       <c r="F67">
-        <v>1236.28872006755</v>
+        <v>1255.308546530128</v>
       </c>
       <c r="G67">
         <v>53.2</v>
@@ -6787,28 +6787,28 @@
         <v>174.925</v>
       </c>
       <c r="M67">
-        <v>111.2659848060795</v>
+        <v>112.9777691877115</v>
       </c>
       <c r="N67">
-        <v>63.65901519392042</v>
+        <v>61.94723081228844</v>
       </c>
       <c r="O67">
-        <v>15.87655838936375</v>
+        <v>15.44963936458474</v>
       </c>
       <c r="P67">
-        <v>47.78245680455667</v>
+        <v>46.4975914477037</v>
       </c>
       <c r="Q67">
-        <v>169.9824568045566</v>
+        <v>168.6975914477037</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1396537205373477</v>
+        <v>0.1421265497882508</v>
       </c>
       <c r="T67">
-        <v>2.167522414257453</v>
+        <v>2.224631634832583</v>
       </c>
       <c r="U67">
         <v>0.09000000000000001</v>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.572133660658905</v>
+        <v>1.548313453679225</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09290866692800528</v>
+        <v>0.09302843166793887</v>
       </c>
       <c r="C68">
-        <v>183.9011534493975</v>
+        <v>161.3665989850399</v>
       </c>
       <c r="D68">
-        <v>1386.009699979525</v>
+        <v>1382.494971977745</v>
       </c>
       <c r="E68">
-        <v>264.7259002723586</v>
+        <v>283.7457267349362</v>
       </c>
       <c r="F68">
-        <v>1255.308546530128</v>
+        <v>1274.328372992705</v>
       </c>
       <c r="G68">
         <v>53.2</v>
@@ -6869,28 +6869,28 @@
         <v>174.925</v>
       </c>
       <c r="M68">
-        <v>112.9777691877115</v>
+        <v>114.6895535693435</v>
       </c>
       <c r="N68">
-        <v>61.94723081228844</v>
+        <v>60.23544643065645</v>
       </c>
       <c r="O68">
-        <v>15.44963936458474</v>
+        <v>15.02272033980572</v>
       </c>
       <c r="P68">
-        <v>46.4975914477037</v>
+        <v>45.21272609085074</v>
       </c>
       <c r="Q68">
-        <v>168.6975914477037</v>
+        <v>167.4127260908507</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1421265497882508</v>
+        <v>0.1447492474786026</v>
       </c>
       <c r="T68">
-        <v>2.224631634832583</v>
+        <v>2.285202020291054</v>
       </c>
       <c r="U68">
         <v>0.09000000000000001</v>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.548313453679225</v>
+        <v>1.525204297654162</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09302843166793887</v>
+        <v>0.09314819640787245</v>
       </c>
       <c r="C69">
-        <v>161.3665989850399</v>
+        <v>138.8498251550884</v>
       </c>
       <c r="D69">
-        <v>1382.494971977745</v>
+        <v>1378.998024610372</v>
       </c>
       <c r="E69">
-        <v>283.7457267349362</v>
+        <v>302.765553197514</v>
       </c>
       <c r="F69">
-        <v>1274.328372992705</v>
+        <v>1293.348199455283</v>
       </c>
       <c r="G69">
         <v>53.2</v>
@@ -6951,28 +6951,28 @@
         <v>174.925</v>
       </c>
       <c r="M69">
-        <v>114.6895535693435</v>
+        <v>116.4013379509755</v>
       </c>
       <c r="N69">
-        <v>60.23544643065645</v>
+        <v>58.52366204902444</v>
       </c>
       <c r="O69">
-        <v>15.02272033980572</v>
+        <v>14.5958013150267</v>
       </c>
       <c r="P69">
-        <v>45.21272609085074</v>
+        <v>43.92786073399774</v>
       </c>
       <c r="Q69">
-        <v>167.4127260908507</v>
+        <v>166.1278607339977</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1447492474786026</v>
+        <v>0.1475358637746014</v>
       </c>
       <c r="T69">
-        <v>2.285202020291054</v>
+        <v>2.349558054840679</v>
       </c>
       <c r="U69">
         <v>0.09000000000000001</v>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.525204297654162</v>
+        <v>1.502774822688659</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09314819640787245</v>
+        <v>0.1256313265199632</v>
       </c>
       <c r="C70">
-        <v>138.8498251550884</v>
+        <v>-441.2802096732903</v>
       </c>
       <c r="D70">
-        <v>1378.998024610372</v>
+        <v>817.8878162445706</v>
       </c>
       <c r="E70">
-        <v>302.765553197514</v>
+        <v>321.7853796600916</v>
       </c>
       <c r="F70">
-        <v>1293.348199455283</v>
+        <v>1312.368025917861</v>
       </c>
       <c r="G70">
         <v>53.2</v>
@@ -7033,45 +7033,45 @@
         <v>174.925</v>
       </c>
       <c r="M70">
-        <v>116.4013379509755</v>
+        <v>192.655626204742</v>
       </c>
       <c r="N70">
-        <v>58.52366204902444</v>
+        <v>-17.73062620474204</v>
       </c>
       <c r="O70">
-        <v>14.5958013150267</v>
+        <v>-4.422018175462664</v>
       </c>
       <c r="P70">
-        <v>43.92786073399774</v>
+        <v>-13.30860802927937</v>
       </c>
       <c r="Q70">
-        <v>166.1278607339977</v>
+        <v>108.8913919707206</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1475358637746014</v>
+        <v>0.1525051594051955</v>
       </c>
       <c r="T70">
-        <v>2.349558054840679</v>
+        <v>2.46432238811075</v>
       </c>
       <c r="U70">
-        <v>0.09000000000000001</v>
+        <v>0.1468</v>
       </c>
       <c r="V70">
-        <v>0.2494</v>
+        <v>0.2264470332864132</v>
       </c>
       <c r="W70">
-        <v>0.067554</v>
+        <v>0.1135575755135545</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y70">
-        <v>1.502774822688659</v>
+        <v>0.9079672545565887</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1256313265199632</v>
+        <v>0.1266413265199632</v>
       </c>
       <c r="C71">
-        <v>-441.2802096732903</v>
+        <v>-470.5184074809133</v>
       </c>
       <c r="D71">
-        <v>817.8878162445706</v>
+        <v>807.6694448995254</v>
       </c>
       <c r="E71">
-        <v>321.7853796600916</v>
+        <v>340.8052061226695</v>
       </c>
       <c r="F71">
-        <v>1312.368025917861</v>
+        <v>1331.387852380439</v>
       </c>
       <c r="G71">
         <v>53.2</v>
@@ -7115,37 +7115,37 @@
         <v>174.925</v>
       </c>
       <c r="M71">
-        <v>192.655626204742</v>
+        <v>195.4477367294484</v>
       </c>
       <c r="N71">
-        <v>-17.73062620474204</v>
+        <v>-20.52273672944847</v>
       </c>
       <c r="O71">
-        <v>-4.422018175462664</v>
+        <v>-5.118370540324448</v>
       </c>
       <c r="P71">
-        <v>-13.30860802927937</v>
+        <v>-15.40436618912402</v>
       </c>
       <c r="Q71">
-        <v>108.8913919707206</v>
+        <v>106.795633810876</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1525051594051955</v>
+        <v>0.1560619980520353</v>
       </c>
       <c r="T71">
-        <v>2.46432238811075</v>
+        <v>2.546466467714442</v>
       </c>
       <c r="U71">
         <v>0.1468</v>
       </c>
       <c r="V71">
-        <v>0.2264470332864132</v>
+        <v>0.2232120756680359</v>
       </c>
       <c r="W71">
-        <v>0.1135575755135545</v>
+        <v>0.1140324672919324</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.9079672545565887</v>
+        <v>0.8949962937772087</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1266413265199632</v>
+        <v>0.1276513265199632</v>
       </c>
       <c r="C72">
-        <v>-470.5184074809133</v>
+        <v>-499.5044272115936</v>
       </c>
       <c r="D72">
-        <v>807.6694448995254</v>
+        <v>797.7032516314227</v>
       </c>
       <c r="E72">
-        <v>340.8052061226695</v>
+        <v>359.8250325852471</v>
       </c>
       <c r="F72">
-        <v>1331.387852380439</v>
+        <v>1350.407678843016</v>
       </c>
       <c r="G72">
         <v>53.2</v>
@@ -7197,37 +7197,37 @@
         <v>174.925</v>
       </c>
       <c r="M72">
-        <v>195.4477367294484</v>
+        <v>198.2398472541548</v>
       </c>
       <c r="N72">
-        <v>-20.52273672944847</v>
+        <v>-23.31484725415487</v>
       </c>
       <c r="O72">
-        <v>-5.118370540324448</v>
+        <v>-5.814722905186224</v>
       </c>
       <c r="P72">
-        <v>-15.40436618912402</v>
+        <v>-17.50012434896865</v>
       </c>
       <c r="Q72">
-        <v>106.795633810876</v>
+        <v>104.6998756510313</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1560619980520353</v>
+        <v>0.1598641359158986</v>
       </c>
       <c r="T72">
-        <v>2.546466467714442</v>
+        <v>2.634275656256319</v>
       </c>
       <c r="U72">
         <v>0.1468</v>
       </c>
       <c r="V72">
-        <v>0.2232120756680359</v>
+        <v>0.2200682436163734</v>
       </c>
       <c r="W72">
-        <v>0.1140324672919324</v>
+        <v>0.1144939818371164</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.8949962937772087</v>
+        <v>0.8823907121747128</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1276513265199632</v>
+        <v>0.1286613265199632</v>
       </c>
       <c r="C73">
-        <v>-499.5044272115931</v>
+        <v>-528.2474902911184</v>
       </c>
       <c r="D73">
-        <v>797.703251631423</v>
+        <v>787.9800150144755</v>
       </c>
       <c r="E73">
-        <v>359.8250325852468</v>
+        <v>378.8448590478247</v>
       </c>
       <c r="F73">
-        <v>1350.407678843016</v>
+        <v>1369.427505305594</v>
       </c>
       <c r="G73">
         <v>53.2</v>
@@ -7279,37 +7279,37 @@
         <v>174.925</v>
       </c>
       <c r="M73">
-        <v>198.2398472541548</v>
+        <v>201.0319577788612</v>
       </c>
       <c r="N73">
-        <v>-23.31484725415484</v>
+        <v>-26.10695777886127</v>
       </c>
       <c r="O73">
-        <v>-5.814722905186218</v>
+        <v>-6.511075270048002</v>
       </c>
       <c r="P73">
-        <v>-17.50012434896862</v>
+        <v>-19.59588250881327</v>
       </c>
       <c r="Q73">
-        <v>104.6998756510314</v>
+        <v>102.6041174911867</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1598641359158986</v>
+        <v>0.1639378550557521</v>
       </c>
       <c r="T73">
-        <v>2.634275656256318</v>
+        <v>2.728356929694044</v>
       </c>
       <c r="U73">
         <v>0.1468</v>
       </c>
       <c r="V73">
-        <v>0.2200682436163734</v>
+        <v>0.2170117402328126</v>
       </c>
       <c r="W73">
-        <v>0.1144939818371164</v>
+        <v>0.1149426765338231</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.8823907121747129</v>
+        <v>0.8701352856167307</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1286613265199632</v>
+        <v>0.1296713265199632</v>
       </c>
       <c r="C74">
-        <v>-528.2474902911184</v>
+        <v>-556.7563739581886</v>
       </c>
       <c r="D74">
-        <v>787.9800150144755</v>
+        <v>778.4909578099829</v>
       </c>
       <c r="E74">
-        <v>378.8448590478247</v>
+        <v>397.8646855104023</v>
       </c>
       <c r="F74">
-        <v>1369.427505305594</v>
+        <v>1388.447331768172</v>
       </c>
       <c r="G74">
         <v>53.2</v>
@@ -7361,37 +7361,37 @@
         <v>174.925</v>
       </c>
       <c r="M74">
-        <v>201.0319577788612</v>
+        <v>203.8240683035676</v>
       </c>
       <c r="N74">
-        <v>-26.10695777886127</v>
+        <v>-28.89906830356765</v>
       </c>
       <c r="O74">
-        <v>-6.511075270048002</v>
+        <v>-7.207427634909771</v>
       </c>
       <c r="P74">
-        <v>-19.59588250881327</v>
+        <v>-21.69164066865788</v>
       </c>
       <c r="Q74">
-        <v>102.6041174911867</v>
+        <v>100.5083593313421</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1639378550557521</v>
+        <v>0.1683133311689281</v>
       </c>
       <c r="T74">
-        <v>2.728356929694044</v>
+        <v>2.829407186349379</v>
       </c>
       <c r="U74">
         <v>0.1468</v>
       </c>
       <c r="V74">
-        <v>0.2170117402328126</v>
+        <v>0.2140389766679796</v>
       </c>
       <c r="W74">
-        <v>0.1149426765338231</v>
+        <v>0.1153790782251406</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.8701352856167307</v>
+        <v>0.8582156241699262</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1296713265199632</v>
+        <v>0.1306813265199632</v>
       </c>
       <c r="C75">
-        <v>-556.7563739581886</v>
+        <v>-585.0394376912533</v>
       </c>
       <c r="D75">
-        <v>778.4909578099829</v>
+        <v>769.2277205394961</v>
       </c>
       <c r="E75">
-        <v>397.8646855104023</v>
+        <v>416.8845119729801</v>
       </c>
       <c r="F75">
-        <v>1388.447331768172</v>
+        <v>1407.467158230749</v>
       </c>
       <c r="G75">
         <v>53.2</v>
@@ -7443,37 +7443,37 @@
         <v>174.925</v>
       </c>
       <c r="M75">
-        <v>203.8240683035676</v>
+        <v>206.616178828274</v>
       </c>
       <c r="N75">
-        <v>-28.89906830356765</v>
+        <v>-31.69117882827408</v>
       </c>
       <c r="O75">
-        <v>-7.207427634909771</v>
+        <v>-7.903779999771555</v>
       </c>
       <c r="P75">
-        <v>-21.69164066865788</v>
+        <v>-23.78739882850252</v>
       </c>
       <c r="Q75">
-        <v>100.5083593313421</v>
+        <v>98.41260117149747</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1683133311689281</v>
+        <v>0.173025382367733</v>
       </c>
       <c r="T75">
-        <v>2.829407186349379</v>
+        <v>2.938230539670509</v>
       </c>
       <c r="U75">
         <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.2140389766679796</v>
+        <v>0.2111465580643583</v>
       </c>
       <c r="W75">
-        <v>0.1153790782251406</v>
+        <v>0.1158036852761522</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.8582156241699262</v>
+        <v>0.8466181157351974</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1306813265199632</v>
+        <v>0.1316913265199632</v>
       </c>
       <c r="C76">
-        <v>-585.0394376912533</v>
+        <v>-613.1046477708172</v>
       </c>
       <c r="D76">
-        <v>769.2277205394961</v>
+        <v>760.1823369225098</v>
       </c>
       <c r="E76">
-        <v>416.8845119729801</v>
+        <v>435.9043384355577</v>
       </c>
       <c r="F76">
-        <v>1407.467158230749</v>
+        <v>1426.486984693327</v>
       </c>
       <c r="G76">
         <v>53.2</v>
@@ -7525,37 +7525,37 @@
         <v>174.925</v>
       </c>
       <c r="M76">
-        <v>206.616178828274</v>
+        <v>209.4082893529804</v>
       </c>
       <c r="N76">
-        <v>-31.69117882827408</v>
+        <v>-34.48328935298048</v>
       </c>
       <c r="O76">
-        <v>-7.903779999771555</v>
+        <v>-8.600132364633332</v>
       </c>
       <c r="P76">
-        <v>-23.78739882850252</v>
+        <v>-25.88315698834715</v>
       </c>
       <c r="Q76">
-        <v>98.41260117149747</v>
+        <v>96.31684301165285</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.173025382367733</v>
+        <v>0.1781143976624424</v>
       </c>
       <c r="T76">
-        <v>2.938230539670509</v>
+        <v>3.055759761257329</v>
       </c>
       <c r="U76">
         <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.2111465580643583</v>
+        <v>0.2083312706235002</v>
       </c>
       <c r="W76">
-        <v>0.1158036852761522</v>
+        <v>0.1162169694724702</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8466181157351974</v>
+        <v>0.8353298741920615</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1316913265199632</v>
+        <v>0.1327013265199632</v>
       </c>
       <c r="C77">
-        <v>-613.1046477708172</v>
+        <v>-640.9596001289169</v>
       </c>
       <c r="D77">
-        <v>760.1823369225098</v>
+        <v>751.3472110269877</v>
       </c>
       <c r="E77">
-        <v>435.9043384355577</v>
+        <v>454.9241648981354</v>
       </c>
       <c r="F77">
-        <v>1426.486984693327</v>
+        <v>1445.506811155905</v>
       </c>
       <c r="G77">
         <v>53.2</v>
@@ -7607,37 +7607,37 @@
         <v>174.925</v>
       </c>
       <c r="M77">
-        <v>209.4082893529804</v>
+        <v>212.2003998776868</v>
       </c>
       <c r="N77">
-        <v>-34.48328935298048</v>
+        <v>-37.27539987768688</v>
       </c>
       <c r="O77">
-        <v>-8.600132364633332</v>
+        <v>-9.296484729495107</v>
       </c>
       <c r="P77">
-        <v>-25.88315698834715</v>
+        <v>-27.97891514819177</v>
       </c>
       <c r="Q77">
-        <v>96.31684301165285</v>
+        <v>94.22108485180821</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1781143976624424</v>
+        <v>0.1836274975650441</v>
       </c>
       <c r="T77">
-        <v>3.055759761257329</v>
+        <v>3.183083084643052</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.2083312706235002</v>
+        <v>0.2055900696942436</v>
       </c>
       <c r="W77">
-        <v>0.1162169694724702</v>
+        <v>0.1166193777688851</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8353298741920615</v>
+        <v>0.8243386916369028</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1327013265199632</v>
+        <v>0.1337113265199632</v>
       </c>
       <c r="C78">
-        <v>-640.9596001289169</v>
+        <v>-668.6115416235086</v>
       </c>
       <c r="D78">
-        <v>751.3472110269877</v>
+        <v>742.7150959949738</v>
       </c>
       <c r="E78">
-        <v>454.9241648981354</v>
+        <v>473.9439913607132</v>
       </c>
       <c r="F78">
-        <v>1445.506811155905</v>
+        <v>1464.526637618482</v>
       </c>
       <c r="G78">
         <v>53.2</v>
@@ -7689,37 +7689,37 @@
         <v>174.925</v>
       </c>
       <c r="M78">
-        <v>212.2003998776868</v>
+        <v>214.9925104023932</v>
       </c>
       <c r="N78">
-        <v>-37.27539987768688</v>
+        <v>-40.06751040239328</v>
       </c>
       <c r="O78">
-        <v>-9.296484729495107</v>
+        <v>-9.992837094356885</v>
       </c>
       <c r="P78">
-        <v>-27.97891514819177</v>
+        <v>-30.0746733080364</v>
       </c>
       <c r="Q78">
-        <v>94.22108485180821</v>
+        <v>92.12532669196359</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1836274975650441</v>
+        <v>0.1896199974591765</v>
       </c>
       <c r="T78">
-        <v>3.183083084643052</v>
+        <v>3.321478001366662</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.2055900696942436</v>
+        <v>0.2029200687891235</v>
       </c>
       <c r="W78">
-        <v>0.1166193777688851</v>
+        <v>0.1170113339017567</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8243386916369028</v>
+        <v>0.813632994342917</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1337113265199632</v>
+        <v>0.1347213265199632</v>
       </c>
       <c r="C79">
-        <v>-668.6115416235086</v>
+        <v>-696.0673898630049</v>
       </c>
       <c r="D79">
-        <v>742.7150959949738</v>
+        <v>734.2790742180551</v>
       </c>
       <c r="E79">
-        <v>473.9439913607132</v>
+        <v>492.9638178232908</v>
       </c>
       <c r="F79">
-        <v>1464.526637618482</v>
+        <v>1483.54646408106</v>
       </c>
       <c r="G79">
         <v>53.2</v>
@@ -7771,37 +7771,37 @@
         <v>174.925</v>
       </c>
       <c r="M79">
-        <v>214.9925104023932</v>
+        <v>217.7846209270996</v>
       </c>
       <c r="N79">
-        <v>-40.06751040239328</v>
+        <v>-42.85962092709968</v>
       </c>
       <c r="O79">
-        <v>-9.992837094356885</v>
+        <v>-10.68918945921866</v>
       </c>
       <c r="P79">
-        <v>-30.0746733080364</v>
+        <v>-32.17043146788102</v>
       </c>
       <c r="Q79">
-        <v>92.12532669196359</v>
+        <v>90.02956853211896</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1896199974591765</v>
+        <v>0.1961572700709572</v>
       </c>
       <c r="T79">
-        <v>3.321478001366662</v>
+        <v>3.472454274156056</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.2029200687891235</v>
+        <v>0.2003185294456732</v>
       </c>
       <c r="W79">
-        <v>0.1170113339017567</v>
+        <v>0.1173932398773752</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.813632994342917</v>
+        <v>0.8032018021077515</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1347213265199632</v>
+        <v>0.1800386477975829</v>
       </c>
       <c r="C80">
-        <v>-696.0673898630049</v>
+        <v>-962.9708270421376</v>
       </c>
       <c r="D80">
-        <v>734.2790742180551</v>
+        <v>486.3954635015003</v>
       </c>
       <c r="E80">
-        <v>492.9638178232908</v>
+        <v>511.9836442858686</v>
       </c>
       <c r="F80">
-        <v>1483.54646408106</v>
+        <v>1502.566290543638</v>
       </c>
       <c r="G80">
         <v>53.2</v>
@@ -7853,45 +7853,45 @@
         <v>174.925</v>
       </c>
       <c r="M80">
-        <v>217.7846209270996</v>
+        <v>301.7153111411625</v>
       </c>
       <c r="N80">
-        <v>-42.85962092709968</v>
+        <v>-126.7903111411625</v>
       </c>
       <c r="O80">
-        <v>-10.68918945921866</v>
+        <v>-31.62150359860594</v>
       </c>
       <c r="P80">
-        <v>-32.17043146788102</v>
+        <v>-95.16880754255659</v>
       </c>
       <c r="Q80">
-        <v>90.02956853211896</v>
+        <v>27.0311924574434</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1961572700709572</v>
+        <v>0.2111615271106203</v>
       </c>
       <c r="T80">
-        <v>3.472454274156056</v>
+        <v>3.818972912485456</v>
       </c>
       <c r="U80">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.2003185294456732</v>
+        <v>0.1445942363183177</v>
       </c>
       <c r="W80">
-        <v>0.1173932398773752</v>
+        <v>0.1717654773472818</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y80">
-        <v>0.8032018021077515</v>
+        <v>0.5797683894078495</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1800386477975829</v>
+        <v>0.1815886477975829</v>
       </c>
       <c r="C81">
-        <v>-962.9708270421376</v>
+        <v>-987.5427595213475</v>
       </c>
       <c r="D81">
-        <v>486.3954635015003</v>
+        <v>480.843357484868</v>
       </c>
       <c r="E81">
-        <v>511.9836442858686</v>
+        <v>531.0034707484463</v>
       </c>
       <c r="F81">
-        <v>1502.566290543638</v>
+        <v>1521.586117006216</v>
       </c>
       <c r="G81">
         <v>53.2</v>
@@ -7935,37 +7935,37 @@
         <v>174.925</v>
       </c>
       <c r="M81">
-        <v>301.7153111411625</v>
+        <v>305.5344922948481</v>
       </c>
       <c r="N81">
-        <v>-126.7903111411625</v>
+        <v>-130.6094922948481</v>
       </c>
       <c r="O81">
-        <v>-31.62150359860594</v>
+        <v>-32.57400737833512</v>
       </c>
       <c r="P81">
-        <v>-95.16880754255659</v>
+        <v>-98.03548491651298</v>
       </c>
       <c r="Q81">
-        <v>27.0311924574434</v>
+        <v>24.164515083487</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2111615271106203</v>
+        <v>0.2194296034661513</v>
       </c>
       <c r="T81">
-        <v>3.818972912485456</v>
+        <v>4.009921558109729</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.1445942363183177</v>
+        <v>0.1427868083643387</v>
       </c>
       <c r="W81">
-        <v>0.1717654773472818</v>
+        <v>0.1721284088804408</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.5797683894078495</v>
+        <v>0.5725212845402514</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1815886477975829</v>
+        <v>0.1831386477975829</v>
       </c>
       <c r="C82">
-        <v>-987.5427595213475</v>
+        <v>-1011.989370185267</v>
       </c>
       <c r="D82">
-        <v>480.843357484868</v>
+        <v>475.4165732835264</v>
       </c>
       <c r="E82">
-        <v>531.0034707484463</v>
+        <v>550.0232972110241</v>
       </c>
       <c r="F82">
-        <v>1521.586117006216</v>
+        <v>1540.605943468793</v>
       </c>
       <c r="G82">
         <v>53.2</v>
@@ -8017,37 +8017,37 @@
         <v>174.925</v>
       </c>
       <c r="M82">
-        <v>305.5344922948481</v>
+        <v>309.3536734485337</v>
       </c>
       <c r="N82">
-        <v>-130.6094922948481</v>
+        <v>-134.4286734485337</v>
       </c>
       <c r="O82">
-        <v>-32.57400737833512</v>
+        <v>-33.52651115806432</v>
       </c>
       <c r="P82">
-        <v>-98.03548491651298</v>
+        <v>-100.9021622904694</v>
       </c>
       <c r="Q82">
-        <v>24.164515083487</v>
+        <v>21.29783770953057</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2194296034661513</v>
+        <v>0.2285680036485802</v>
       </c>
       <c r="T82">
-        <v>4.009921558109729</v>
+        <v>4.220970061168135</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.1427868083643387</v>
+        <v>0.1410240082610753</v>
       </c>
       <c r="W82">
-        <v>0.1721284088804408</v>
+        <v>0.1724823791411761</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.5725212845402514</v>
+        <v>0.5654531205335815</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1831386477975829</v>
+        <v>0.1846886477975829</v>
       </c>
       <c r="C83">
-        <v>-1011.989370185267</v>
+        <v>-1036.314854815555</v>
       </c>
       <c r="D83">
-        <v>475.4165732835264</v>
+        <v>470.1109151158162</v>
       </c>
       <c r="E83">
-        <v>550.0232972110241</v>
+        <v>569.0431236736017</v>
       </c>
       <c r="F83">
-        <v>1540.605943468793</v>
+        <v>1559.625769931371</v>
       </c>
       <c r="G83">
         <v>53.2</v>
@@ -8099,37 +8099,37 @@
         <v>174.925</v>
       </c>
       <c r="M83">
-        <v>309.3536734485337</v>
+        <v>313.1728546022193</v>
       </c>
       <c r="N83">
-        <v>-134.4286734485337</v>
+        <v>-138.2478546022194</v>
       </c>
       <c r="O83">
-        <v>-33.52651115806432</v>
+        <v>-34.47901493779352</v>
       </c>
       <c r="P83">
-        <v>-100.9021622904694</v>
+        <v>-103.7688396644259</v>
       </c>
       <c r="Q83">
-        <v>21.29783770953057</v>
+        <v>18.43116033557413</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2285680036485802</v>
+        <v>0.238721781629057</v>
       </c>
       <c r="T83">
-        <v>4.220970061168135</v>
+        <v>4.455468397899699</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.1410240082610753</v>
+        <v>0.1393042032822817</v>
       </c>
       <c r="W83">
-        <v>0.1724823791411761</v>
+        <v>0.1728277159809178</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.5654531205335815</v>
+        <v>0.5585573507709769</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1846886477975829</v>
+        <v>0.1862386477975829</v>
       </c>
       <c r="C84">
-        <v>-1036.314854815555</v>
+        <v>-1060.523223961054</v>
       </c>
       <c r="D84">
-        <v>470.1109151158162</v>
+        <v>464.922372432895</v>
       </c>
       <c r="E84">
-        <v>569.0431236736017</v>
+        <v>588.0629501361793</v>
       </c>
       <c r="F84">
-        <v>1559.625769931371</v>
+        <v>1578.645596393949</v>
       </c>
       <c r="G84">
         <v>53.2</v>
@@ -8181,37 +8181,37 @@
         <v>174.925</v>
       </c>
       <c r="M84">
-        <v>313.1728546022193</v>
+        <v>316.9920357559049</v>
       </c>
       <c r="N84">
-        <v>-138.2478546022194</v>
+        <v>-142.067035755905</v>
       </c>
       <c r="O84">
-        <v>-34.47901493779352</v>
+        <v>-35.4315187175227</v>
       </c>
       <c r="P84">
-        <v>-103.7688396644259</v>
+        <v>-106.6355170383823</v>
       </c>
       <c r="Q84">
-        <v>18.43116033557413</v>
+        <v>15.56448296161773</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.238721781629057</v>
+        <v>0.2500701217248839</v>
       </c>
       <c r="T84">
-        <v>4.455468397899699</v>
+        <v>4.71755477424674</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.1393042032822817</v>
+        <v>0.1376258393873144</v>
       </c>
       <c r="W84">
-        <v>0.1728277159809178</v>
+        <v>0.1731647314510273</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.5585573507709769</v>
+        <v>0.551827744135182</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1862386477975829</v>
+        <v>0.1877886477975829</v>
       </c>
       <c r="C85">
-        <v>-1060.523223961054</v>
+        <v>-1084.618313048136</v>
       </c>
       <c r="D85">
-        <v>464.922372432895</v>
+        <v>459.8471098083906</v>
       </c>
       <c r="E85">
-        <v>588.0629501361793</v>
+        <v>607.0827765987572</v>
       </c>
       <c r="F85">
-        <v>1578.645596393949</v>
+        <v>1597.665422856526</v>
       </c>
       <c r="G85">
         <v>53.2</v>
@@ -8263,37 +8263,37 @@
         <v>174.925</v>
       </c>
       <c r="M85">
-        <v>316.9920357559049</v>
+        <v>320.8112169095905</v>
       </c>
       <c r="N85">
-        <v>-142.067035755905</v>
+        <v>-145.8862169095906</v>
       </c>
       <c r="O85">
-        <v>-35.4315187175227</v>
+        <v>-36.38402249725189</v>
       </c>
       <c r="P85">
-        <v>-106.6355170383823</v>
+        <v>-109.5021944123387</v>
       </c>
       <c r="Q85">
-        <v>15.56448296161773</v>
+        <v>12.69780558766129</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2500701217248839</v>
+        <v>0.2628370043326891</v>
       </c>
       <c r="T85">
-        <v>4.71755477424674</v>
+        <v>5.012401947637162</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.1376258393873144</v>
+        <v>0.1359874365374654</v>
       </c>
       <c r="W85">
-        <v>0.1731647314510273</v>
+        <v>0.173493722743277</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.551827744135182</v>
+        <v>0.5452583662288107</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1877886477975829</v>
+        <v>0.1893386477975829</v>
       </c>
       <c r="C86">
-        <v>-1084.618313048136</v>
+        <v>-1108.603791835989</v>
       </c>
       <c r="D86">
-        <v>459.8471098083904</v>
+        <v>454.881457483115</v>
       </c>
       <c r="E86">
-        <v>607.0827765987569</v>
+        <v>626.1026030613345</v>
       </c>
       <c r="F86">
-        <v>1597.665422856526</v>
+        <v>1616.685249319104</v>
       </c>
       <c r="G86">
         <v>53.2</v>
@@ -8345,37 +8345,37 @@
         <v>174.925</v>
       </c>
       <c r="M86">
-        <v>320.8112169095905</v>
+        <v>324.6303980632761</v>
       </c>
       <c r="N86">
-        <v>-145.8862169095905</v>
+        <v>-149.7053980632761</v>
       </c>
       <c r="O86">
-        <v>-36.38402249725188</v>
+        <v>-37.33652627698106</v>
       </c>
       <c r="P86">
-        <v>-109.5021944123387</v>
+        <v>-112.368871786295</v>
       </c>
       <c r="Q86">
-        <v>12.69780558766134</v>
+        <v>9.831128213704943</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.262837004332689</v>
+        <v>0.2773061379548682</v>
       </c>
       <c r="T86">
-        <v>5.01240194763716</v>
+        <v>5.346562077479637</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1359874365374654</v>
+        <v>0.134387584342907</v>
       </c>
       <c r="W86">
-        <v>0.173493722743277</v>
+        <v>0.1738149730639443</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.5452583662288109</v>
+        <v>0.5388435619202366</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1893386477975829</v>
+        <v>0.1908886477975829</v>
       </c>
       <c r="C87">
-        <v>-1108.603791835989</v>
+        <v>-1132.483173265834</v>
       </c>
       <c r="D87">
-        <v>454.881457483115</v>
+        <v>450.0219025158474</v>
       </c>
       <c r="E87">
-        <v>626.1026030613345</v>
+        <v>645.1224295239124</v>
       </c>
       <c r="F87">
-        <v>1616.685249319104</v>
+        <v>1635.705075781682</v>
       </c>
       <c r="G87">
         <v>53.2</v>
@@ -8427,37 +8427,37 @@
         <v>174.925</v>
       </c>
       <c r="M87">
-        <v>324.6303980632761</v>
+        <v>328.4495792169617</v>
       </c>
       <c r="N87">
-        <v>-149.7053980632761</v>
+        <v>-153.5245792169617</v>
       </c>
       <c r="O87">
-        <v>-37.33652627698106</v>
+        <v>-38.28903005671026</v>
       </c>
       <c r="P87">
-        <v>-112.368871786295</v>
+        <v>-115.2355491602515</v>
       </c>
       <c r="Q87">
-        <v>9.831128213704943</v>
+        <v>6.964450839748508</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2773061379548682</v>
+        <v>0.2938422906659303</v>
       </c>
       <c r="T87">
-        <v>5.346562077479637</v>
+        <v>5.728459368728182</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.134387584342907</v>
+        <v>0.1328249380133383</v>
       </c>
       <c r="W87">
-        <v>0.1738149730639443</v>
+        <v>0.1741287524469217</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5388435619202366</v>
+        <v>0.5325779391072105</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1908886477975829</v>
+        <v>0.1924386477975829</v>
       </c>
       <c r="C88">
-        <v>-1132.483173265834</v>
+        <v>-1156.259821748909</v>
       </c>
       <c r="D88">
-        <v>450.0219025158474</v>
+        <v>445.2650804953498</v>
       </c>
       <c r="E88">
-        <v>645.1224295239124</v>
+        <v>664.14225598649</v>
       </c>
       <c r="F88">
-        <v>1635.705075781682</v>
+        <v>1654.724902244259</v>
       </c>
       <c r="G88">
         <v>53.2</v>
@@ -8509,37 +8509,37 @@
         <v>174.925</v>
       </c>
       <c r="M88">
-        <v>328.4495792169617</v>
+        <v>332.2687603706473</v>
       </c>
       <c r="N88">
-        <v>-153.5245792169617</v>
+        <v>-157.3437603706473</v>
       </c>
       <c r="O88">
-        <v>-38.28903005671026</v>
+        <v>-39.24153383643944</v>
       </c>
       <c r="P88">
-        <v>-115.2355491602515</v>
+        <v>-118.1022265342079</v>
       </c>
       <c r="Q88">
-        <v>6.964450839748508</v>
+        <v>4.097773465792116</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2938422906659303</v>
+        <v>0.3129224668710018</v>
       </c>
       <c r="T88">
-        <v>5.728459368728182</v>
+        <v>6.169110089399581</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1328249380133383</v>
+        <v>0.1312982145878976</v>
       </c>
       <c r="W88">
-        <v>0.1741287524469217</v>
+        <v>0.1744353185107502</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5325779391072105</v>
+        <v>0.5264563536002311</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1924386477975829</v>
+        <v>0.1939886477975829</v>
       </c>
       <c r="C89">
-        <v>-1156.259821748909</v>
+        <v>-1179.936960934325</v>
       </c>
       <c r="D89">
-        <v>445.2650804953498</v>
+        <v>440.6077677725121</v>
       </c>
       <c r="E89">
-        <v>664.14225598649</v>
+        <v>683.1620824490678</v>
       </c>
       <c r="F89">
-        <v>1654.724902244259</v>
+        <v>1673.744728706837</v>
       </c>
       <c r="G89">
         <v>53.2</v>
@@ -8591,37 +8591,37 @@
         <v>174.925</v>
       </c>
       <c r="M89">
-        <v>332.2687603706473</v>
+        <v>336.0879415243329</v>
       </c>
       <c r="N89">
-        <v>-157.3437603706473</v>
+        <v>-161.162941524333</v>
       </c>
       <c r="O89">
-        <v>-39.24153383643944</v>
+        <v>-40.19403761616864</v>
       </c>
       <c r="P89">
-        <v>-118.1022265342079</v>
+        <v>-120.9689039081643</v>
       </c>
       <c r="Q89">
-        <v>4.097773465792116</v>
+        <v>1.231096091835681</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3129224668710018</v>
+        <v>0.3351826724435853</v>
       </c>
       <c r="T89">
-        <v>6.169110089399581</v>
+        <v>6.683202596849546</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1312982145878976</v>
+        <v>0.1298061894221261</v>
       </c>
       <c r="W89">
-        <v>0.1744353185107502</v>
+        <v>0.1747349171640371</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5264563536002311</v>
+        <v>0.5204738950365921</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1939886477975829</v>
+        <v>0.1955386477975829</v>
       </c>
       <c r="C90">
-        <v>-1179.936960934325</v>
+        <v>-1203.517680994463</v>
       </c>
       <c r="D90">
-        <v>440.6077677725121</v>
+        <v>436.0468741749514</v>
       </c>
       <c r="E90">
-        <v>683.1620824490678</v>
+        <v>702.1819089116455</v>
       </c>
       <c r="F90">
-        <v>1673.744728706837</v>
+        <v>1692.764555169415</v>
       </c>
       <c r="G90">
         <v>53.2</v>
@@ -8673,37 +8673,37 @@
         <v>174.925</v>
       </c>
       <c r="M90">
-        <v>336.0879415243329</v>
+        <v>339.9071226780185</v>
       </c>
       <c r="N90">
-        <v>-161.162941524333</v>
+        <v>-164.9821226780185</v>
       </c>
       <c r="O90">
-        <v>-40.19403761616864</v>
+        <v>-41.14654139589782</v>
       </c>
       <c r="P90">
-        <v>-120.9689039081643</v>
+        <v>-123.8355812821207</v>
       </c>
       <c r="Q90">
-        <v>1.231096091835681</v>
+        <v>-1.635581282120711</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3351826724435853</v>
+        <v>0.3614901881202749</v>
       </c>
       <c r="T90">
-        <v>6.683202596849546</v>
+        <v>7.290766469290415</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.1298061894221261</v>
+        <v>0.1283476929117651</v>
       </c>
       <c r="W90">
-        <v>0.1747349171640371</v>
+        <v>0.1750277832633176</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5204738950365921</v>
+        <v>0.5146258737440461</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1955386477975829</v>
+        <v>0.1970886477975829</v>
       </c>
       <c r="C91">
-        <v>-1203.517680994463</v>
+        <v>-1227.004945462538</v>
       </c>
       <c r="D91">
-        <v>436.0468741749514</v>
+        <v>431.5794361694544</v>
       </c>
       <c r="E91">
-        <v>702.1819089116455</v>
+        <v>721.2017353742233</v>
       </c>
       <c r="F91">
-        <v>1692.764555169415</v>
+        <v>1711.784381631993</v>
       </c>
       <c r="G91">
         <v>53.2</v>
@@ -8755,37 +8755,37 @@
         <v>174.925</v>
       </c>
       <c r="M91">
-        <v>339.9071226780185</v>
+        <v>343.7263038317041</v>
       </c>
       <c r="N91">
-        <v>-164.9821226780185</v>
+        <v>-168.8013038317042</v>
       </c>
       <c r="O91">
-        <v>-41.14654139589782</v>
+        <v>-42.09904517562702</v>
       </c>
       <c r="P91">
-        <v>-123.8355812821207</v>
+        <v>-126.7022586560771</v>
       </c>
       <c r="Q91">
-        <v>-1.635581282120711</v>
+        <v>-4.502258656077146</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3614901881202749</v>
+        <v>0.3930592069323024</v>
       </c>
       <c r="T91">
-        <v>7.290766469290415</v>
+        <v>8.019843116219455</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1283476929117651</v>
+        <v>0.1269216074349677</v>
       </c>
       <c r="W91">
-        <v>0.1750277832633176</v>
+        <v>0.1753141412270585</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5146258737440461</v>
+        <v>0.5089078084802234</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1970886477975829</v>
+        <v>0.1986386477975829</v>
       </c>
       <c r="C92">
-        <v>-1227.004945462538</v>
+        <v>-1250.401597654094</v>
       </c>
       <c r="D92">
-        <v>431.5794361694544</v>
+        <v>427.2026104404765</v>
       </c>
       <c r="E92">
-        <v>721.2017353742233</v>
+        <v>740.2215618368009</v>
       </c>
       <c r="F92">
-        <v>1711.784381631993</v>
+        <v>1730.80420809457</v>
       </c>
       <c r="G92">
         <v>53.2</v>
@@ -8837,37 +8837,37 @@
         <v>174.925</v>
       </c>
       <c r="M92">
-        <v>343.7263038317041</v>
+        <v>347.5454849853897</v>
       </c>
       <c r="N92">
-        <v>-168.8013038317042</v>
+        <v>-172.6204849853897</v>
       </c>
       <c r="O92">
-        <v>-42.09904517562702</v>
+        <v>-43.0515489553562</v>
       </c>
       <c r="P92">
-        <v>-126.7022586560771</v>
+        <v>-129.5689360300335</v>
       </c>
       <c r="Q92">
-        <v>-4.502258656077146</v>
+        <v>-7.368936030033552</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3930592069323024</v>
+        <v>0.4316435632581139</v>
       </c>
       <c r="T92">
-        <v>8.019843116219455</v>
+        <v>8.910936795799397</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.1269216074349677</v>
+        <v>0.1255268644961219</v>
       </c>
       <c r="W92">
-        <v>0.1753141412270585</v>
+        <v>0.1755942056091787</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5089078084802234</v>
+        <v>0.5033154149804407</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1986386477975829</v>
+        <v>0.2330533618305369</v>
       </c>
       <c r="C93">
-        <v>-1250.401597654094</v>
+        <v>-1347.935665616622</v>
       </c>
       <c r="D93">
-        <v>427.2026104404765</v>
+        <v>348.6883689405257</v>
       </c>
       <c r="E93">
-        <v>740.2215618368009</v>
+        <v>759.2413882993785</v>
       </c>
       <c r="F93">
-        <v>1730.80420809457</v>
+        <v>1749.824034557148</v>
       </c>
       <c r="G93">
         <v>53.2</v>
@@ -8919,45 +8919,45 @@
         <v>174.925</v>
       </c>
       <c r="M93">
-        <v>347.5454849853897</v>
+        <v>412.6085073485755</v>
       </c>
       <c r="N93">
-        <v>-172.6204849853897</v>
+        <v>-237.6835073485755</v>
       </c>
       <c r="O93">
-        <v>-43.0515489553562</v>
+        <v>-59.27826673273474</v>
       </c>
       <c r="P93">
-        <v>-129.5689360300335</v>
+        <v>-178.4052406158408</v>
       </c>
       <c r="Q93">
-        <v>-7.368936030033552</v>
+        <v>-56.20524061584081</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4316435632581139</v>
+        <v>0.4881829340773032</v>
       </c>
       <c r="T93">
-        <v>8.910936795799397</v>
+        <v>10.21669593712017</v>
       </c>
       <c r="U93">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.1255268644961219</v>
+        <v>0.1057329023105772</v>
       </c>
       <c r="W93">
-        <v>0.1755942056091787</v>
+        <v>0.2108681816351659</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y93">
-        <v>0.5033154149804407</v>
+        <v>0.4239490870512316</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2330533618305369</v>
+        <v>0.2349533618305368</v>
       </c>
       <c r="C94">
-        <v>-1347.935665616622</v>
+        <v>-1370.457982833663</v>
       </c>
       <c r="D94">
-        <v>348.6883689405257</v>
+        <v>345.185878186063</v>
       </c>
       <c r="E94">
-        <v>759.2413882993785</v>
+        <v>778.2612147619564</v>
       </c>
       <c r="F94">
-        <v>1749.824034557148</v>
+        <v>1768.843861019726</v>
       </c>
       <c r="G94">
         <v>53.2</v>
@@ -9001,37 +9001,37 @@
         <v>174.925</v>
       </c>
       <c r="M94">
-        <v>412.6085073485755</v>
+        <v>417.0933824284513</v>
       </c>
       <c r="N94">
-        <v>-237.6835073485755</v>
+        <v>-242.1683824284514</v>
       </c>
       <c r="O94">
-        <v>-59.27826673273474</v>
+        <v>-60.39679457765578</v>
       </c>
       <c r="P94">
-        <v>-178.4052406158408</v>
+        <v>-181.7715878507956</v>
       </c>
       <c r="Q94">
-        <v>-56.20524061584081</v>
+        <v>-59.57158785079559</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4881829340773032</v>
+        <v>0.5513804960883464</v>
       </c>
       <c r="T94">
-        <v>10.21669593712017</v>
+        <v>11.67622392813733</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.1057329023105772</v>
+        <v>0.1045959893825064</v>
       </c>
       <c r="W94">
-        <v>0.2108681816351659</v>
+        <v>0.211136265703605</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.4239490870512316</v>
+        <v>0.4193904947173474</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2349533618305368</v>
+        <v>0.2368533618305369</v>
       </c>
       <c r="C95">
-        <v>-1370.457982833663</v>
+        <v>-1392.91063645128</v>
       </c>
       <c r="D95">
-        <v>345.185878186063</v>
+        <v>341.7530510310231</v>
       </c>
       <c r="E95">
-        <v>778.2612147619564</v>
+        <v>797.281041224534</v>
       </c>
       <c r="F95">
-        <v>1768.843861019726</v>
+        <v>1787.863687482303</v>
       </c>
       <c r="G95">
         <v>53.2</v>
@@ -9083,37 +9083,37 @@
         <v>174.925</v>
       </c>
       <c r="M95">
-        <v>417.0933824284513</v>
+        <v>421.5782575083271</v>
       </c>
       <c r="N95">
-        <v>-242.1683824284514</v>
+        <v>-246.6532575083272</v>
       </c>
       <c r="O95">
-        <v>-60.39679457765578</v>
+        <v>-61.51532242257679</v>
       </c>
       <c r="P95">
-        <v>-181.7715878507956</v>
+        <v>-185.1379350857504</v>
       </c>
       <c r="Q95">
-        <v>-59.57158785079559</v>
+        <v>-62.93793508575038</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5513804960883464</v>
+        <v>0.635643912103071</v>
       </c>
       <c r="T95">
-        <v>11.67622392813733</v>
+        <v>13.62226124949356</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.1045959893825064</v>
+        <v>0.1034832660912032</v>
       </c>
       <c r="W95">
-        <v>0.211136265703605</v>
+        <v>0.2113986458556943</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.4193904947173474</v>
+        <v>0.4149288937097161</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2368533618305369</v>
+        <v>0.2387533618305369</v>
       </c>
       <c r="C96">
-        <v>-1392.91063645128</v>
+        <v>-1415.295684389135</v>
       </c>
       <c r="D96">
-        <v>341.7530510310231</v>
+        <v>338.3878295557463</v>
       </c>
       <c r="E96">
-        <v>797.281041224534</v>
+        <v>816.3008676871118</v>
       </c>
       <c r="F96">
-        <v>1787.863687482303</v>
+        <v>1806.883513944881</v>
       </c>
       <c r="G96">
         <v>53.2</v>
@@ -9165,37 +9165,37 @@
         <v>174.925</v>
       </c>
       <c r="M96">
-        <v>421.5782575083271</v>
+        <v>426.063132588203</v>
       </c>
       <c r="N96">
-        <v>-246.6532575083272</v>
+        <v>-251.138132588203</v>
       </c>
       <c r="O96">
-        <v>-61.51532242257679</v>
+        <v>-62.63385026749783</v>
       </c>
       <c r="P96">
-        <v>-185.1379350857504</v>
+        <v>-188.5042823207052</v>
       </c>
       <c r="Q96">
-        <v>-62.93793508575038</v>
+        <v>-66.30428232070517</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.635643912103071</v>
+        <v>0.7536126945236856</v>
       </c>
       <c r="T96">
-        <v>13.62226124949356</v>
+        <v>16.34671349939228</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.1034832660912032</v>
+        <v>0.102393968553401</v>
       </c>
       <c r="W96">
-        <v>0.2113986458556943</v>
+        <v>0.2116555022151081</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.4149288937097161</v>
+        <v>0.4105612211443506</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2387533618305369</v>
+        <v>0.2406533618305369</v>
       </c>
       <c r="C97">
-        <v>-1415.295684389135</v>
+        <v>-1437.615104300426</v>
       </c>
       <c r="D97">
-        <v>338.3878295557463</v>
+        <v>335.0882361070326</v>
       </c>
       <c r="E97">
-        <v>816.3008676871118</v>
+        <v>835.3206941496894</v>
       </c>
       <c r="F97">
-        <v>1806.883513944881</v>
+        <v>1825.903340407459</v>
       </c>
       <c r="G97">
         <v>53.2</v>
@@ -9247,37 +9247,37 @@
         <v>174.925</v>
       </c>
       <c r="M97">
-        <v>426.063132588203</v>
+        <v>430.5480076680788</v>
       </c>
       <c r="N97">
-        <v>-251.138132588203</v>
+        <v>-255.6230076680788</v>
       </c>
       <c r="O97">
-        <v>-62.63385026749783</v>
+        <v>-63.75237811241885</v>
       </c>
       <c r="P97">
-        <v>-188.5042823207052</v>
+        <v>-191.8706295556599</v>
       </c>
       <c r="Q97">
-        <v>-66.30428232070517</v>
+        <v>-69.67062955565996</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7536126945236856</v>
+        <v>0.9305658681546074</v>
       </c>
       <c r="T97">
-        <v>16.34671349939228</v>
+        <v>20.43339187424036</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.102393968553401</v>
+        <v>0.1013273647143031</v>
       </c>
       <c r="W97">
-        <v>0.2116555022151081</v>
+        <v>0.2119070074003673</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.4105612211443506</v>
+        <v>0.4062845417574302</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2406533618305369</v>
+        <v>0.2425533618305369</v>
       </c>
       <c r="C98">
-        <v>-1437.615104300426</v>
+        <v>-1459.870797447466</v>
       </c>
       <c r="D98">
-        <v>335.0882361070326</v>
+        <v>331.8523694225705</v>
       </c>
       <c r="E98">
-        <v>835.3206941496892</v>
+        <v>854.340520612267</v>
       </c>
       <c r="F98">
-        <v>1825.903340407458</v>
+        <v>1844.923166870036</v>
       </c>
       <c r="G98">
         <v>53.2</v>
@@ -9329,37 +9329,37 @@
         <v>174.925</v>
       </c>
       <c r="M98">
-        <v>430.5480076680788</v>
+        <v>435.0328827479546</v>
       </c>
       <c r="N98">
-        <v>-255.6230076680788</v>
+        <v>-260.1078827479546</v>
       </c>
       <c r="O98">
-        <v>-63.75237811241885</v>
+        <v>-64.87090595733989</v>
       </c>
       <c r="P98">
-        <v>-191.8706295556599</v>
+        <v>-195.2369767906148</v>
       </c>
       <c r="Q98">
-        <v>-69.67062955565996</v>
+        <v>-73.03697679061477</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9305658681546051</v>
+        <v>1.22548782420614</v>
       </c>
       <c r="T98">
-        <v>20.4333918742403</v>
+        <v>27.24452249898707</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.1013273647143031</v>
+        <v>0.1002827527069392</v>
       </c>
       <c r="W98">
-        <v>0.2119070074003673</v>
+        <v>0.2121533269117037</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.4062845417574302</v>
+        <v>0.4020960413269413</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2425533618305369</v>
+        <v>0.2444533618305369</v>
       </c>
       <c r="C99">
-        <v>-1459.870797447466</v>
+        <v>-1482.06459235484</v>
       </c>
       <c r="D99">
-        <v>331.8523694225705</v>
+        <v>328.6784009777737</v>
       </c>
       <c r="E99">
-        <v>854.340520612267</v>
+        <v>873.3603470748446</v>
       </c>
       <c r="F99">
-        <v>1844.923166870036</v>
+        <v>1863.942993332614</v>
       </c>
       <c r="G99">
         <v>53.2</v>
@@ -9411,37 +9411,37 @@
         <v>174.925</v>
       </c>
       <c r="M99">
-        <v>435.0328827479546</v>
+        <v>439.5177578278304</v>
       </c>
       <c r="N99">
-        <v>-260.1078827479546</v>
+        <v>-264.5927578278304</v>
       </c>
       <c r="O99">
-        <v>-64.87090595733989</v>
+        <v>-65.98943380226092</v>
       </c>
       <c r="P99">
-        <v>-195.2369767906148</v>
+        <v>-198.6033240255695</v>
       </c>
       <c r="Q99">
-        <v>-73.03697679061477</v>
+        <v>-76.40332402556953</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.22548782420614</v>
+        <v>1.81533173630921</v>
       </c>
       <c r="T99">
-        <v>27.24452249898707</v>
+        <v>40.86678374848061</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.1002827527069392</v>
+        <v>0.0992594593119704</v>
       </c>
       <c r="W99">
-        <v>0.2121533269117037</v>
+        <v>0.2123946194942374</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.4020960413269413</v>
+        <v>0.3979930204970745</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2444533618305369</v>
+        <v>0.2463533618305369</v>
       </c>
       <c r="C100">
-        <v>-1482.06459235484</v>
+        <v>-1504.198248254919</v>
       </c>
       <c r="D100">
-        <v>328.6784009777737</v>
+        <v>325.5645715402725</v>
       </c>
       <c r="E100">
-        <v>873.3603470748446</v>
+        <v>892.3801735374225</v>
       </c>
       <c r="F100">
-        <v>1863.942993332614</v>
+        <v>1882.962819795192</v>
       </c>
       <c r="G100">
         <v>53.2</v>
@@ -9493,37 +9493,37 @@
         <v>174.925</v>
       </c>
       <c r="M100">
-        <v>439.5177578278304</v>
+        <v>444.0026329077062</v>
       </c>
       <c r="N100">
-        <v>-264.5927578278304</v>
+        <v>-269.0776329077063</v>
       </c>
       <c r="O100">
-        <v>-65.98943380226092</v>
+        <v>-67.10796164718195</v>
       </c>
       <c r="P100">
-        <v>-198.6033240255695</v>
+        <v>-201.9696712605243</v>
       </c>
       <c r="Q100">
-        <v>-76.40332402556953</v>
+        <v>-79.76967126052435</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.81533173630921</v>
+        <v>3.58486347261842</v>
       </c>
       <c r="T100">
-        <v>40.86678374848061</v>
+        <v>81.73356749696121</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.0992594593119704</v>
+        <v>0.09825683851083938</v>
       </c>
       <c r="W100">
-        <v>0.2123946194942374</v>
+        <v>0.2126310374791441</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3979930204970745</v>
+        <v>0.3939728889769021</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2463533618305369</v>
-      </c>
-      <c r="C101">
-        <v>-1504.198248254919</v>
-      </c>
-      <c r="D101">
-        <v>325.5645715402725</v>
-      </c>
-      <c r="E101">
-        <v>892.3801735374225</v>
-      </c>
-      <c r="F101">
-        <v>1882.962819795192</v>
-      </c>
-      <c r="G101">
-        <v>53.2</v>
-      </c>
-      <c r="H101">
-        <v>911.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>297.1249999999999</v>
-      </c>
-      <c r="K101">
-        <v>122.2</v>
-      </c>
-      <c r="L101">
-        <v>174.925</v>
-      </c>
-      <c r="M101">
-        <v>444.0026329077062</v>
-      </c>
-      <c r="N101">
-        <v>-269.0776329077063</v>
-      </c>
-      <c r="O101">
-        <v>-67.10796164718195</v>
-      </c>
-      <c r="P101">
-        <v>-201.9696712605243</v>
-      </c>
-      <c r="Q101">
-        <v>-79.76967126052435</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.58486347261842</v>
-      </c>
-      <c r="T101">
-        <v>81.73356749696121</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.09825683851083938</v>
-      </c>
-      <c r="W101">
-        <v>0.2126310374791441</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3939728889769021</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
